--- a/S62aMigration/csv_and_xlsx_files/MASTER LEGACY cases S62A .xlsx
+++ b/S62aMigration/csv_and_xlsx_files/MASTER LEGACY cases S62A .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nisalihalwathura/PINS/S62A migration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nisalihalwathura/PINS/ODW-Service/odw-synapse-workspace/S62aMigration/csv_and_xlsx_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D559C45-6E9B-1641-9CD8-9A51F3D06573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4E55BF-62A7-4542-9DBF-19D642A1DA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34560" yWindow="-5440" windowWidth="38400" windowHeight="21000" xr2:uid="{D8D669B2-A080-7F4F-8289-7C521AE39FEF}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Not added for ref" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Template!$A$2:$EJ$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Template!$A$2:$EI$41</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -60,7 +60,7 @@
     <author>tc={81F1EE3A-7242-47C1-9EF2-8470DBE8D7A3}</author>
   </authors>
   <commentList>
-    <comment ref="AP1" authorId="0" shapeId="0" xr:uid="{62A6EB9B-683D-5248-B381-40CE452EACCA}">
+    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{62A6EB9B-683D-5248-B381-40CE452EACCA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -68,7 +68,7 @@
     Only complete if case is an application not relevant for pre-application</t>
       </text>
     </comment>
-    <comment ref="AX1" authorId="1" shapeId="0" xr:uid="{884F2B73-6820-B440-92C1-E7C9B68B200D}">
+    <comment ref="AW1" authorId="1" shapeId="0" xr:uid="{884F2B73-6820-B440-92C1-E7C9B68B200D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -76,7 +76,7 @@
     Leave blank if not relevant</t>
       </text>
     </comment>
-    <comment ref="DT1" authorId="2" shapeId="0" xr:uid="{81E8BF92-AB4B-734C-90C8-80D549D0639F}">
+    <comment ref="DS1" authorId="2" shapeId="0" xr:uid="{81E8BF92-AB4B-734C-90C8-80D549D0639F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -116,7 +116,7 @@
     This is to be used for both pre applications and applications </t>
       </text>
     </comment>
-    <comment ref="CX2" authorId="7" shapeId="0" xr:uid="{41A43461-2F93-BC41-8294-48DC9972CB00}">
+    <comment ref="CW2" authorId="7" shapeId="0" xr:uid="{41A43461-2F93-BC41-8294-48DC9972CB00}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -124,7 +124,7 @@
     Is this relevant prior to moving to MPA?</t>
       </text>
     </comment>
-    <comment ref="DR2" authorId="8" shapeId="0" xr:uid="{8A87C44E-7BB9-714B-B4C5-289C80BA2C73}">
+    <comment ref="DQ2" authorId="8" shapeId="0" xr:uid="{8A87C44E-7BB9-714B-B4C5-289C80BA2C73}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -132,7 +132,7 @@
     Where has the press notice been placed?</t>
       </text>
     </comment>
-    <comment ref="EI2" authorId="9" shapeId="0" xr:uid="{108C95A3-8670-3F46-B7DB-28A872D9ADC8}">
+    <comment ref="EH2" authorId="9" shapeId="0" xr:uid="{108C95A3-8670-3F46-B7DB-28A872D9ADC8}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -140,7 +140,7 @@
     Only necessary if decision is reviewed</t>
       </text>
     </comment>
-    <comment ref="EN2" authorId="10" shapeId="0" xr:uid="{557C5137-3BFB-1845-AAB1-EFF303B4988D}">
+    <comment ref="EM2" authorId="10" shapeId="0" xr:uid="{557C5137-3BFB-1845-AAB1-EFF303B4988D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="362">
   <si>
     <t>Case progress</t>
   </si>
@@ -1517,14 +1517,14 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1535,18 +1535,6 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1555,15 +1543,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1577,6 +1556,15 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1585,6 +1573,18 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1936,13 +1936,13 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AP1" dT="2026-06-18T10:49:04.58" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{62A6EB9B-683D-5248-B381-40CE452EACCA}">
+  <threadedComment ref="AO1" dT="2026-06-18T10:49:04.58" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{62A6EB9B-683D-5248-B381-40CE452EACCA}">
     <text>Only complete if case is an application not relevant for pre-application</text>
   </threadedComment>
-  <threadedComment ref="AX1" dT="2026-06-22T08:20:33.92" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{884F2B73-6820-B440-92C1-E7C9B68B200D}">
+  <threadedComment ref="AW1" dT="2026-06-22T08:20:33.92" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{884F2B73-6820-B440-92C1-E7C9B68B200D}">
     <text>Leave blank if not relevant</text>
   </threadedComment>
-  <threadedComment ref="DT1" dT="2026-06-18T11:06:10.18" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{81E8BF92-AB4B-734C-90C8-80D549D0639F}">
+  <threadedComment ref="DS1" dT="2026-06-18T11:06:10.18" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{81E8BF92-AB4B-734C-90C8-80D549D0639F}">
     <text>Only complete for pre-application</text>
   </threadedComment>
   <threadedComment ref="B2" dT="2026-06-17T15:23:33.29" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{55DCDFB5-17AD-7B42-98FE-734FF9E8E9AC}">
@@ -1957,16 +1957,16 @@
   <threadedComment ref="J2" dT="2026-06-16T14:45:40.42" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{68275D5E-2BE3-0E48-A0A8-5482389936C8}">
     <text xml:space="preserve">This is to be used for both pre applications and applications </text>
   </threadedComment>
-  <threadedComment ref="CX2" dT="2026-06-17T15:49:11.64" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{41A43461-2F93-BC41-8294-48DC9972CB00}">
+  <threadedComment ref="CW2" dT="2026-06-17T15:49:11.64" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{41A43461-2F93-BC41-8294-48DC9972CB00}">
     <text>Is this relevant prior to moving to MPA?</text>
   </threadedComment>
-  <threadedComment ref="DR2" dT="2026-06-19T08:56:29.22" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{8A87C44E-7BB9-714B-B4C5-289C80BA2C73}">
+  <threadedComment ref="DQ2" dT="2026-06-19T08:56:29.22" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{8A87C44E-7BB9-714B-B4C5-289C80BA2C73}">
     <text>Where has the press notice been placed?</text>
   </threadedComment>
-  <threadedComment ref="EI2" dT="2026-06-22T10:45:32.18" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{108C95A3-8670-3F46-B7DB-28A872D9ADC8}">
+  <threadedComment ref="EH2" dT="2026-06-22T10:45:32.18" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{108C95A3-8670-3F46-B7DB-28A872D9ADC8}">
     <text>Only necessary if decision is reviewed</text>
   </threadedComment>
-  <threadedComment ref="EN2" dT="2026-07-15T10:56:27.35" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{557C5137-3BFB-1845-AAB1-EFF303B4988D}">
+  <threadedComment ref="EM2" dT="2026-07-15T10:56:27.35" personId="{3DD021DC-6036-B841-AF93-3F522BD0BD2A}" id="{557C5137-3BFB-1845-AAB1-EFF303B4988D}">
     <text>Abbas doing a scrape of gov.uk to confirm which cases are uploaded</text>
   </threadedComment>
   <threadedComment ref="B3" dT="2026-07-01T09:07:04.19" personId="{64B43527-DDBB-2E43-ACDB-AB5D663623A1}" id="{81F1EE3A-7242-47C1-9EF2-8470DBE8D7A3}" done="1">
@@ -1977,7 +1977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7D8389-CC47-1246-87AB-996B447D177D}">
-  <dimension ref="A1:GN41"/>
+  <dimension ref="A1:GM41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="25" customWidth="1"/>
@@ -1989,184 +1989,184 @@
     <col min="9" max="9" width="22.5" style="25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.33203125" style="25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="29.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="25" width="29.1640625" style="25" customWidth="1"/>
-    <col min="26" max="26" width="33.6640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="29.1640625" style="25" customWidth="1"/>
-    <col min="32" max="32" width="31.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="41" width="29.1640625" style="25" customWidth="1"/>
-    <col min="42" max="42" width="24" style="25" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="17.1640625" style="25" customWidth="1"/>
-    <col min="45" max="45" width="22.1640625" style="25" customWidth="1"/>
-    <col min="46" max="46" width="20.6640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="20.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="23.1640625" style="25" customWidth="1"/>
-    <col min="49" max="49" width="20.33203125" style="25" customWidth="1"/>
-    <col min="50" max="50" width="22.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="51" max="54" width="20.33203125" style="25" customWidth="1"/>
-    <col min="55" max="55" width="22" style="25" bestFit="1" customWidth="1"/>
-    <col min="56" max="75" width="20.33203125" style="25" customWidth="1"/>
-    <col min="76" max="76" width="20.6640625" style="25" customWidth="1"/>
-    <col min="77" max="77" width="24.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="10.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="24.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="10.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="81" max="83" width="24.1640625" style="25" customWidth="1"/>
-    <col min="84" max="91" width="20.33203125" style="25" customWidth="1"/>
-    <col min="92" max="92" width="23" style="25" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="10" style="25" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="12.6640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="34.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="24.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="10.83203125" style="25"/>
-    <col min="98" max="98" width="13.1640625" style="25" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="34.1640625" style="25" customWidth="1"/>
-    <col min="100" max="110" width="25" style="25" customWidth="1"/>
-    <col min="111" max="111" width="30.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="112" max="114" width="25" style="25" customWidth="1"/>
-    <col min="115" max="115" width="30.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="116" max="127" width="25" style="25" customWidth="1"/>
-    <col min="128" max="128" width="28.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="129" max="135" width="28.33203125" style="25" customWidth="1"/>
-    <col min="136" max="136" width="12.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="20.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="138" max="138" width="12.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="18.83203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="140" max="140" width="23.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="141" max="144" width="36.33203125" style="25" customWidth="1"/>
-    <col min="145" max="186" width="10.83203125" style="25"/>
-    <col min="187" max="187" width="13.5" style="25" bestFit="1" customWidth="1"/>
-    <col min="188" max="188" width="10.83203125" style="25"/>
-    <col min="189" max="189" width="22" style="25" customWidth="1"/>
-    <col min="190" max="191" width="30.33203125" style="25" customWidth="1"/>
-    <col min="192" max="192" width="25.5" style="25" customWidth="1"/>
-    <col min="193" max="193" width="24.33203125" style="25" customWidth="1"/>
-    <col min="194" max="194" width="10.83203125" style="25"/>
-    <col min="195" max="195" width="25.6640625" style="25" customWidth="1"/>
-    <col min="196" max="196" width="14.1640625" style="25" customWidth="1"/>
-    <col min="197" max="16384" width="10.83203125" style="25"/>
+    <col min="12" max="24" width="29.1640625" style="25" customWidth="1"/>
+    <col min="25" max="25" width="33.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="29.1640625" style="25" customWidth="1"/>
+    <col min="31" max="31" width="31.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="32" max="40" width="29.1640625" style="25" customWidth="1"/>
+    <col min="41" max="41" width="24" style="25" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="17.1640625" style="25" customWidth="1"/>
+    <col min="44" max="44" width="22.1640625" style="25" customWidth="1"/>
+    <col min="45" max="45" width="20.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="20.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="23.1640625" style="25" customWidth="1"/>
+    <col min="48" max="48" width="20.33203125" style="25" customWidth="1"/>
+    <col min="49" max="49" width="22.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="50" max="53" width="20.33203125" style="25" customWidth="1"/>
+    <col min="54" max="54" width="22" style="25" bestFit="1" customWidth="1"/>
+    <col min="55" max="74" width="20.33203125" style="25" customWidth="1"/>
+    <col min="75" max="75" width="20.6640625" style="25" customWidth="1"/>
+    <col min="76" max="76" width="24.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="10.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="24.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="10.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="80" max="82" width="24.1640625" style="25" customWidth="1"/>
+    <col min="83" max="90" width="20.33203125" style="25" customWidth="1"/>
+    <col min="91" max="91" width="23" style="25" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="10" style="25" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="12.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="34.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="24.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="10.83203125" style="25"/>
+    <col min="97" max="97" width="13.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="34.1640625" style="25" customWidth="1"/>
+    <col min="99" max="109" width="25" style="25" customWidth="1"/>
+    <col min="110" max="110" width="30.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="111" max="113" width="25" style="25" customWidth="1"/>
+    <col min="114" max="114" width="30.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="115" max="126" width="25" style="25" customWidth="1"/>
+    <col min="127" max="127" width="28.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="128" max="134" width="28.33203125" style="25" customWidth="1"/>
+    <col min="135" max="135" width="12.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="20.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="12.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="18.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="23.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="140" max="143" width="36.33203125" style="25" customWidth="1"/>
+    <col min="144" max="185" width="10.83203125" style="25"/>
+    <col min="186" max="186" width="13.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="187" max="187" width="10.83203125" style="25"/>
+    <col min="188" max="188" width="22" style="25" customWidth="1"/>
+    <col min="189" max="190" width="30.33203125" style="25" customWidth="1"/>
+    <col min="191" max="191" width="25.5" style="25" customWidth="1"/>
+    <col min="192" max="192" width="24.33203125" style="25" customWidth="1"/>
+    <col min="193" max="193" width="10.83203125" style="25"/>
+    <col min="194" max="194" width="25.6640625" style="25" customWidth="1"/>
+    <col min="195" max="195" width="14.1640625" style="25" customWidth="1"/>
+    <col min="196" max="16384" width="10.83203125" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:196" s="6" customFormat="1" ht="23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:195" s="6" customFormat="1" ht="23" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="46" t="s">
+      <c r="C1" s="31"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="50" t="s">
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="51"/>
-      <c r="AD1" s="51"/>
-      <c r="AE1" s="51"/>
-      <c r="AF1" s="51"/>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="43" t="s">
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="48"/>
+      <c r="AM1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="AO1" s="44"/>
-      <c r="AP1" s="30" t="s">
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="AQ1" s="31"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="47" t="s">
+      <c r="AP1" s="44"/>
+      <c r="AQ1" s="45"/>
+      <c r="AR1" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="AT1" s="47"/>
-      <c r="AU1" s="47"/>
-      <c r="AV1" s="47"/>
-      <c r="AW1" s="47"/>
-      <c r="AX1" s="48" t="s">
+      <c r="AS1" s="40"/>
+      <c r="AT1" s="40"/>
+      <c r="AU1" s="40"/>
+      <c r="AV1" s="40"/>
+      <c r="AW1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="AY1" s="48"/>
-      <c r="AZ1" s="48"/>
-      <c r="BA1" s="48"/>
-      <c r="BB1" s="48"/>
-      <c r="BC1" s="49" t="s">
+      <c r="AX1" s="41"/>
+      <c r="AY1" s="41"/>
+      <c r="AZ1" s="41"/>
+      <c r="BA1" s="41"/>
+      <c r="BB1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="BD1" s="49"/>
-      <c r="BE1" s="49"/>
-      <c r="BF1" s="49"/>
-      <c r="BG1" s="49"/>
-      <c r="BH1" s="49"/>
-      <c r="BI1" s="49"/>
-      <c r="BJ1" s="49"/>
-      <c r="BK1" s="49"/>
-      <c r="BL1" s="49"/>
-      <c r="BM1" s="47" t="s">
+      <c r="BC1" s="42"/>
+      <c r="BD1" s="42"/>
+      <c r="BE1" s="42"/>
+      <c r="BF1" s="42"/>
+      <c r="BG1" s="42"/>
+      <c r="BH1" s="42"/>
+      <c r="BI1" s="42"/>
+      <c r="BJ1" s="42"/>
+      <c r="BK1" s="42"/>
+      <c r="BL1" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="BN1" s="47"/>
-      <c r="BO1" s="47"/>
-      <c r="BP1" s="47"/>
-      <c r="BQ1" s="47"/>
-      <c r="BR1" s="47"/>
-      <c r="BS1" s="47"/>
-      <c r="BT1" s="47"/>
-      <c r="BU1" s="47"/>
-      <c r="BV1" s="47"/>
-      <c r="BW1" s="47"/>
-      <c r="BX1" s="40" t="s">
+      <c r="BM1" s="40"/>
+      <c r="BN1" s="40"/>
+      <c r="BO1" s="40"/>
+      <c r="BP1" s="40"/>
+      <c r="BQ1" s="40"/>
+      <c r="BR1" s="40"/>
+      <c r="BS1" s="40"/>
+      <c r="BT1" s="40"/>
+      <c r="BU1" s="40"/>
+      <c r="BV1" s="40"/>
+      <c r="BW1" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="BY1" s="41"/>
-      <c r="BZ1" s="41"/>
-      <c r="CA1" s="41"/>
-      <c r="CB1" s="41"/>
-      <c r="CC1" s="41"/>
-      <c r="CD1" s="41"/>
-      <c r="CE1" s="41"/>
-      <c r="CF1" s="41"/>
-      <c r="CG1" s="42"/>
-      <c r="CH1" s="49" t="s">
+      <c r="BX1" s="37"/>
+      <c r="BY1" s="37"/>
+      <c r="BZ1" s="37"/>
+      <c r="CA1" s="37"/>
+      <c r="CB1" s="37"/>
+      <c r="CC1" s="37"/>
+      <c r="CD1" s="37"/>
+      <c r="CE1" s="37"/>
+      <c r="CF1" s="38"/>
+      <c r="CG1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="CI1" s="49"/>
-      <c r="CJ1" s="49"/>
-      <c r="CK1" s="49"/>
-      <c r="CL1" s="49"/>
-      <c r="CM1" s="49"/>
-      <c r="CN1" s="49"/>
-      <c r="CO1" s="49"/>
-      <c r="CP1" s="49"/>
-      <c r="CQ1" s="49"/>
-      <c r="CR1" s="33" t="s">
+      <c r="CH1" s="42"/>
+      <c r="CI1" s="42"/>
+      <c r="CJ1" s="42"/>
+      <c r="CK1" s="42"/>
+      <c r="CL1" s="42"/>
+      <c r="CM1" s="42"/>
+      <c r="CN1" s="42"/>
+      <c r="CO1" s="42"/>
+      <c r="CP1" s="42"/>
+      <c r="CQ1" s="33" t="s">
         <v>11</v>
       </c>
+      <c r="CR1" s="34"/>
       <c r="CS1" s="34"/>
       <c r="CT1" s="34"/>
       <c r="CU1" s="34"/>
@@ -2177,119 +2177,118 @@
       <c r="CZ1" s="34"/>
       <c r="DA1" s="34"/>
       <c r="DB1" s="34"/>
-      <c r="DC1" s="34"/>
-      <c r="DD1" s="35"/>
-      <c r="DE1" s="40" t="s">
+      <c r="DC1" s="35"/>
+      <c r="DD1" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="DF1" s="41"/>
-      <c r="DG1" s="42"/>
-      <c r="DH1" s="30" t="s">
+      <c r="DE1" s="37"/>
+      <c r="DF1" s="38"/>
+      <c r="DG1" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="DI1" s="31"/>
-      <c r="DJ1" s="31"/>
-      <c r="DK1" s="31"/>
-      <c r="DL1" s="31"/>
-      <c r="DM1" s="31"/>
-      <c r="DN1" s="31"/>
-      <c r="DO1" s="31"/>
-      <c r="DP1" s="32"/>
-      <c r="DQ1" s="33" t="s">
+      <c r="DH1" s="44"/>
+      <c r="DI1" s="44"/>
+      <c r="DJ1" s="44"/>
+      <c r="DK1" s="44"/>
+      <c r="DL1" s="44"/>
+      <c r="DM1" s="44"/>
+      <c r="DN1" s="44"/>
+      <c r="DO1" s="45"/>
+      <c r="DP1" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="DR1" s="34"/>
-      <c r="DS1" s="35"/>
-      <c r="DT1" s="40" t="s">
+      <c r="DQ1" s="34"/>
+      <c r="DR1" s="35"/>
+      <c r="DS1" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="DU1" s="41"/>
-      <c r="DV1" s="41"/>
-      <c r="DW1" s="41"/>
-      <c r="DX1" s="42"/>
-      <c r="DY1" s="30" t="s">
+      <c r="DT1" s="37"/>
+      <c r="DU1" s="37"/>
+      <c r="DV1" s="37"/>
+      <c r="DW1" s="38"/>
+      <c r="DX1" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="DZ1" s="31"/>
-      <c r="EA1" s="31"/>
-      <c r="EB1" s="31"/>
-      <c r="EC1" s="31"/>
-      <c r="ED1" s="32"/>
-      <c r="EE1" s="33" t="s">
+      <c r="DY1" s="44"/>
+      <c r="DZ1" s="44"/>
+      <c r="EA1" s="44"/>
+      <c r="EB1" s="44"/>
+      <c r="EC1" s="45"/>
+      <c r="ED1" s="33" t="s">
         <v>17</v>
       </c>
+      <c r="EE1" s="34"/>
       <c r="EF1" s="34"/>
       <c r="EG1" s="34"/>
       <c r="EH1" s="34"/>
-      <c r="EI1" s="34"/>
-      <c r="EJ1" s="35"/>
-      <c r="EK1" s="29" t="s">
+      <c r="EI1" s="35"/>
+      <c r="EJ1" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="EL1" s="40" t="s">
+      <c r="EK1" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="EM1" s="41"/>
-      <c r="EN1" s="42"/>
-      <c r="EO1" s="37" t="s">
+      <c r="EL1" s="37"/>
+      <c r="EM1" s="38"/>
+      <c r="EN1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="EP1" s="38"/>
-      <c r="EQ1" s="38"/>
-      <c r="ER1" s="38"/>
-      <c r="ES1" s="38"/>
-      <c r="ET1" s="38"/>
-      <c r="EU1" s="38"/>
-      <c r="EV1" s="38"/>
-      <c r="EW1" s="38"/>
-      <c r="EX1" s="38"/>
-      <c r="EY1" s="38"/>
-      <c r="EZ1" s="38"/>
-      <c r="FA1" s="38"/>
-      <c r="FB1" s="38"/>
-      <c r="FC1" s="38"/>
-      <c r="FD1" s="38"/>
-      <c r="FE1" s="38"/>
-      <c r="FF1" s="38"/>
-      <c r="FG1" s="38"/>
-      <c r="FH1" s="38"/>
-      <c r="FI1" s="38"/>
-      <c r="FJ1" s="38"/>
-      <c r="FK1" s="38"/>
-      <c r="FL1" s="38"/>
-      <c r="FM1" s="38"/>
-      <c r="FN1" s="38"/>
-      <c r="FO1" s="38"/>
-      <c r="FP1" s="38"/>
-      <c r="FQ1" s="38"/>
-      <c r="FR1" s="38"/>
-      <c r="FS1" s="38"/>
-      <c r="FT1" s="38"/>
-      <c r="FU1" s="38"/>
-      <c r="FV1" s="38"/>
-      <c r="FW1" s="38"/>
-      <c r="FX1" s="38"/>
-      <c r="FY1" s="38"/>
-      <c r="FZ1" s="38"/>
-      <c r="GA1" s="38"/>
-      <c r="GB1" s="38"/>
-      <c r="GC1" s="38"/>
-      <c r="GD1" s="39"/>
-      <c r="GE1" s="36" t="s">
+      <c r="EO1" s="51"/>
+      <c r="EP1" s="51"/>
+      <c r="EQ1" s="51"/>
+      <c r="ER1" s="51"/>
+      <c r="ES1" s="51"/>
+      <c r="ET1" s="51"/>
+      <c r="EU1" s="51"/>
+      <c r="EV1" s="51"/>
+      <c r="EW1" s="51"/>
+      <c r="EX1" s="51"/>
+      <c r="EY1" s="51"/>
+      <c r="EZ1" s="51"/>
+      <c r="FA1" s="51"/>
+      <c r="FB1" s="51"/>
+      <c r="FC1" s="51"/>
+      <c r="FD1" s="51"/>
+      <c r="FE1" s="51"/>
+      <c r="FF1" s="51"/>
+      <c r="FG1" s="51"/>
+      <c r="FH1" s="51"/>
+      <c r="FI1" s="51"/>
+      <c r="FJ1" s="51"/>
+      <c r="FK1" s="51"/>
+      <c r="FL1" s="51"/>
+      <c r="FM1" s="51"/>
+      <c r="FN1" s="51"/>
+      <c r="FO1" s="51"/>
+      <c r="FP1" s="51"/>
+      <c r="FQ1" s="51"/>
+      <c r="FR1" s="51"/>
+      <c r="FS1" s="51"/>
+      <c r="FT1" s="51"/>
+      <c r="FU1" s="51"/>
+      <c r="FV1" s="51"/>
+      <c r="FW1" s="51"/>
+      <c r="FX1" s="51"/>
+      <c r="FY1" s="51"/>
+      <c r="FZ1" s="51"/>
+      <c r="GA1" s="51"/>
+      <c r="GB1" s="51"/>
+      <c r="GC1" s="52"/>
+      <c r="GD1" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="GF1" s="36"/>
-      <c r="GG1" s="36"/>
-      <c r="GH1" s="36"/>
-      <c r="GI1" s="36"/>
-      <c r="GJ1" s="36"/>
-      <c r="GK1" s="28" t="s">
+      <c r="GE1" s="49"/>
+      <c r="GF1" s="49"/>
+      <c r="GG1" s="49"/>
+      <c r="GH1" s="49"/>
+      <c r="GI1" s="49"/>
+      <c r="GJ1" s="28" t="s">
         <v>22</v>
       </c>
+      <c r="GK1" s="28"/>
       <c r="GL1" s="28"/>
-      <c r="GM1" s="28"/>
-    </row>
-    <row r="2" spans="1:196" s="10" customFormat="1" ht="68" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:195" s="10" customFormat="1" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -2357,529 +2356,526 @@
         <v>44</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X2" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y2" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AE2" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AK2" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AL2" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AM2" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN2" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AO2" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AP2" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AQ2" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AR2" s="7" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AS2" s="7" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="AT2" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AU2" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AV2" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AW2" s="7" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="AX2" s="7" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="AY2" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AZ2" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BA2" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="BB2" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BC2" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BD2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE2" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="BF2" s="9" t="s">
+      <c r="BE2" s="9" t="s">
         <v>77</v>
       </c>
+      <c r="BF2" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="BG2" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BH2" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="BI2" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="BJ2" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="BK2" s="9" t="s">
+      <c r="BJ2" s="9" t="s">
         <v>82</v>
       </c>
+      <c r="BK2" s="7" t="s">
+        <v>83</v>
+      </c>
       <c r="BL2" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="BM2" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="BN2" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="BO2" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="BP2" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BQ2" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="BR2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="BS2" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="BT2" s="9" t="s">
+      <c r="BS2" s="9" t="s">
         <v>91</v>
       </c>
+      <c r="BT2" s="7" t="s">
+        <v>92</v>
+      </c>
       <c r="BU2" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BV2" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="BW2" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BX2" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="BY2" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BZ2" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="CA2" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="CB2" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="CC2" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="CD2" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="CE2" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="CF2" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="CG2" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="CH2" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="CI2" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="CJ2" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="CK2" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="CL2" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="CM2" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="CN2" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="CO2" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="CP2" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="CQ2" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="CR2" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="CS2" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="CT2" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="CU2" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="CV2" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="CW2" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="CX2" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="CY2" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="CZ2" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="DA2" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="DB2" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="DC2" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="DD2" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="DE2" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="DF2" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="DG2" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="DH2" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="DI2" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="DJ2" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="DK2" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="DL2" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="DM2" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="DN2" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="DO2" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="DP2" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="DQ2" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="DR2" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="DS2" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="DT2" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="DU2" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="DV2" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="DW2" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="DX2" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="DY2" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="DZ2" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="EA2" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="EB2" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="EC2" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="ED2" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="EE2" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="EF2" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="EG2" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="EH2" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="EI2" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="EJ2" s="7" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="EK2" s="7" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="EL2" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="EM2" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="EN2" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="EO2" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="EP2" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="EQ2" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="ER2" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="ES2" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="ET2" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="EU2" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="EV2" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="EW2" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="EX2" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="EY2" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="EZ2" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="FA2" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="FB2" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="FC2" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="FD2" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="FE2" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="FF2" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="FG2" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="FH2" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="FI2" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="FJ2" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="FK2" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="FL2" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="FM2" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FN2" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="FO2" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="FP2" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="FQ2" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="FR2" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="FS2" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="FT2" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="FU2" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="FV2" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="FW2" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="FX2" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="FY2" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="FZ2" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="GA2" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="GB2" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="GC2" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="GD2" s="7" t="s">
         <v>204</v>
       </c>
+      <c r="GD2" s="27" t="s">
+        <v>205</v>
+      </c>
       <c r="GE2" s="27" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="GF2" s="27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="GG2" s="27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="GH2" s="27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="GI2" s="27" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="GJ2" s="27" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="GK2" s="27" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="GL2" s="27" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="GM2" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="GN2" s="27" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:196" s="17" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:195" s="17" customFormat="1" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>215</v>
       </c>
@@ -2959,7 +2955,7 @@
       <c r="AA3" s="12">
         <v>32874</v>
       </c>
-      <c r="AB3" s="12">
+      <c r="AB3" s="13">
         <v>32874</v>
       </c>
       <c r="AC3" s="13">
@@ -2986,11 +2982,11 @@
       <c r="AJ3" s="13">
         <v>32874</v>
       </c>
-      <c r="AK3" s="13">
+      <c r="AK3" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="AL3" s="13">
         <v>32874</v>
-      </c>
-      <c r="AL3" s="12" t="s">
-        <v>221</v>
       </c>
       <c r="AM3" s="13">
         <v>32874</v>
@@ -2998,206 +2994,206 @@
       <c r="AN3" s="13">
         <v>32874</v>
       </c>
-      <c r="AO3" s="13">
+      <c r="AO3" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="AP3" s="13">
         <v>32874</v>
       </c>
-      <c r="AP3" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="AQ3" s="13">
-        <v>32874</v>
+      <c r="AQ3" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="AR3" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AS3" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AT3" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="AU3" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="AV3" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="AW3" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="AX3" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="AU3" s="11" t="s">
+      <c r="AY3" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="AV3" s="11" t="s">
+      <c r="AZ3" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="AW3" s="14" t="s">
+      <c r="BA3" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="AX3" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="AY3" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="AZ3" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="BA3" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="BB3" s="14" t="s">
-        <v>228</v>
+      <c r="BB3" s="11" t="s">
+        <v>230</v>
       </c>
       <c r="BC3" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="BD3" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="BE3" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="BF3" s="11" t="s">
         <v>233</v>
       </c>
       <c r="BG3" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="BH3" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="BI3" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="BJ3" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="BK3" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="BL3" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="BM3" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="BN3" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="BO3" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="BP3" s="11" t="s">
         <v>233</v>
-      </c>
-      <c r="BH3" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="BI3" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="BJ3" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="BK3" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="BL3" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="BM3" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="BN3" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="BO3" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="BP3" s="11" t="s">
-        <v>239</v>
       </c>
       <c r="BQ3" s="11" t="s">
         <v>233</v>
       </c>
       <c r="BR3" s="11" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="BS3" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="BT3" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="BU3" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="BV3" s="14" t="s">
+      <c r="BU3" s="14" t="s">
         <v>243</v>
       </c>
+      <c r="BV3" s="11" t="s">
+        <v>244</v>
+      </c>
       <c r="BW3" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="BX3" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="BY3" s="12">
+      <c r="BX3" s="12">
         <v>32874</v>
       </c>
-      <c r="BZ3" s="11" t="s">
+      <c r="BY3" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="CA3" s="12" t="s">
+      <c r="BZ3" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="CB3" s="11" t="s">
+      <c r="CA3" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="CC3" s="12" t="s">
+      <c r="CB3" s="12" t="s">
         <v>237</v>
       </c>
+      <c r="CC3" s="11" t="s">
+        <v>246</v>
+      </c>
       <c r="CD3" s="11" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="CE3" s="11" t="s">
         <v>237</v>
       </c>
       <c r="CF3" s="11" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="CG3" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="CH3" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="CI3" s="11" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="CJ3" s="11" t="s">
         <v>233</v>
       </c>
       <c r="CK3" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="CL3" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="CM3" s="15">
+      <c r="CL3" s="15">
         <v>357906</v>
       </c>
-      <c r="CN3" s="11">
+      <c r="CM3" s="11">
         <v>171912</v>
       </c>
-      <c r="CO3" s="16">
+      <c r="CN3" s="16">
         <v>2000</v>
       </c>
+      <c r="CO3" s="11" t="s">
+        <v>251</v>
+      </c>
       <c r="CP3" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="CQ3" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="CR3" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="CS3" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="CT3" s="11">
+      <c r="CS3" s="11">
         <v>2</v>
       </c>
+      <c r="CT3" s="11" t="s">
+        <v>255</v>
+      </c>
       <c r="CU3" s="11" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="CV3" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="CW3" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="CX3" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="CW3" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="CX3" s="11" t="s">
-        <v>257</v>
-      </c>
       <c r="CY3" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="CZ3" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="DA3" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="CZ3" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="DA3" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="DB3" s="11" t="s">
+      <c r="DB3" s="18">
+        <v>1980</v>
+      </c>
+      <c r="DC3" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="DC3" s="18">
-        <v>1980</v>
       </c>
       <c r="DD3" s="11" t="s">
         <v>222</v>
@@ -3205,8 +3201,8 @@
       <c r="DE3" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="DF3" s="11" t="s">
-        <v>222</v>
+      <c r="DF3" s="12">
+        <v>32874</v>
       </c>
       <c r="DG3" s="12">
         <v>32874</v>
@@ -3220,35 +3216,35 @@
       <c r="DJ3" s="12">
         <v>32874</v>
       </c>
-      <c r="DK3" s="12">
+      <c r="DK3" s="19">
+        <v>1</v>
+      </c>
+      <c r="DL3" s="19">
+        <v>2</v>
+      </c>
+      <c r="DM3" s="19">
+        <v>1</v>
+      </c>
+      <c r="DN3" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="DO3" s="12">
         <v>32874</v>
       </c>
-      <c r="DL3" s="19">
-        <v>1</v>
-      </c>
-      <c r="DM3" s="19">
-        <v>2</v>
-      </c>
-      <c r="DN3" s="19">
-        <v>1</v>
-      </c>
-      <c r="DO3" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP3" s="12">
+      <c r="DP3" s="18">
+        <v>300</v>
+      </c>
+      <c r="DQ3" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="DR3" s="11">
+        <v>1234567</v>
+      </c>
+      <c r="DS3" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="DT3" s="12">
         <v>32874</v>
-      </c>
-      <c r="DQ3" s="18">
-        <v>300</v>
-      </c>
-      <c r="DR3" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="DS3" s="11">
-        <v>1234567</v>
-      </c>
-      <c r="DT3" s="11" t="s">
-        <v>222</v>
       </c>
       <c r="DU3" s="12">
         <v>32874</v>
@@ -3259,35 +3255,35 @@
       <c r="DW3" s="12">
         <v>32874</v>
       </c>
-      <c r="DX3" s="12">
+      <c r="DX3" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="DY3" s="18">
+        <v>100</v>
+      </c>
+      <c r="DZ3" s="12">
         <v>32874</v>
       </c>
-      <c r="DY3" s="11" t="s">
+      <c r="EA3" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="DZ3" s="18">
+      <c r="EB3" s="18">
         <v>100</v>
       </c>
-      <c r="EA3" s="12">
+      <c r="EC3" s="12">
         <v>32874</v>
-      </c>
-      <c r="EB3" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="EC3" s="18">
-        <v>100</v>
       </c>
       <c r="ED3" s="12">
         <v>32874</v>
       </c>
-      <c r="EE3" s="12">
+      <c r="EE3" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="EF3" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="EG3" s="12">
         <v>32874</v>
-      </c>
-      <c r="EF3" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="EG3" s="11" t="s">
-        <v>263</v>
       </c>
       <c r="EH3" s="12">
         <v>32874</v>
@@ -3295,16 +3291,14 @@
       <c r="EI3" s="12">
         <v>32874</v>
       </c>
-      <c r="EJ3" s="12">
+      <c r="EJ3" s="11"/>
+      <c r="EK3" s="12">
         <v>32874</v>
       </c>
-      <c r="EK3" s="11"/>
       <c r="EL3" s="12">
         <v>32874</v>
       </c>
-      <c r="EM3" s="12">
-        <v>32874</v>
-      </c>
+      <c r="EM3" s="11"/>
       <c r="EN3" s="11"/>
       <c r="EO3" s="11"/>
       <c r="EP3" s="11"/>
@@ -3357,9 +3351,8 @@
       <c r="GK3" s="11"/>
       <c r="GL3" s="11"/>
       <c r="GM3" s="11"/>
-      <c r="GN3" s="11"/>
-    </row>
-    <row r="4" spans="1:196" s="10" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:195" s="10" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>264</v>
       </c>
@@ -3402,7 +3395,7 @@
       <c r="AL4" s="20"/>
       <c r="AM4" s="20"/>
       <c r="AN4" s="20"/>
-      <c r="AO4" s="20"/>
+      <c r="AO4" s="7"/>
       <c r="AP4" s="7"/>
       <c r="AQ4" s="7"/>
       <c r="AR4" s="7"/>
@@ -3437,12 +3430,12 @@
       <c r="BU4" s="7"/>
       <c r="BV4" s="7"/>
       <c r="BW4" s="7"/>
-      <c r="BX4" s="7"/>
-      <c r="BY4" s="20"/>
-      <c r="BZ4" s="7"/>
-      <c r="CA4" s="20"/>
-      <c r="CB4" s="7"/>
-      <c r="CC4" s="20"/>
+      <c r="BX4" s="20"/>
+      <c r="BY4" s="7"/>
+      <c r="BZ4" s="20"/>
+      <c r="CA4" s="7"/>
+      <c r="CB4" s="20"/>
+      <c r="CC4" s="7"/>
       <c r="CD4" s="7"/>
       <c r="CE4" s="7"/>
       <c r="CF4" s="7"/>
@@ -3451,13 +3444,13 @@
       <c r="CI4" s="7"/>
       <c r="CJ4" s="7"/>
       <c r="CK4" s="7"/>
-      <c r="CL4" s="7"/>
+      <c r="CL4" s="21"/>
       <c r="CM4" s="21"/>
-      <c r="CN4" s="21"/>
-      <c r="CO4" s="22"/>
+      <c r="CN4" s="22"/>
+      <c r="CO4" s="7"/>
       <c r="CP4" s="7"/>
       <c r="CQ4" s="7"/>
-      <c r="CR4" s="7"/>
+      <c r="CS4" s="7"/>
       <c r="CT4" s="7"/>
       <c r="CU4" s="7"/>
       <c r="CV4" s="7"/>
@@ -3466,41 +3459,41 @@
       <c r="CY4" s="7"/>
       <c r="CZ4" s="7"/>
       <c r="DA4" s="7"/>
-      <c r="DB4" s="7"/>
-      <c r="DC4" s="23"/>
+      <c r="DB4" s="23"/>
+      <c r="DC4" s="7"/>
       <c r="DD4" s="7"/>
       <c r="DE4" s="7"/>
-      <c r="DF4" s="7"/>
+      <c r="DF4" s="20"/>
       <c r="DG4" s="20"/>
       <c r="DH4" s="20"/>
       <c r="DI4" s="20"/>
       <c r="DJ4" s="20"/>
-      <c r="DK4" s="20"/>
+      <c r="DK4" s="24"/>
       <c r="DL4" s="24"/>
       <c r="DM4" s="24"/>
-      <c r="DN4" s="24"/>
-      <c r="DO4" s="7"/>
-      <c r="DP4" s="20"/>
-      <c r="DQ4" s="23"/>
+      <c r="DN4" s="7"/>
+      <c r="DO4" s="20"/>
+      <c r="DP4" s="23"/>
+      <c r="DQ4" s="7"/>
       <c r="DR4" s="7"/>
       <c r="DS4" s="7"/>
-      <c r="DT4" s="7"/>
+      <c r="DT4" s="20"/>
       <c r="DU4" s="20"/>
       <c r="DV4" s="20"/>
       <c r="DW4" s="20"/>
-      <c r="DX4" s="20"/>
-      <c r="DY4" s="7"/>
-      <c r="DZ4" s="23"/>
-      <c r="EA4" s="20"/>
-      <c r="EB4" s="7"/>
-      <c r="EC4" s="23"/>
-      <c r="ED4" s="20"/>
+      <c r="DX4" s="7"/>
+      <c r="DY4" s="23"/>
+      <c r="DZ4" s="20"/>
+      <c r="EA4" s="7"/>
+      <c r="EB4" s="23"/>
+      <c r="EC4" s="20"/>
+      <c r="ED4" s="7"/>
       <c r="EE4" s="7"/>
       <c r="EF4" s="7"/>
-      <c r="EG4" s="7"/>
+      <c r="EG4" s="20"/>
       <c r="EH4" s="20"/>
       <c r="EI4" s="20"/>
-      <c r="EJ4" s="20"/>
+      <c r="EJ4" s="7"/>
       <c r="EK4" s="7"/>
       <c r="EL4" s="7"/>
       <c r="EM4" s="7"/>
@@ -3556,9 +3549,8 @@
       <c r="GK4" s="7"/>
       <c r="GL4" s="7"/>
       <c r="GM4" s="7"/>
-      <c r="GN4" s="7"/>
-    </row>
-    <row r="5" spans="1:196" s="10" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:195" s="10" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>265</v>
       </c>
@@ -3601,7 +3593,7 @@
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
       <c r="AN5" s="20"/>
-      <c r="AO5" s="20"/>
+      <c r="AO5" s="7"/>
       <c r="AP5" s="7"/>
       <c r="AQ5" s="7"/>
       <c r="AR5" s="7"/>
@@ -3636,12 +3628,12 @@
       <c r="BU5" s="7"/>
       <c r="BV5" s="7"/>
       <c r="BW5" s="7"/>
-      <c r="BX5" s="7"/>
-      <c r="BY5" s="20"/>
-      <c r="BZ5" s="7"/>
-      <c r="CA5" s="20"/>
-      <c r="CB5" s="7"/>
-      <c r="CC5" s="20"/>
+      <c r="BX5" s="20"/>
+      <c r="BY5" s="7"/>
+      <c r="BZ5" s="20"/>
+      <c r="CA5" s="7"/>
+      <c r="CB5" s="20"/>
+      <c r="CC5" s="7"/>
       <c r="CD5" s="7"/>
       <c r="CE5" s="7"/>
       <c r="CF5" s="7"/>
@@ -3650,10 +3642,10 @@
       <c r="CI5" s="7"/>
       <c r="CJ5" s="7"/>
       <c r="CK5" s="7"/>
-      <c r="CL5" s="7"/>
+      <c r="CL5" s="21"/>
       <c r="CM5" s="21"/>
-      <c r="CN5" s="21"/>
-      <c r="CO5" s="22"/>
+      <c r="CN5" s="22"/>
+      <c r="CO5" s="7"/>
       <c r="CP5" s="7"/>
       <c r="CQ5" s="7"/>
       <c r="CR5" s="7"/>
@@ -3666,41 +3658,41 @@
       <c r="CY5" s="7"/>
       <c r="CZ5" s="7"/>
       <c r="DA5" s="7"/>
-      <c r="DB5" s="7"/>
-      <c r="DC5" s="23"/>
+      <c r="DB5" s="23"/>
+      <c r="DC5" s="7"/>
       <c r="DD5" s="7"/>
       <c r="DE5" s="7"/>
-      <c r="DF5" s="7"/>
+      <c r="DF5" s="20"/>
       <c r="DG5" s="20"/>
       <c r="DH5" s="20"/>
       <c r="DI5" s="20"/>
       <c r="DJ5" s="20"/>
-      <c r="DK5" s="20"/>
+      <c r="DK5" s="24"/>
       <c r="DL5" s="24"/>
       <c r="DM5" s="24"/>
-      <c r="DN5" s="24"/>
-      <c r="DO5" s="7"/>
-      <c r="DP5" s="20"/>
-      <c r="DQ5" s="23"/>
+      <c r="DN5" s="7"/>
+      <c r="DO5" s="20"/>
+      <c r="DP5" s="23"/>
+      <c r="DQ5" s="7"/>
       <c r="DR5" s="7"/>
       <c r="DS5" s="7"/>
-      <c r="DT5" s="7"/>
+      <c r="DT5" s="20"/>
       <c r="DU5" s="20"/>
       <c r="DV5" s="20"/>
       <c r="DW5" s="20"/>
-      <c r="DX5" s="20"/>
-      <c r="DY5" s="7"/>
-      <c r="DZ5" s="23"/>
-      <c r="EA5" s="20"/>
-      <c r="EB5" s="7"/>
-      <c r="EC5" s="23"/>
-      <c r="ED5" s="20"/>
+      <c r="DX5" s="7"/>
+      <c r="DY5" s="23"/>
+      <c r="DZ5" s="20"/>
+      <c r="EA5" s="7"/>
+      <c r="EB5" s="23"/>
+      <c r="EC5" s="20"/>
+      <c r="ED5" s="7"/>
       <c r="EE5" s="7"/>
       <c r="EF5" s="7"/>
-      <c r="EG5" s="7"/>
+      <c r="EG5" s="20"/>
       <c r="EH5" s="20"/>
       <c r="EI5" s="20"/>
-      <c r="EJ5" s="20"/>
+      <c r="EJ5" s="7"/>
       <c r="EK5" s="7"/>
       <c r="EL5" s="7"/>
       <c r="EM5" s="7"/>
@@ -3756,9 +3748,8 @@
       <c r="GK5" s="7"/>
       <c r="GL5" s="7"/>
       <c r="GM5" s="7"/>
-      <c r="GN5" s="7"/>
-    </row>
-    <row r="6" spans="1:196" s="10" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:195" s="10" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>266</v>
       </c>
@@ -3801,7 +3792,7 @@
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
       <c r="AN6" s="20"/>
-      <c r="AO6" s="20"/>
+      <c r="AO6" s="7"/>
       <c r="AP6" s="7"/>
       <c r="AQ6" s="7"/>
       <c r="AR6" s="7"/>
@@ -3836,12 +3827,12 @@
       <c r="BU6" s="7"/>
       <c r="BV6" s="7"/>
       <c r="BW6" s="7"/>
-      <c r="BX6" s="7"/>
-      <c r="BY6" s="20"/>
-      <c r="BZ6" s="7"/>
-      <c r="CA6" s="20"/>
-      <c r="CB6" s="7"/>
-      <c r="CC6" s="20"/>
+      <c r="BX6" s="20"/>
+      <c r="BY6" s="7"/>
+      <c r="BZ6" s="20"/>
+      <c r="CA6" s="7"/>
+      <c r="CB6" s="20"/>
+      <c r="CC6" s="7"/>
       <c r="CD6" s="7"/>
       <c r="CE6" s="7"/>
       <c r="CF6" s="7"/>
@@ -3850,10 +3841,10 @@
       <c r="CI6" s="7"/>
       <c r="CJ6" s="7"/>
       <c r="CK6" s="7"/>
-      <c r="CL6" s="7"/>
+      <c r="CL6" s="21"/>
       <c r="CM6" s="21"/>
-      <c r="CN6" s="21"/>
-      <c r="CO6" s="22"/>
+      <c r="CN6" s="22"/>
+      <c r="CO6" s="7"/>
       <c r="CP6" s="7"/>
       <c r="CQ6" s="7"/>
       <c r="CR6" s="7"/>
@@ -3866,41 +3857,41 @@
       <c r="CY6" s="7"/>
       <c r="CZ6" s="7"/>
       <c r="DA6" s="7"/>
-      <c r="DB6" s="7"/>
-      <c r="DC6" s="23"/>
+      <c r="DB6" s="23"/>
+      <c r="DC6" s="7"/>
       <c r="DD6" s="7"/>
       <c r="DE6" s="7"/>
-      <c r="DF6" s="7"/>
+      <c r="DF6" s="20"/>
       <c r="DG6" s="20"/>
       <c r="DH6" s="20"/>
       <c r="DI6" s="20"/>
       <c r="DJ6" s="20"/>
-      <c r="DK6" s="20"/>
+      <c r="DK6" s="24"/>
       <c r="DL6" s="24"/>
       <c r="DM6" s="24"/>
-      <c r="DN6" s="24"/>
-      <c r="DO6" s="7"/>
-      <c r="DP6" s="20"/>
-      <c r="DQ6" s="23"/>
+      <c r="DN6" s="7"/>
+      <c r="DO6" s="20"/>
+      <c r="DP6" s="23"/>
+      <c r="DQ6" s="7"/>
       <c r="DR6" s="7"/>
       <c r="DS6" s="7"/>
-      <c r="DT6" s="7"/>
+      <c r="DT6" s="20"/>
       <c r="DU6" s="20"/>
       <c r="DV6" s="20"/>
       <c r="DW6" s="20"/>
-      <c r="DX6" s="20"/>
-      <c r="DY6" s="7"/>
-      <c r="DZ6" s="23"/>
-      <c r="EA6" s="20"/>
-      <c r="EB6" s="7"/>
-      <c r="EC6" s="23"/>
-      <c r="ED6" s="20"/>
+      <c r="DX6" s="7"/>
+      <c r="DY6" s="23"/>
+      <c r="DZ6" s="20"/>
+      <c r="EA6" s="7"/>
+      <c r="EB6" s="23"/>
+      <c r="EC6" s="20"/>
+      <c r="ED6" s="7"/>
       <c r="EE6" s="7"/>
       <c r="EF6" s="7"/>
-      <c r="EG6" s="7"/>
+      <c r="EG6" s="20"/>
       <c r="EH6" s="20"/>
       <c r="EI6" s="20"/>
-      <c r="EJ6" s="20"/>
+      <c r="EJ6" s="7"/>
       <c r="EK6" s="7"/>
       <c r="EL6" s="7"/>
       <c r="EM6" s="7"/>
@@ -3956,9 +3947,8 @@
       <c r="GK6" s="7"/>
       <c r="GL6" s="7"/>
       <c r="GM6" s="7"/>
-      <c r="GN6" s="7"/>
-    </row>
-    <row r="7" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -3999,7 +3989,7 @@
       <c r="AL7" s="20"/>
       <c r="AM7" s="20"/>
       <c r="AN7" s="20"/>
-      <c r="AO7" s="20"/>
+      <c r="AO7" s="7"/>
       <c r="AP7" s="7"/>
       <c r="AQ7" s="7"/>
       <c r="AR7" s="7"/>
@@ -4034,12 +4024,12 @@
       <c r="BU7" s="7"/>
       <c r="BV7" s="7"/>
       <c r="BW7" s="7"/>
-      <c r="BX7" s="7"/>
-      <c r="BY7" s="20"/>
-      <c r="BZ7" s="7"/>
-      <c r="CA7" s="20"/>
-      <c r="CB7" s="7"/>
-      <c r="CC7" s="20"/>
+      <c r="BX7" s="20"/>
+      <c r="BY7" s="7"/>
+      <c r="BZ7" s="20"/>
+      <c r="CA7" s="7"/>
+      <c r="CB7" s="20"/>
+      <c r="CC7" s="7"/>
       <c r="CD7" s="7"/>
       <c r="CE7" s="7"/>
       <c r="CF7" s="7"/>
@@ -4048,10 +4038,10 @@
       <c r="CI7" s="7"/>
       <c r="CJ7" s="7"/>
       <c r="CK7" s="7"/>
-      <c r="CL7" s="7"/>
+      <c r="CL7" s="21"/>
       <c r="CM7" s="21"/>
-      <c r="CN7" s="21"/>
-      <c r="CO7" s="22"/>
+      <c r="CN7" s="22"/>
+      <c r="CO7" s="7"/>
       <c r="CP7" s="7"/>
       <c r="CQ7" s="7"/>
       <c r="CR7" s="7"/>
@@ -4064,41 +4054,41 @@
       <c r="CY7" s="7"/>
       <c r="CZ7" s="7"/>
       <c r="DA7" s="7"/>
-      <c r="DB7" s="7"/>
-      <c r="DC7" s="23"/>
+      <c r="DB7" s="23"/>
+      <c r="DC7" s="7"/>
       <c r="DD7" s="7"/>
       <c r="DE7" s="7"/>
-      <c r="DF7" s="7"/>
+      <c r="DF7" s="20"/>
       <c r="DG7" s="20"/>
       <c r="DH7" s="20"/>
       <c r="DI7" s="20"/>
       <c r="DJ7" s="20"/>
-      <c r="DK7" s="20"/>
+      <c r="DK7" s="24"/>
       <c r="DL7" s="24"/>
       <c r="DM7" s="24"/>
-      <c r="DN7" s="24"/>
-      <c r="DO7" s="7"/>
-      <c r="DP7" s="20"/>
-      <c r="DQ7" s="23"/>
+      <c r="DN7" s="7"/>
+      <c r="DO7" s="20"/>
+      <c r="DP7" s="23"/>
+      <c r="DQ7" s="7"/>
       <c r="DR7" s="7"/>
       <c r="DS7" s="7"/>
-      <c r="DT7" s="7"/>
+      <c r="DT7" s="20"/>
       <c r="DU7" s="20"/>
       <c r="DV7" s="20"/>
       <c r="DW7" s="20"/>
-      <c r="DX7" s="20"/>
-      <c r="DY7" s="7"/>
-      <c r="DZ7" s="23"/>
-      <c r="EA7" s="20"/>
-      <c r="EB7" s="7"/>
-      <c r="EC7" s="23"/>
-      <c r="ED7" s="20"/>
+      <c r="DX7" s="7"/>
+      <c r="DY7" s="23"/>
+      <c r="DZ7" s="20"/>
+      <c r="EA7" s="7"/>
+      <c r="EB7" s="23"/>
+      <c r="EC7" s="20"/>
+      <c r="ED7" s="7"/>
       <c r="EE7" s="7"/>
       <c r="EF7" s="7"/>
-      <c r="EG7" s="7"/>
+      <c r="EG7" s="20"/>
       <c r="EH7" s="20"/>
       <c r="EI7" s="20"/>
-      <c r="EJ7" s="20"/>
+      <c r="EJ7" s="7"/>
       <c r="EK7" s="7"/>
       <c r="EL7" s="7"/>
       <c r="EM7" s="7"/>
@@ -4154,9 +4144,8 @@
       <c r="GK7" s="7"/>
       <c r="GL7" s="7"/>
       <c r="GM7" s="7"/>
-      <c r="GN7" s="7"/>
-    </row>
-    <row r="8" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -4197,7 +4186,7 @@
       <c r="AL8" s="20"/>
       <c r="AM8" s="20"/>
       <c r="AN8" s="20"/>
-      <c r="AO8" s="20"/>
+      <c r="AO8" s="7"/>
       <c r="AP8" s="7"/>
       <c r="AQ8" s="7"/>
       <c r="AR8" s="7"/>
@@ -4232,12 +4221,12 @@
       <c r="BU8" s="7"/>
       <c r="BV8" s="7"/>
       <c r="BW8" s="7"/>
-      <c r="BX8" s="7"/>
-      <c r="BY8" s="20"/>
-      <c r="BZ8" s="7"/>
-      <c r="CA8" s="20"/>
-      <c r="CB8" s="7"/>
-      <c r="CC8" s="20"/>
+      <c r="BX8" s="20"/>
+      <c r="BY8" s="7"/>
+      <c r="BZ8" s="20"/>
+      <c r="CA8" s="7"/>
+      <c r="CB8" s="20"/>
+      <c r="CC8" s="7"/>
       <c r="CD8" s="7"/>
       <c r="CE8" s="7"/>
       <c r="CF8" s="7"/>
@@ -4246,10 +4235,10 @@
       <c r="CI8" s="7"/>
       <c r="CJ8" s="7"/>
       <c r="CK8" s="7"/>
-      <c r="CL8" s="7"/>
+      <c r="CL8" s="21"/>
       <c r="CM8" s="21"/>
-      <c r="CN8" s="21"/>
-      <c r="CO8" s="22"/>
+      <c r="CN8" s="22"/>
+      <c r="CO8" s="7"/>
       <c r="CP8" s="7"/>
       <c r="CQ8" s="7"/>
       <c r="CR8" s="7"/>
@@ -4262,41 +4251,41 @@
       <c r="CY8" s="7"/>
       <c r="CZ8" s="7"/>
       <c r="DA8" s="7"/>
-      <c r="DB8" s="7"/>
-      <c r="DC8" s="23"/>
+      <c r="DB8" s="23"/>
+      <c r="DC8" s="7"/>
       <c r="DD8" s="7"/>
       <c r="DE8" s="7"/>
-      <c r="DF8" s="7"/>
+      <c r="DF8" s="20"/>
       <c r="DG8" s="20"/>
       <c r="DH8" s="20"/>
       <c r="DI8" s="20"/>
       <c r="DJ8" s="20"/>
-      <c r="DK8" s="20"/>
+      <c r="DK8" s="24"/>
       <c r="DL8" s="24"/>
       <c r="DM8" s="24"/>
-      <c r="DN8" s="24"/>
-      <c r="DO8" s="7"/>
-      <c r="DP8" s="20"/>
-      <c r="DQ8" s="23"/>
+      <c r="DN8" s="7"/>
+      <c r="DO8" s="20"/>
+      <c r="DP8" s="23"/>
+      <c r="DQ8" s="7"/>
       <c r="DR8" s="7"/>
       <c r="DS8" s="7"/>
-      <c r="DT8" s="7"/>
+      <c r="DT8" s="20"/>
       <c r="DU8" s="20"/>
       <c r="DV8" s="20"/>
       <c r="DW8" s="20"/>
-      <c r="DX8" s="20"/>
-      <c r="DY8" s="7"/>
-      <c r="DZ8" s="23"/>
-      <c r="EA8" s="20"/>
-      <c r="EB8" s="7"/>
-      <c r="EC8" s="23"/>
-      <c r="ED8" s="20"/>
+      <c r="DX8" s="7"/>
+      <c r="DY8" s="23"/>
+      <c r="DZ8" s="20"/>
+      <c r="EA8" s="7"/>
+      <c r="EB8" s="23"/>
+      <c r="EC8" s="20"/>
+      <c r="ED8" s="7"/>
       <c r="EE8" s="7"/>
       <c r="EF8" s="7"/>
-      <c r="EG8" s="7"/>
+      <c r="EG8" s="20"/>
       <c r="EH8" s="20"/>
       <c r="EI8" s="20"/>
-      <c r="EJ8" s="20"/>
+      <c r="EJ8" s="7"/>
       <c r="EK8" s="7"/>
       <c r="EL8" s="7"/>
       <c r="EM8" s="7"/>
@@ -4352,9 +4341,8 @@
       <c r="GK8" s="7"/>
       <c r="GL8" s="7"/>
       <c r="GM8" s="7"/>
-      <c r="GN8" s="7"/>
-    </row>
-    <row r="9" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -4395,7 +4383,7 @@
       <c r="AL9" s="20"/>
       <c r="AM9" s="20"/>
       <c r="AN9" s="20"/>
-      <c r="AO9" s="20"/>
+      <c r="AO9" s="7"/>
       <c r="AP9" s="7"/>
       <c r="AQ9" s="7"/>
       <c r="AR9" s="7"/>
@@ -4430,12 +4418,12 @@
       <c r="BU9" s="7"/>
       <c r="BV9" s="7"/>
       <c r="BW9" s="7"/>
-      <c r="BX9" s="7"/>
-      <c r="BY9" s="20"/>
-      <c r="BZ9" s="7"/>
-      <c r="CA9" s="20"/>
-      <c r="CB9" s="7"/>
-      <c r="CC9" s="20"/>
+      <c r="BX9" s="20"/>
+      <c r="BY9" s="7"/>
+      <c r="BZ9" s="20"/>
+      <c r="CA9" s="7"/>
+      <c r="CB9" s="20"/>
+      <c r="CC9" s="7"/>
       <c r="CD9" s="7"/>
       <c r="CE9" s="7"/>
       <c r="CF9" s="7"/>
@@ -4444,10 +4432,10 @@
       <c r="CI9" s="7"/>
       <c r="CJ9" s="7"/>
       <c r="CK9" s="7"/>
-      <c r="CL9" s="7"/>
+      <c r="CL9" s="21"/>
       <c r="CM9" s="21"/>
-      <c r="CN9" s="21"/>
-      <c r="CO9" s="22"/>
+      <c r="CN9" s="22"/>
+      <c r="CO9" s="7"/>
       <c r="CP9" s="7"/>
       <c r="CQ9" s="7"/>
       <c r="CR9" s="7"/>
@@ -4460,41 +4448,41 @@
       <c r="CY9" s="7"/>
       <c r="CZ9" s="7"/>
       <c r="DA9" s="7"/>
-      <c r="DB9" s="7"/>
-      <c r="DC9" s="23"/>
+      <c r="DB9" s="23"/>
+      <c r="DC9" s="7"/>
       <c r="DD9" s="7"/>
       <c r="DE9" s="7"/>
-      <c r="DF9" s="7"/>
+      <c r="DF9" s="20"/>
       <c r="DG9" s="20"/>
       <c r="DH9" s="20"/>
       <c r="DI9" s="20"/>
       <c r="DJ9" s="20"/>
-      <c r="DK9" s="20"/>
+      <c r="DK9" s="24"/>
       <c r="DL9" s="24"/>
       <c r="DM9" s="24"/>
-      <c r="DN9" s="24"/>
-      <c r="DO9" s="7"/>
-      <c r="DP9" s="20"/>
-      <c r="DQ9" s="23"/>
+      <c r="DN9" s="7"/>
+      <c r="DO9" s="20"/>
+      <c r="DP9" s="23"/>
+      <c r="DQ9" s="7"/>
       <c r="DR9" s="7"/>
       <c r="DS9" s="7"/>
-      <c r="DT9" s="7"/>
+      <c r="DT9" s="20"/>
       <c r="DU9" s="20"/>
       <c r="DV9" s="20"/>
       <c r="DW9" s="20"/>
-      <c r="DX9" s="20"/>
-      <c r="DY9" s="7"/>
-      <c r="DZ9" s="23"/>
-      <c r="EA9" s="20"/>
-      <c r="EB9" s="7"/>
-      <c r="EC9" s="23"/>
-      <c r="ED9" s="20"/>
+      <c r="DX9" s="7"/>
+      <c r="DY9" s="23"/>
+      <c r="DZ9" s="20"/>
+      <c r="EA9" s="7"/>
+      <c r="EB9" s="23"/>
+      <c r="EC9" s="20"/>
+      <c r="ED9" s="7"/>
       <c r="EE9" s="7"/>
       <c r="EF9" s="7"/>
-      <c r="EG9" s="7"/>
+      <c r="EG9" s="20"/>
       <c r="EH9" s="20"/>
       <c r="EI9" s="20"/>
-      <c r="EJ9" s="20"/>
+      <c r="EJ9" s="7"/>
       <c r="EK9" s="7"/>
       <c r="EL9" s="7"/>
       <c r="EM9" s="7"/>
@@ -4550,9 +4538,8 @@
       <c r="GK9" s="7"/>
       <c r="GL9" s="7"/>
       <c r="GM9" s="7"/>
-      <c r="GN9" s="7"/>
-    </row>
-    <row r="10" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -4593,7 +4580,7 @@
       <c r="AL10" s="20"/>
       <c r="AM10" s="20"/>
       <c r="AN10" s="20"/>
-      <c r="AO10" s="20"/>
+      <c r="AO10" s="7"/>
       <c r="AP10" s="7"/>
       <c r="AQ10" s="7"/>
       <c r="AR10" s="7"/>
@@ -4628,12 +4615,12 @@
       <c r="BU10" s="7"/>
       <c r="BV10" s="7"/>
       <c r="BW10" s="7"/>
-      <c r="BX10" s="7"/>
-      <c r="BY10" s="20"/>
-      <c r="BZ10" s="7"/>
-      <c r="CA10" s="20"/>
-      <c r="CB10" s="7"/>
-      <c r="CC10" s="20"/>
+      <c r="BX10" s="20"/>
+      <c r="BY10" s="7"/>
+      <c r="BZ10" s="20"/>
+      <c r="CA10" s="7"/>
+      <c r="CB10" s="20"/>
+      <c r="CC10" s="7"/>
       <c r="CD10" s="7"/>
       <c r="CE10" s="7"/>
       <c r="CF10" s="7"/>
@@ -4642,10 +4629,10 @@
       <c r="CI10" s="7"/>
       <c r="CJ10" s="7"/>
       <c r="CK10" s="7"/>
-      <c r="CL10" s="7"/>
+      <c r="CL10" s="21"/>
       <c r="CM10" s="21"/>
-      <c r="CN10" s="21"/>
-      <c r="CO10" s="22"/>
+      <c r="CN10" s="22"/>
+      <c r="CO10" s="7"/>
       <c r="CP10" s="7"/>
       <c r="CQ10" s="7"/>
       <c r="CR10" s="7"/>
@@ -4658,41 +4645,41 @@
       <c r="CY10" s="7"/>
       <c r="CZ10" s="7"/>
       <c r="DA10" s="7"/>
-      <c r="DB10" s="7"/>
-      <c r="DC10" s="23"/>
+      <c r="DB10" s="23"/>
+      <c r="DC10" s="7"/>
       <c r="DD10" s="7"/>
       <c r="DE10" s="7"/>
-      <c r="DF10" s="7"/>
+      <c r="DF10" s="20"/>
       <c r="DG10" s="20"/>
       <c r="DH10" s="20"/>
       <c r="DI10" s="20"/>
       <c r="DJ10" s="20"/>
-      <c r="DK10" s="20"/>
+      <c r="DK10" s="24"/>
       <c r="DL10" s="24"/>
       <c r="DM10" s="24"/>
-      <c r="DN10" s="24"/>
-      <c r="DO10" s="7"/>
-      <c r="DP10" s="20"/>
-      <c r="DQ10" s="23"/>
+      <c r="DN10" s="7"/>
+      <c r="DO10" s="20"/>
+      <c r="DP10" s="23"/>
+      <c r="DQ10" s="7"/>
       <c r="DR10" s="7"/>
       <c r="DS10" s="7"/>
-      <c r="DT10" s="7"/>
+      <c r="DT10" s="20"/>
       <c r="DU10" s="20"/>
       <c r="DV10" s="20"/>
       <c r="DW10" s="20"/>
-      <c r="DX10" s="20"/>
-      <c r="DY10" s="7"/>
-      <c r="DZ10" s="23"/>
-      <c r="EA10" s="20"/>
-      <c r="EB10" s="7"/>
-      <c r="EC10" s="23"/>
-      <c r="ED10" s="20"/>
+      <c r="DX10" s="7"/>
+      <c r="DY10" s="23"/>
+      <c r="DZ10" s="20"/>
+      <c r="EA10" s="7"/>
+      <c r="EB10" s="23"/>
+      <c r="EC10" s="20"/>
+      <c r="ED10" s="7"/>
       <c r="EE10" s="7"/>
       <c r="EF10" s="7"/>
-      <c r="EG10" s="7"/>
+      <c r="EG10" s="20"/>
       <c r="EH10" s="20"/>
       <c r="EI10" s="20"/>
-      <c r="EJ10" s="20"/>
+      <c r="EJ10" s="7"/>
       <c r="EK10" s="7"/>
       <c r="EL10" s="7"/>
       <c r="EM10" s="7"/>
@@ -4748,9 +4735,8 @@
       <c r="GK10" s="7"/>
       <c r="GL10" s="7"/>
       <c r="GM10" s="7"/>
-      <c r="GN10" s="7"/>
-    </row>
-    <row r="11" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -4791,7 +4777,7 @@
       <c r="AL11" s="20"/>
       <c r="AM11" s="20"/>
       <c r="AN11" s="20"/>
-      <c r="AO11" s="20"/>
+      <c r="AO11" s="7"/>
       <c r="AP11" s="7"/>
       <c r="AQ11" s="7"/>
       <c r="AR11" s="7"/>
@@ -4826,12 +4812,12 @@
       <c r="BU11" s="7"/>
       <c r="BV11" s="7"/>
       <c r="BW11" s="7"/>
-      <c r="BX11" s="7"/>
-      <c r="BY11" s="20"/>
-      <c r="BZ11" s="7"/>
-      <c r="CA11" s="20"/>
-      <c r="CB11" s="7"/>
-      <c r="CC11" s="20"/>
+      <c r="BX11" s="20"/>
+      <c r="BY11" s="7"/>
+      <c r="BZ11" s="20"/>
+      <c r="CA11" s="7"/>
+      <c r="CB11" s="20"/>
+      <c r="CC11" s="7"/>
       <c r="CD11" s="7"/>
       <c r="CE11" s="7"/>
       <c r="CF11" s="7"/>
@@ -4840,10 +4826,10 @@
       <c r="CI11" s="7"/>
       <c r="CJ11" s="7"/>
       <c r="CK11" s="7"/>
-      <c r="CL11" s="7"/>
+      <c r="CL11" s="21"/>
       <c r="CM11" s="21"/>
-      <c r="CN11" s="21"/>
-      <c r="CO11" s="22"/>
+      <c r="CN11" s="22"/>
+      <c r="CO11" s="7"/>
       <c r="CP11" s="7"/>
       <c r="CQ11" s="7"/>
       <c r="CR11" s="7"/>
@@ -4856,41 +4842,41 @@
       <c r="CY11" s="7"/>
       <c r="CZ11" s="7"/>
       <c r="DA11" s="7"/>
-      <c r="DB11" s="7"/>
-      <c r="DC11" s="23"/>
+      <c r="DB11" s="23"/>
+      <c r="DC11" s="7"/>
       <c r="DD11" s="7"/>
       <c r="DE11" s="7"/>
-      <c r="DF11" s="7"/>
+      <c r="DF11" s="20"/>
       <c r="DG11" s="20"/>
       <c r="DH11" s="20"/>
       <c r="DI11" s="20"/>
       <c r="DJ11" s="20"/>
-      <c r="DK11" s="20"/>
+      <c r="DK11" s="24"/>
       <c r="DL11" s="24"/>
       <c r="DM11" s="24"/>
-      <c r="DN11" s="24"/>
-      <c r="DO11" s="7"/>
-      <c r="DP11" s="20"/>
-      <c r="DQ11" s="23"/>
+      <c r="DN11" s="7"/>
+      <c r="DO11" s="20"/>
+      <c r="DP11" s="23"/>
+      <c r="DQ11" s="7"/>
       <c r="DR11" s="7"/>
       <c r="DS11" s="7"/>
-      <c r="DT11" s="7"/>
+      <c r="DT11" s="20"/>
       <c r="DU11" s="20"/>
       <c r="DV11" s="20"/>
       <c r="DW11" s="20"/>
-      <c r="DX11" s="20"/>
-      <c r="DY11" s="7"/>
-      <c r="DZ11" s="23"/>
-      <c r="EA11" s="20"/>
-      <c r="EB11" s="7"/>
-      <c r="EC11" s="23"/>
-      <c r="ED11" s="20"/>
+      <c r="DX11" s="7"/>
+      <c r="DY11" s="23"/>
+      <c r="DZ11" s="20"/>
+      <c r="EA11" s="7"/>
+      <c r="EB11" s="23"/>
+      <c r="EC11" s="20"/>
+      <c r="ED11" s="7"/>
       <c r="EE11" s="7"/>
       <c r="EF11" s="7"/>
-      <c r="EG11" s="7"/>
+      <c r="EG11" s="20"/>
       <c r="EH11" s="20"/>
       <c r="EI11" s="20"/>
-      <c r="EJ11" s="20"/>
+      <c r="EJ11" s="7"/>
       <c r="EK11" s="7"/>
       <c r="EL11" s="7"/>
       <c r="EM11" s="7"/>
@@ -4946,9 +4932,8 @@
       <c r="GK11" s="7"/>
       <c r="GL11" s="7"/>
       <c r="GM11" s="7"/>
-      <c r="GN11" s="7"/>
-    </row>
-    <row r="12" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -4989,7 +4974,7 @@
       <c r="AL12" s="20"/>
       <c r="AM12" s="20"/>
       <c r="AN12" s="20"/>
-      <c r="AO12" s="20"/>
+      <c r="AO12" s="7"/>
       <c r="AP12" s="7"/>
       <c r="AQ12" s="7"/>
       <c r="AR12" s="7"/>
@@ -5024,12 +5009,12 @@
       <c r="BU12" s="7"/>
       <c r="BV12" s="7"/>
       <c r="BW12" s="7"/>
-      <c r="BX12" s="7"/>
-      <c r="BY12" s="20"/>
-      <c r="BZ12" s="7"/>
-      <c r="CA12" s="20"/>
-      <c r="CB12" s="7"/>
-      <c r="CC12" s="20"/>
+      <c r="BX12" s="20"/>
+      <c r="BY12" s="7"/>
+      <c r="BZ12" s="20"/>
+      <c r="CA12" s="7"/>
+      <c r="CB12" s="20"/>
+      <c r="CC12" s="7"/>
       <c r="CD12" s="7"/>
       <c r="CE12" s="7"/>
       <c r="CF12" s="7"/>
@@ -5038,10 +5023,10 @@
       <c r="CI12" s="7"/>
       <c r="CJ12" s="7"/>
       <c r="CK12" s="7"/>
-      <c r="CL12" s="7"/>
+      <c r="CL12" s="21"/>
       <c r="CM12" s="21"/>
-      <c r="CN12" s="21"/>
-      <c r="CO12" s="22"/>
+      <c r="CN12" s="22"/>
+      <c r="CO12" s="7"/>
       <c r="CP12" s="7"/>
       <c r="CQ12" s="7"/>
       <c r="CR12" s="7"/>
@@ -5054,41 +5039,41 @@
       <c r="CY12" s="7"/>
       <c r="CZ12" s="7"/>
       <c r="DA12" s="7"/>
-      <c r="DB12" s="7"/>
-      <c r="DC12" s="23"/>
+      <c r="DB12" s="23"/>
+      <c r="DC12" s="7"/>
       <c r="DD12" s="7"/>
       <c r="DE12" s="7"/>
-      <c r="DF12" s="7"/>
+      <c r="DF12" s="20"/>
       <c r="DG12" s="20"/>
       <c r="DH12" s="20"/>
       <c r="DI12" s="20"/>
       <c r="DJ12" s="20"/>
-      <c r="DK12" s="20"/>
+      <c r="DK12" s="24"/>
       <c r="DL12" s="24"/>
       <c r="DM12" s="24"/>
-      <c r="DN12" s="24"/>
-      <c r="DO12" s="7"/>
-      <c r="DP12" s="20"/>
-      <c r="DQ12" s="23"/>
+      <c r="DN12" s="7"/>
+      <c r="DO12" s="20"/>
+      <c r="DP12" s="23"/>
+      <c r="DQ12" s="7"/>
       <c r="DR12" s="7"/>
       <c r="DS12" s="7"/>
-      <c r="DT12" s="7"/>
+      <c r="DT12" s="20"/>
       <c r="DU12" s="20"/>
       <c r="DV12" s="20"/>
       <c r="DW12" s="20"/>
-      <c r="DX12" s="20"/>
-      <c r="DY12" s="7"/>
-      <c r="DZ12" s="23"/>
-      <c r="EA12" s="20"/>
-      <c r="EB12" s="7"/>
-      <c r="EC12" s="23"/>
-      <c r="ED12" s="20"/>
+      <c r="DX12" s="7"/>
+      <c r="DY12" s="23"/>
+      <c r="DZ12" s="20"/>
+      <c r="EA12" s="7"/>
+      <c r="EB12" s="23"/>
+      <c r="EC12" s="20"/>
+      <c r="ED12" s="7"/>
       <c r="EE12" s="7"/>
       <c r="EF12" s="7"/>
-      <c r="EG12" s="7"/>
+      <c r="EG12" s="20"/>
       <c r="EH12" s="20"/>
       <c r="EI12" s="20"/>
-      <c r="EJ12" s="20"/>
+      <c r="EJ12" s="7"/>
       <c r="EK12" s="7"/>
       <c r="EL12" s="7"/>
       <c r="EM12" s="7"/>
@@ -5144,9 +5129,8 @@
       <c r="GK12" s="7"/>
       <c r="GL12" s="7"/>
       <c r="GM12" s="7"/>
-      <c r="GN12" s="7"/>
-    </row>
-    <row r="13" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -5187,7 +5171,7 @@
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
       <c r="AN13" s="20"/>
-      <c r="AO13" s="20"/>
+      <c r="AO13" s="7"/>
       <c r="AP13" s="7"/>
       <c r="AQ13" s="7"/>
       <c r="AR13" s="7"/>
@@ -5222,12 +5206,12 @@
       <c r="BU13" s="7"/>
       <c r="BV13" s="7"/>
       <c r="BW13" s="7"/>
-      <c r="BX13" s="7"/>
-      <c r="BY13" s="20"/>
-      <c r="BZ13" s="7"/>
-      <c r="CA13" s="20"/>
-      <c r="CB13" s="7"/>
-      <c r="CC13" s="20"/>
+      <c r="BX13" s="20"/>
+      <c r="BY13" s="7"/>
+      <c r="BZ13" s="20"/>
+      <c r="CA13" s="7"/>
+      <c r="CB13" s="20"/>
+      <c r="CC13" s="7"/>
       <c r="CD13" s="7"/>
       <c r="CE13" s="7"/>
       <c r="CF13" s="7"/>
@@ -5236,10 +5220,10 @@
       <c r="CI13" s="7"/>
       <c r="CJ13" s="7"/>
       <c r="CK13" s="7"/>
-      <c r="CL13" s="7"/>
+      <c r="CL13" s="21"/>
       <c r="CM13" s="21"/>
-      <c r="CN13" s="21"/>
-      <c r="CO13" s="22"/>
+      <c r="CN13" s="22"/>
+      <c r="CO13" s="7"/>
       <c r="CP13" s="7"/>
       <c r="CQ13" s="7"/>
       <c r="CR13" s="7"/>
@@ -5252,41 +5236,41 @@
       <c r="CY13" s="7"/>
       <c r="CZ13" s="7"/>
       <c r="DA13" s="7"/>
-      <c r="DB13" s="7"/>
-      <c r="DC13" s="23"/>
+      <c r="DB13" s="23"/>
+      <c r="DC13" s="7"/>
       <c r="DD13" s="7"/>
       <c r="DE13" s="7"/>
-      <c r="DF13" s="7"/>
+      <c r="DF13" s="20"/>
       <c r="DG13" s="20"/>
       <c r="DH13" s="20"/>
       <c r="DI13" s="20"/>
       <c r="DJ13" s="20"/>
-      <c r="DK13" s="20"/>
+      <c r="DK13" s="24"/>
       <c r="DL13" s="24"/>
       <c r="DM13" s="24"/>
-      <c r="DN13" s="24"/>
-      <c r="DO13" s="7"/>
-      <c r="DP13" s="20"/>
-      <c r="DQ13" s="23"/>
+      <c r="DN13" s="7"/>
+      <c r="DO13" s="20"/>
+      <c r="DP13" s="23"/>
+      <c r="DQ13" s="7"/>
       <c r="DR13" s="7"/>
       <c r="DS13" s="7"/>
-      <c r="DT13" s="7"/>
+      <c r="DT13" s="20"/>
       <c r="DU13" s="20"/>
       <c r="DV13" s="20"/>
       <c r="DW13" s="20"/>
-      <c r="DX13" s="20"/>
-      <c r="DY13" s="7"/>
-      <c r="DZ13" s="23"/>
-      <c r="EA13" s="20"/>
-      <c r="EB13" s="7"/>
-      <c r="EC13" s="23"/>
-      <c r="ED13" s="20"/>
+      <c r="DX13" s="7"/>
+      <c r="DY13" s="23"/>
+      <c r="DZ13" s="20"/>
+      <c r="EA13" s="7"/>
+      <c r="EB13" s="23"/>
+      <c r="EC13" s="20"/>
+      <c r="ED13" s="7"/>
       <c r="EE13" s="7"/>
       <c r="EF13" s="7"/>
-      <c r="EG13" s="7"/>
+      <c r="EG13" s="20"/>
       <c r="EH13" s="20"/>
       <c r="EI13" s="20"/>
-      <c r="EJ13" s="20"/>
+      <c r="EJ13" s="7"/>
       <c r="EK13" s="7"/>
       <c r="EL13" s="7"/>
       <c r="EM13" s="7"/>
@@ -5342,9 +5326,8 @@
       <c r="GK13" s="7"/>
       <c r="GL13" s="7"/>
       <c r="GM13" s="7"/>
-      <c r="GN13" s="7"/>
-    </row>
-    <row r="14" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -5385,7 +5368,7 @@
       <c r="AL14" s="20"/>
       <c r="AM14" s="20"/>
       <c r="AN14" s="20"/>
-      <c r="AO14" s="20"/>
+      <c r="AO14" s="7"/>
       <c r="AP14" s="7"/>
       <c r="AQ14" s="7"/>
       <c r="AR14" s="7"/>
@@ -5420,12 +5403,12 @@
       <c r="BU14" s="7"/>
       <c r="BV14" s="7"/>
       <c r="BW14" s="7"/>
-      <c r="BX14" s="7"/>
-      <c r="BY14" s="20"/>
-      <c r="BZ14" s="7"/>
-      <c r="CA14" s="20"/>
-      <c r="CB14" s="7"/>
-      <c r="CC14" s="20"/>
+      <c r="BX14" s="20"/>
+      <c r="BY14" s="7"/>
+      <c r="BZ14" s="20"/>
+      <c r="CA14" s="7"/>
+      <c r="CB14" s="20"/>
+      <c r="CC14" s="7"/>
       <c r="CD14" s="7"/>
       <c r="CE14" s="7"/>
       <c r="CF14" s="7"/>
@@ -5434,10 +5417,10 @@
       <c r="CI14" s="7"/>
       <c r="CJ14" s="7"/>
       <c r="CK14" s="7"/>
-      <c r="CL14" s="7"/>
+      <c r="CL14" s="21"/>
       <c r="CM14" s="21"/>
-      <c r="CN14" s="21"/>
-      <c r="CO14" s="22"/>
+      <c r="CN14" s="22"/>
+      <c r="CO14" s="7"/>
       <c r="CP14" s="7"/>
       <c r="CQ14" s="7"/>
       <c r="CR14" s="7"/>
@@ -5450,41 +5433,41 @@
       <c r="CY14" s="7"/>
       <c r="CZ14" s="7"/>
       <c r="DA14" s="7"/>
-      <c r="DB14" s="7"/>
-      <c r="DC14" s="23"/>
+      <c r="DB14" s="23"/>
+      <c r="DC14" s="7"/>
       <c r="DD14" s="7"/>
       <c r="DE14" s="7"/>
-      <c r="DF14" s="7"/>
+      <c r="DF14" s="20"/>
       <c r="DG14" s="20"/>
       <c r="DH14" s="20"/>
       <c r="DI14" s="20"/>
       <c r="DJ14" s="20"/>
-      <c r="DK14" s="20"/>
+      <c r="DK14" s="24"/>
       <c r="DL14" s="24"/>
       <c r="DM14" s="24"/>
-      <c r="DN14" s="24"/>
-      <c r="DO14" s="7"/>
-      <c r="DP14" s="20"/>
-      <c r="DQ14" s="23"/>
+      <c r="DN14" s="7"/>
+      <c r="DO14" s="20"/>
+      <c r="DP14" s="23"/>
+      <c r="DQ14" s="7"/>
       <c r="DR14" s="7"/>
       <c r="DS14" s="7"/>
-      <c r="DT14" s="7"/>
+      <c r="DT14" s="20"/>
       <c r="DU14" s="20"/>
       <c r="DV14" s="20"/>
       <c r="DW14" s="20"/>
-      <c r="DX14" s="20"/>
-      <c r="DY14" s="7"/>
-      <c r="DZ14" s="23"/>
-      <c r="EA14" s="20"/>
-      <c r="EB14" s="7"/>
-      <c r="EC14" s="23"/>
-      <c r="ED14" s="20"/>
+      <c r="DX14" s="7"/>
+      <c r="DY14" s="23"/>
+      <c r="DZ14" s="20"/>
+      <c r="EA14" s="7"/>
+      <c r="EB14" s="23"/>
+      <c r="EC14" s="20"/>
+      <c r="ED14" s="7"/>
       <c r="EE14" s="7"/>
       <c r="EF14" s="7"/>
-      <c r="EG14" s="7"/>
+      <c r="EG14" s="20"/>
       <c r="EH14" s="20"/>
       <c r="EI14" s="20"/>
-      <c r="EJ14" s="20"/>
+      <c r="EJ14" s="7"/>
       <c r="EK14" s="7"/>
       <c r="EL14" s="7"/>
       <c r="EM14" s="7"/>
@@ -5540,9 +5523,8 @@
       <c r="GK14" s="7"/>
       <c r="GL14" s="7"/>
       <c r="GM14" s="7"/>
-      <c r="GN14" s="7"/>
-    </row>
-    <row r="15" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -5583,7 +5565,7 @@
       <c r="AL15" s="20"/>
       <c r="AM15" s="20"/>
       <c r="AN15" s="20"/>
-      <c r="AO15" s="20"/>
+      <c r="AO15" s="7"/>
       <c r="AP15" s="7"/>
       <c r="AQ15" s="7"/>
       <c r="AR15" s="7"/>
@@ -5618,12 +5600,12 @@
       <c r="BU15" s="7"/>
       <c r="BV15" s="7"/>
       <c r="BW15" s="7"/>
-      <c r="BX15" s="7"/>
-      <c r="BY15" s="20"/>
-      <c r="BZ15" s="7"/>
-      <c r="CA15" s="20"/>
-      <c r="CB15" s="7"/>
-      <c r="CC15" s="20"/>
+      <c r="BX15" s="20"/>
+      <c r="BY15" s="7"/>
+      <c r="BZ15" s="20"/>
+      <c r="CA15" s="7"/>
+      <c r="CB15" s="20"/>
+      <c r="CC15" s="7"/>
       <c r="CD15" s="7"/>
       <c r="CE15" s="7"/>
       <c r="CF15" s="7"/>
@@ -5632,10 +5614,10 @@
       <c r="CI15" s="7"/>
       <c r="CJ15" s="7"/>
       <c r="CK15" s="7"/>
-      <c r="CL15" s="7"/>
+      <c r="CL15" s="21"/>
       <c r="CM15" s="21"/>
-      <c r="CN15" s="21"/>
-      <c r="CO15" s="22"/>
+      <c r="CN15" s="22"/>
+      <c r="CO15" s="7"/>
       <c r="CP15" s="7"/>
       <c r="CQ15" s="7"/>
       <c r="CR15" s="7"/>
@@ -5648,41 +5630,41 @@
       <c r="CY15" s="7"/>
       <c r="CZ15" s="7"/>
       <c r="DA15" s="7"/>
-      <c r="DB15" s="7"/>
-      <c r="DC15" s="23"/>
+      <c r="DB15" s="23"/>
+      <c r="DC15" s="7"/>
       <c r="DD15" s="7"/>
       <c r="DE15" s="7"/>
-      <c r="DF15" s="7"/>
+      <c r="DF15" s="20"/>
       <c r="DG15" s="20"/>
       <c r="DH15" s="20"/>
       <c r="DI15" s="20"/>
       <c r="DJ15" s="20"/>
-      <c r="DK15" s="20"/>
+      <c r="DK15" s="24"/>
       <c r="DL15" s="24"/>
       <c r="DM15" s="24"/>
-      <c r="DN15" s="24"/>
-      <c r="DO15" s="7"/>
-      <c r="DP15" s="20"/>
-      <c r="DQ15" s="23"/>
+      <c r="DN15" s="7"/>
+      <c r="DO15" s="20"/>
+      <c r="DP15" s="23"/>
+      <c r="DQ15" s="7"/>
       <c r="DR15" s="7"/>
       <c r="DS15" s="7"/>
-      <c r="DT15" s="7"/>
+      <c r="DT15" s="20"/>
       <c r="DU15" s="20"/>
       <c r="DV15" s="20"/>
       <c r="DW15" s="20"/>
-      <c r="DX15" s="20"/>
-      <c r="DY15" s="7"/>
-      <c r="DZ15" s="23"/>
-      <c r="EA15" s="20"/>
-      <c r="EB15" s="7"/>
-      <c r="EC15" s="23"/>
-      <c r="ED15" s="20"/>
+      <c r="DX15" s="7"/>
+      <c r="DY15" s="23"/>
+      <c r="DZ15" s="20"/>
+      <c r="EA15" s="7"/>
+      <c r="EB15" s="23"/>
+      <c r="EC15" s="20"/>
+      <c r="ED15" s="7"/>
       <c r="EE15" s="7"/>
       <c r="EF15" s="7"/>
-      <c r="EG15" s="7"/>
+      <c r="EG15" s="20"/>
       <c r="EH15" s="20"/>
       <c r="EI15" s="20"/>
-      <c r="EJ15" s="20"/>
+      <c r="EJ15" s="7"/>
       <c r="EK15" s="7"/>
       <c r="EL15" s="7"/>
       <c r="EM15" s="7"/>
@@ -5738,9 +5720,8 @@
       <c r="GK15" s="7"/>
       <c r="GL15" s="7"/>
       <c r="GM15" s="7"/>
-      <c r="GN15" s="7"/>
-    </row>
-    <row r="16" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -5781,7 +5762,7 @@
       <c r="AL16" s="20"/>
       <c r="AM16" s="20"/>
       <c r="AN16" s="20"/>
-      <c r="AO16" s="20"/>
+      <c r="AO16" s="7"/>
       <c r="AP16" s="7"/>
       <c r="AQ16" s="7"/>
       <c r="AR16" s="7"/>
@@ -5816,12 +5797,12 @@
       <c r="BU16" s="7"/>
       <c r="BV16" s="7"/>
       <c r="BW16" s="7"/>
-      <c r="BX16" s="7"/>
-      <c r="BY16" s="20"/>
-      <c r="BZ16" s="7"/>
-      <c r="CA16" s="20"/>
-      <c r="CB16" s="7"/>
-      <c r="CC16" s="20"/>
+      <c r="BX16" s="20"/>
+      <c r="BY16" s="7"/>
+      <c r="BZ16" s="20"/>
+      <c r="CA16" s="7"/>
+      <c r="CB16" s="20"/>
+      <c r="CC16" s="7"/>
       <c r="CD16" s="7"/>
       <c r="CE16" s="7"/>
       <c r="CF16" s="7"/>
@@ -5830,10 +5811,10 @@
       <c r="CI16" s="7"/>
       <c r="CJ16" s="7"/>
       <c r="CK16" s="7"/>
-      <c r="CL16" s="7"/>
+      <c r="CL16" s="21"/>
       <c r="CM16" s="21"/>
-      <c r="CN16" s="21"/>
-      <c r="CO16" s="22"/>
+      <c r="CN16" s="22"/>
+      <c r="CO16" s="7"/>
       <c r="CP16" s="7"/>
       <c r="CQ16" s="7"/>
       <c r="CR16" s="7"/>
@@ -5846,41 +5827,41 @@
       <c r="CY16" s="7"/>
       <c r="CZ16" s="7"/>
       <c r="DA16" s="7"/>
-      <c r="DB16" s="7"/>
-      <c r="DC16" s="23"/>
+      <c r="DB16" s="23"/>
+      <c r="DC16" s="7"/>
       <c r="DD16" s="7"/>
       <c r="DE16" s="7"/>
-      <c r="DF16" s="7"/>
+      <c r="DF16" s="20"/>
       <c r="DG16" s="20"/>
       <c r="DH16" s="20"/>
       <c r="DI16" s="20"/>
       <c r="DJ16" s="20"/>
-      <c r="DK16" s="20"/>
+      <c r="DK16" s="24"/>
       <c r="DL16" s="24"/>
       <c r="DM16" s="24"/>
-      <c r="DN16" s="24"/>
-      <c r="DO16" s="7"/>
-      <c r="DP16" s="20"/>
-      <c r="DQ16" s="23"/>
+      <c r="DN16" s="7"/>
+      <c r="DO16" s="20"/>
+      <c r="DP16" s="23"/>
+      <c r="DQ16" s="7"/>
       <c r="DR16" s="7"/>
       <c r="DS16" s="7"/>
-      <c r="DT16" s="7"/>
+      <c r="DT16" s="20"/>
       <c r="DU16" s="20"/>
       <c r="DV16" s="20"/>
       <c r="DW16" s="20"/>
-      <c r="DX16" s="20"/>
-      <c r="DY16" s="7"/>
-      <c r="DZ16" s="23"/>
-      <c r="EA16" s="20"/>
-      <c r="EB16" s="7"/>
-      <c r="EC16" s="23"/>
-      <c r="ED16" s="20"/>
+      <c r="DX16" s="7"/>
+      <c r="DY16" s="23"/>
+      <c r="DZ16" s="20"/>
+      <c r="EA16" s="7"/>
+      <c r="EB16" s="23"/>
+      <c r="EC16" s="20"/>
+      <c r="ED16" s="7"/>
       <c r="EE16" s="7"/>
       <c r="EF16" s="7"/>
-      <c r="EG16" s="7"/>
+      <c r="EG16" s="20"/>
       <c r="EH16" s="20"/>
       <c r="EI16" s="20"/>
-      <c r="EJ16" s="20"/>
+      <c r="EJ16" s="7"/>
       <c r="EK16" s="7"/>
       <c r="EL16" s="7"/>
       <c r="EM16" s="7"/>
@@ -5936,9 +5917,8 @@
       <c r="GK16" s="7"/>
       <c r="GL16" s="7"/>
       <c r="GM16" s="7"/>
-      <c r="GN16" s="7"/>
-    </row>
-    <row r="17" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -5979,7 +5959,7 @@
       <c r="AL17" s="20"/>
       <c r="AM17" s="20"/>
       <c r="AN17" s="20"/>
-      <c r="AO17" s="20"/>
+      <c r="AO17" s="7"/>
       <c r="AP17" s="7"/>
       <c r="AQ17" s="7"/>
       <c r="AR17" s="7"/>
@@ -6014,12 +5994,12 @@
       <c r="BU17" s="7"/>
       <c r="BV17" s="7"/>
       <c r="BW17" s="7"/>
-      <c r="BX17" s="7"/>
-      <c r="BY17" s="20"/>
-      <c r="BZ17" s="7"/>
-      <c r="CA17" s="20"/>
-      <c r="CB17" s="7"/>
-      <c r="CC17" s="20"/>
+      <c r="BX17" s="20"/>
+      <c r="BY17" s="7"/>
+      <c r="BZ17" s="20"/>
+      <c r="CA17" s="7"/>
+      <c r="CB17" s="20"/>
+      <c r="CC17" s="7"/>
       <c r="CD17" s="7"/>
       <c r="CE17" s="7"/>
       <c r="CF17" s="7"/>
@@ -6028,10 +6008,10 @@
       <c r="CI17" s="7"/>
       <c r="CJ17" s="7"/>
       <c r="CK17" s="7"/>
-      <c r="CL17" s="7"/>
+      <c r="CL17" s="21"/>
       <c r="CM17" s="21"/>
-      <c r="CN17" s="21"/>
-      <c r="CO17" s="22"/>
+      <c r="CN17" s="22"/>
+      <c r="CO17" s="7"/>
       <c r="CP17" s="7"/>
       <c r="CQ17" s="7"/>
       <c r="CR17" s="7"/>
@@ -6044,41 +6024,41 @@
       <c r="CY17" s="7"/>
       <c r="CZ17" s="7"/>
       <c r="DA17" s="7"/>
-      <c r="DB17" s="7"/>
-      <c r="DC17" s="23"/>
+      <c r="DB17" s="23"/>
+      <c r="DC17" s="7"/>
       <c r="DD17" s="7"/>
       <c r="DE17" s="7"/>
-      <c r="DF17" s="7"/>
+      <c r="DF17" s="20"/>
       <c r="DG17" s="20"/>
       <c r="DH17" s="20"/>
       <c r="DI17" s="20"/>
       <c r="DJ17" s="20"/>
-      <c r="DK17" s="20"/>
+      <c r="DK17" s="24"/>
       <c r="DL17" s="24"/>
       <c r="DM17" s="24"/>
-      <c r="DN17" s="24"/>
-      <c r="DO17" s="7"/>
-      <c r="DP17" s="20"/>
-      <c r="DQ17" s="23"/>
+      <c r="DN17" s="7"/>
+      <c r="DO17" s="20"/>
+      <c r="DP17" s="23"/>
+      <c r="DQ17" s="7"/>
       <c r="DR17" s="7"/>
       <c r="DS17" s="7"/>
-      <c r="DT17" s="7"/>
+      <c r="DT17" s="20"/>
       <c r="DU17" s="20"/>
       <c r="DV17" s="20"/>
       <c r="DW17" s="20"/>
-      <c r="DX17" s="20"/>
-      <c r="DY17" s="7"/>
-      <c r="DZ17" s="23"/>
-      <c r="EA17" s="20"/>
-      <c r="EB17" s="7"/>
-      <c r="EC17" s="23"/>
-      <c r="ED17" s="20"/>
+      <c r="DX17" s="7"/>
+      <c r="DY17" s="23"/>
+      <c r="DZ17" s="20"/>
+      <c r="EA17" s="7"/>
+      <c r="EB17" s="23"/>
+      <c r="EC17" s="20"/>
+      <c r="ED17" s="7"/>
       <c r="EE17" s="7"/>
       <c r="EF17" s="7"/>
-      <c r="EG17" s="7"/>
+      <c r="EG17" s="20"/>
       <c r="EH17" s="20"/>
       <c r="EI17" s="20"/>
-      <c r="EJ17" s="20"/>
+      <c r="EJ17" s="7"/>
       <c r="EK17" s="7"/>
       <c r="EL17" s="7"/>
       <c r="EM17" s="7"/>
@@ -6134,9 +6114,8 @@
       <c r="GK17" s="7"/>
       <c r="GL17" s="7"/>
       <c r="GM17" s="7"/>
-      <c r="GN17" s="7"/>
-    </row>
-    <row r="18" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -6177,7 +6156,7 @@
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
       <c r="AN18" s="20"/>
-      <c r="AO18" s="20"/>
+      <c r="AO18" s="7"/>
       <c r="AP18" s="7"/>
       <c r="AQ18" s="7"/>
       <c r="AR18" s="7"/>
@@ -6212,12 +6191,12 @@
       <c r="BU18" s="7"/>
       <c r="BV18" s="7"/>
       <c r="BW18" s="7"/>
-      <c r="BX18" s="7"/>
-      <c r="BY18" s="20"/>
-      <c r="BZ18" s="7"/>
-      <c r="CA18" s="20"/>
-      <c r="CB18" s="7"/>
-      <c r="CC18" s="20"/>
+      <c r="BX18" s="20"/>
+      <c r="BY18" s="7"/>
+      <c r="BZ18" s="20"/>
+      <c r="CA18" s="7"/>
+      <c r="CB18" s="20"/>
+      <c r="CC18" s="7"/>
       <c r="CD18" s="7"/>
       <c r="CE18" s="7"/>
       <c r="CF18" s="7"/>
@@ -6226,10 +6205,10 @@
       <c r="CI18" s="7"/>
       <c r="CJ18" s="7"/>
       <c r="CK18" s="7"/>
-      <c r="CL18" s="7"/>
+      <c r="CL18" s="21"/>
       <c r="CM18" s="21"/>
-      <c r="CN18" s="21"/>
-      <c r="CO18" s="22"/>
+      <c r="CN18" s="22"/>
+      <c r="CO18" s="7"/>
       <c r="CP18" s="7"/>
       <c r="CQ18" s="7"/>
       <c r="CR18" s="7"/>
@@ -6242,41 +6221,41 @@
       <c r="CY18" s="7"/>
       <c r="CZ18" s="7"/>
       <c r="DA18" s="7"/>
-      <c r="DB18" s="7"/>
-      <c r="DC18" s="23"/>
+      <c r="DB18" s="23"/>
+      <c r="DC18" s="7"/>
       <c r="DD18" s="7"/>
       <c r="DE18" s="7"/>
-      <c r="DF18" s="7"/>
+      <c r="DF18" s="20"/>
       <c r="DG18" s="20"/>
       <c r="DH18" s="20"/>
       <c r="DI18" s="20"/>
       <c r="DJ18" s="20"/>
-      <c r="DK18" s="20"/>
+      <c r="DK18" s="24"/>
       <c r="DL18" s="24"/>
       <c r="DM18" s="24"/>
-      <c r="DN18" s="24"/>
-      <c r="DO18" s="7"/>
-      <c r="DP18" s="20"/>
-      <c r="DQ18" s="23"/>
+      <c r="DN18" s="7"/>
+      <c r="DO18" s="20"/>
+      <c r="DP18" s="23"/>
+      <c r="DQ18" s="7"/>
       <c r="DR18" s="7"/>
       <c r="DS18" s="7"/>
-      <c r="DT18" s="7"/>
+      <c r="DT18" s="20"/>
       <c r="DU18" s="20"/>
       <c r="DV18" s="20"/>
       <c r="DW18" s="20"/>
-      <c r="DX18" s="20"/>
-      <c r="DY18" s="7"/>
-      <c r="DZ18" s="23"/>
-      <c r="EA18" s="20"/>
-      <c r="EB18" s="7"/>
-      <c r="EC18" s="23"/>
-      <c r="ED18" s="20"/>
+      <c r="DX18" s="7"/>
+      <c r="DY18" s="23"/>
+      <c r="DZ18" s="20"/>
+      <c r="EA18" s="7"/>
+      <c r="EB18" s="23"/>
+      <c r="EC18" s="20"/>
+      <c r="ED18" s="7"/>
       <c r="EE18" s="7"/>
       <c r="EF18" s="7"/>
-      <c r="EG18" s="7"/>
+      <c r="EG18" s="20"/>
       <c r="EH18" s="20"/>
       <c r="EI18" s="20"/>
-      <c r="EJ18" s="20"/>
+      <c r="EJ18" s="7"/>
       <c r="EK18" s="7"/>
       <c r="EL18" s="7"/>
       <c r="EM18" s="7"/>
@@ -6332,9 +6311,8 @@
       <c r="GK18" s="7"/>
       <c r="GL18" s="7"/>
       <c r="GM18" s="7"/>
-      <c r="GN18" s="7"/>
-    </row>
-    <row r="19" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -6375,7 +6353,7 @@
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
       <c r="AN19" s="20"/>
-      <c r="AO19" s="20"/>
+      <c r="AO19" s="7"/>
       <c r="AP19" s="7"/>
       <c r="AQ19" s="7"/>
       <c r="AR19" s="7"/>
@@ -6410,12 +6388,12 @@
       <c r="BU19" s="7"/>
       <c r="BV19" s="7"/>
       <c r="BW19" s="7"/>
-      <c r="BX19" s="7"/>
-      <c r="BY19" s="20"/>
-      <c r="BZ19" s="7"/>
-      <c r="CA19" s="20"/>
-      <c r="CB19" s="7"/>
-      <c r="CC19" s="20"/>
+      <c r="BX19" s="20"/>
+      <c r="BY19" s="7"/>
+      <c r="BZ19" s="20"/>
+      <c r="CA19" s="7"/>
+      <c r="CB19" s="20"/>
+      <c r="CC19" s="7"/>
       <c r="CD19" s="7"/>
       <c r="CE19" s="7"/>
       <c r="CF19" s="7"/>
@@ -6424,10 +6402,10 @@
       <c r="CI19" s="7"/>
       <c r="CJ19" s="7"/>
       <c r="CK19" s="7"/>
-      <c r="CL19" s="7"/>
+      <c r="CL19" s="21"/>
       <c r="CM19" s="21"/>
-      <c r="CN19" s="21"/>
-      <c r="CO19" s="22"/>
+      <c r="CN19" s="22"/>
+      <c r="CO19" s="7"/>
       <c r="CP19" s="7"/>
       <c r="CQ19" s="7"/>
       <c r="CR19" s="7"/>
@@ -6440,41 +6418,41 @@
       <c r="CY19" s="7"/>
       <c r="CZ19" s="7"/>
       <c r="DA19" s="7"/>
-      <c r="DB19" s="7"/>
-      <c r="DC19" s="23"/>
+      <c r="DB19" s="23"/>
+      <c r="DC19" s="7"/>
       <c r="DD19" s="7"/>
       <c r="DE19" s="7"/>
-      <c r="DF19" s="7"/>
+      <c r="DF19" s="20"/>
       <c r="DG19" s="20"/>
       <c r="DH19" s="20"/>
       <c r="DI19" s="20"/>
       <c r="DJ19" s="20"/>
-      <c r="DK19" s="20"/>
+      <c r="DK19" s="24"/>
       <c r="DL19" s="24"/>
       <c r="DM19" s="24"/>
-      <c r="DN19" s="24"/>
-      <c r="DO19" s="7"/>
-      <c r="DP19" s="20"/>
-      <c r="DQ19" s="23"/>
+      <c r="DN19" s="7"/>
+      <c r="DO19" s="20"/>
+      <c r="DP19" s="23"/>
+      <c r="DQ19" s="7"/>
       <c r="DR19" s="7"/>
       <c r="DS19" s="7"/>
-      <c r="DT19" s="7"/>
+      <c r="DT19" s="20"/>
       <c r="DU19" s="20"/>
       <c r="DV19" s="20"/>
       <c r="DW19" s="20"/>
-      <c r="DX19" s="20"/>
-      <c r="DY19" s="7"/>
-      <c r="DZ19" s="23"/>
-      <c r="EA19" s="20"/>
-      <c r="EB19" s="7"/>
-      <c r="EC19" s="23"/>
-      <c r="ED19" s="20"/>
+      <c r="DX19" s="7"/>
+      <c r="DY19" s="23"/>
+      <c r="DZ19" s="20"/>
+      <c r="EA19" s="7"/>
+      <c r="EB19" s="23"/>
+      <c r="EC19" s="20"/>
+      <c r="ED19" s="7"/>
       <c r="EE19" s="7"/>
       <c r="EF19" s="7"/>
-      <c r="EG19" s="7"/>
+      <c r="EG19" s="20"/>
       <c r="EH19" s="20"/>
       <c r="EI19" s="20"/>
-      <c r="EJ19" s="20"/>
+      <c r="EJ19" s="7"/>
       <c r="EK19" s="7"/>
       <c r="EL19" s="7"/>
       <c r="EM19" s="7"/>
@@ -6530,9 +6508,8 @@
       <c r="GK19" s="7"/>
       <c r="GL19" s="7"/>
       <c r="GM19" s="7"/>
-      <c r="GN19" s="7"/>
-    </row>
-    <row r="20" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -6573,7 +6550,7 @@
       <c r="AL20" s="20"/>
       <c r="AM20" s="20"/>
       <c r="AN20" s="20"/>
-      <c r="AO20" s="20"/>
+      <c r="AO20" s="7"/>
       <c r="AP20" s="7"/>
       <c r="AQ20" s="7"/>
       <c r="AR20" s="7"/>
@@ -6608,12 +6585,12 @@
       <c r="BU20" s="7"/>
       <c r="BV20" s="7"/>
       <c r="BW20" s="7"/>
-      <c r="BX20" s="7"/>
-      <c r="BY20" s="20"/>
-      <c r="BZ20" s="7"/>
-      <c r="CA20" s="20"/>
-      <c r="CB20" s="7"/>
-      <c r="CC20" s="20"/>
+      <c r="BX20" s="20"/>
+      <c r="BY20" s="7"/>
+      <c r="BZ20" s="20"/>
+      <c r="CA20" s="7"/>
+      <c r="CB20" s="20"/>
+      <c r="CC20" s="7"/>
       <c r="CD20" s="7"/>
       <c r="CE20" s="7"/>
       <c r="CF20" s="7"/>
@@ -6622,10 +6599,10 @@
       <c r="CI20" s="7"/>
       <c r="CJ20" s="7"/>
       <c r="CK20" s="7"/>
-      <c r="CL20" s="7"/>
+      <c r="CL20" s="21"/>
       <c r="CM20" s="21"/>
-      <c r="CN20" s="21"/>
-      <c r="CO20" s="22"/>
+      <c r="CN20" s="22"/>
+      <c r="CO20" s="7"/>
       <c r="CP20" s="7"/>
       <c r="CQ20" s="7"/>
       <c r="CR20" s="7"/>
@@ -6638,41 +6615,41 @@
       <c r="CY20" s="7"/>
       <c r="CZ20" s="7"/>
       <c r="DA20" s="7"/>
-      <c r="DB20" s="7"/>
-      <c r="DC20" s="23"/>
+      <c r="DB20" s="23"/>
+      <c r="DC20" s="7"/>
       <c r="DD20" s="7"/>
       <c r="DE20" s="7"/>
-      <c r="DF20" s="7"/>
+      <c r="DF20" s="20"/>
       <c r="DG20" s="20"/>
       <c r="DH20" s="20"/>
       <c r="DI20" s="20"/>
       <c r="DJ20" s="20"/>
-      <c r="DK20" s="20"/>
+      <c r="DK20" s="24"/>
       <c r="DL20" s="24"/>
       <c r="DM20" s="24"/>
-      <c r="DN20" s="24"/>
-      <c r="DO20" s="7"/>
-      <c r="DP20" s="20"/>
-      <c r="DQ20" s="23"/>
+      <c r="DN20" s="7"/>
+      <c r="DO20" s="20"/>
+      <c r="DP20" s="23"/>
+      <c r="DQ20" s="7"/>
       <c r="DR20" s="7"/>
       <c r="DS20" s="7"/>
-      <c r="DT20" s="7"/>
+      <c r="DT20" s="20"/>
       <c r="DU20" s="20"/>
       <c r="DV20" s="20"/>
       <c r="DW20" s="20"/>
-      <c r="DX20" s="20"/>
-      <c r="DY20" s="7"/>
-      <c r="DZ20" s="23"/>
-      <c r="EA20" s="20"/>
-      <c r="EB20" s="7"/>
-      <c r="EC20" s="23"/>
-      <c r="ED20" s="20"/>
+      <c r="DX20" s="7"/>
+      <c r="DY20" s="23"/>
+      <c r="DZ20" s="20"/>
+      <c r="EA20" s="7"/>
+      <c r="EB20" s="23"/>
+      <c r="EC20" s="20"/>
+      <c r="ED20" s="7"/>
       <c r="EE20" s="7"/>
       <c r="EF20" s="7"/>
-      <c r="EG20" s="7"/>
+      <c r="EG20" s="20"/>
       <c r="EH20" s="20"/>
       <c r="EI20" s="20"/>
-      <c r="EJ20" s="20"/>
+      <c r="EJ20" s="7"/>
       <c r="EK20" s="7"/>
       <c r="EL20" s="7"/>
       <c r="EM20" s="7"/>
@@ -6728,9 +6705,8 @@
       <c r="GK20" s="7"/>
       <c r="GL20" s="7"/>
       <c r="GM20" s="7"/>
-      <c r="GN20" s="7"/>
-    </row>
-    <row r="21" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6771,7 +6747,7 @@
       <c r="AL21" s="20"/>
       <c r="AM21" s="20"/>
       <c r="AN21" s="20"/>
-      <c r="AO21" s="20"/>
+      <c r="AO21" s="7"/>
       <c r="AP21" s="7"/>
       <c r="AQ21" s="7"/>
       <c r="AR21" s="7"/>
@@ -6806,12 +6782,12 @@
       <c r="BU21" s="7"/>
       <c r="BV21" s="7"/>
       <c r="BW21" s="7"/>
-      <c r="BX21" s="7"/>
-      <c r="BY21" s="20"/>
-      <c r="BZ21" s="7"/>
-      <c r="CA21" s="20"/>
-      <c r="CB21" s="7"/>
-      <c r="CC21" s="20"/>
+      <c r="BX21" s="20"/>
+      <c r="BY21" s="7"/>
+      <c r="BZ21" s="20"/>
+      <c r="CA21" s="7"/>
+      <c r="CB21" s="20"/>
+      <c r="CC21" s="7"/>
       <c r="CD21" s="7"/>
       <c r="CE21" s="7"/>
       <c r="CF21" s="7"/>
@@ -6820,10 +6796,10 @@
       <c r="CI21" s="7"/>
       <c r="CJ21" s="7"/>
       <c r="CK21" s="7"/>
-      <c r="CL21" s="7"/>
+      <c r="CL21" s="21"/>
       <c r="CM21" s="21"/>
-      <c r="CN21" s="21"/>
-      <c r="CO21" s="22"/>
+      <c r="CN21" s="22"/>
+      <c r="CO21" s="7"/>
       <c r="CP21" s="7"/>
       <c r="CQ21" s="7"/>
       <c r="CR21" s="7"/>
@@ -6836,41 +6812,41 @@
       <c r="CY21" s="7"/>
       <c r="CZ21" s="7"/>
       <c r="DA21" s="7"/>
-      <c r="DB21" s="7"/>
-      <c r="DC21" s="23"/>
+      <c r="DB21" s="23"/>
+      <c r="DC21" s="7"/>
       <c r="DD21" s="7"/>
       <c r="DE21" s="7"/>
-      <c r="DF21" s="7"/>
+      <c r="DF21" s="20"/>
       <c r="DG21" s="20"/>
       <c r="DH21" s="20"/>
       <c r="DI21" s="20"/>
       <c r="DJ21" s="20"/>
-      <c r="DK21" s="20"/>
+      <c r="DK21" s="24"/>
       <c r="DL21" s="24"/>
       <c r="DM21" s="24"/>
-      <c r="DN21" s="24"/>
-      <c r="DO21" s="7"/>
-      <c r="DP21" s="20"/>
-      <c r="DQ21" s="23"/>
+      <c r="DN21" s="7"/>
+      <c r="DO21" s="20"/>
+      <c r="DP21" s="23"/>
+      <c r="DQ21" s="7"/>
       <c r="DR21" s="7"/>
       <c r="DS21" s="7"/>
-      <c r="DT21" s="7"/>
+      <c r="DT21" s="20"/>
       <c r="DU21" s="20"/>
       <c r="DV21" s="20"/>
       <c r="DW21" s="20"/>
-      <c r="DX21" s="20"/>
-      <c r="DY21" s="7"/>
-      <c r="DZ21" s="23"/>
-      <c r="EA21" s="20"/>
-      <c r="EB21" s="7"/>
-      <c r="EC21" s="23"/>
-      <c r="ED21" s="20"/>
+      <c r="DX21" s="7"/>
+      <c r="DY21" s="23"/>
+      <c r="DZ21" s="20"/>
+      <c r="EA21" s="7"/>
+      <c r="EB21" s="23"/>
+      <c r="EC21" s="20"/>
+      <c r="ED21" s="7"/>
       <c r="EE21" s="7"/>
       <c r="EF21" s="7"/>
-      <c r="EG21" s="7"/>
+      <c r="EG21" s="20"/>
       <c r="EH21" s="20"/>
       <c r="EI21" s="20"/>
-      <c r="EJ21" s="20"/>
+      <c r="EJ21" s="7"/>
       <c r="EK21" s="7"/>
       <c r="EL21" s="7"/>
       <c r="EM21" s="7"/>
@@ -6926,9 +6902,8 @@
       <c r="GK21" s="7"/>
       <c r="GL21" s="7"/>
       <c r="GM21" s="7"/>
-      <c r="GN21" s="7"/>
-    </row>
-    <row r="22" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -6969,7 +6944,7 @@
       <c r="AL22" s="20"/>
       <c r="AM22" s="20"/>
       <c r="AN22" s="20"/>
-      <c r="AO22" s="20"/>
+      <c r="AO22" s="7"/>
       <c r="AP22" s="7"/>
       <c r="AQ22" s="7"/>
       <c r="AR22" s="7"/>
@@ -7004,12 +6979,12 @@
       <c r="BU22" s="7"/>
       <c r="BV22" s="7"/>
       <c r="BW22" s="7"/>
-      <c r="BX22" s="7"/>
-      <c r="BY22" s="20"/>
-      <c r="BZ22" s="7"/>
-      <c r="CA22" s="20"/>
-      <c r="CB22" s="7"/>
-      <c r="CC22" s="20"/>
+      <c r="BX22" s="20"/>
+      <c r="BY22" s="7"/>
+      <c r="BZ22" s="20"/>
+      <c r="CA22" s="7"/>
+      <c r="CB22" s="20"/>
+      <c r="CC22" s="7"/>
       <c r="CD22" s="7"/>
       <c r="CE22" s="7"/>
       <c r="CF22" s="7"/>
@@ -7018,10 +6993,10 @@
       <c r="CI22" s="7"/>
       <c r="CJ22" s="7"/>
       <c r="CK22" s="7"/>
-      <c r="CL22" s="7"/>
+      <c r="CL22" s="21"/>
       <c r="CM22" s="21"/>
-      <c r="CN22" s="21"/>
-      <c r="CO22" s="22"/>
+      <c r="CN22" s="22"/>
+      <c r="CO22" s="7"/>
       <c r="CP22" s="7"/>
       <c r="CQ22" s="7"/>
       <c r="CR22" s="7"/>
@@ -7034,41 +7009,41 @@
       <c r="CY22" s="7"/>
       <c r="CZ22" s="7"/>
       <c r="DA22" s="7"/>
-      <c r="DB22" s="7"/>
-      <c r="DC22" s="23"/>
+      <c r="DB22" s="23"/>
+      <c r="DC22" s="7"/>
       <c r="DD22" s="7"/>
       <c r="DE22" s="7"/>
-      <c r="DF22" s="7"/>
+      <c r="DF22" s="20"/>
       <c r="DG22" s="20"/>
       <c r="DH22" s="20"/>
       <c r="DI22" s="20"/>
       <c r="DJ22" s="20"/>
-      <c r="DK22" s="20"/>
+      <c r="DK22" s="24"/>
       <c r="DL22" s="24"/>
       <c r="DM22" s="24"/>
-      <c r="DN22" s="24"/>
-      <c r="DO22" s="7"/>
-      <c r="DP22" s="20"/>
-      <c r="DQ22" s="23"/>
+      <c r="DN22" s="7"/>
+      <c r="DO22" s="20"/>
+      <c r="DP22" s="23"/>
+      <c r="DQ22" s="7"/>
       <c r="DR22" s="7"/>
       <c r="DS22" s="7"/>
-      <c r="DT22" s="7"/>
+      <c r="DT22" s="20"/>
       <c r="DU22" s="20"/>
       <c r="DV22" s="20"/>
       <c r="DW22" s="20"/>
-      <c r="DX22" s="20"/>
-      <c r="DY22" s="7"/>
-      <c r="DZ22" s="23"/>
-      <c r="EA22" s="20"/>
-      <c r="EB22" s="7"/>
-      <c r="EC22" s="23"/>
-      <c r="ED22" s="20"/>
+      <c r="DX22" s="7"/>
+      <c r="DY22" s="23"/>
+      <c r="DZ22" s="20"/>
+      <c r="EA22" s="7"/>
+      <c r="EB22" s="23"/>
+      <c r="EC22" s="20"/>
+      <c r="ED22" s="7"/>
       <c r="EE22" s="7"/>
       <c r="EF22" s="7"/>
-      <c r="EG22" s="7"/>
+      <c r="EG22" s="20"/>
       <c r="EH22" s="20"/>
       <c r="EI22" s="20"/>
-      <c r="EJ22" s="20"/>
+      <c r="EJ22" s="7"/>
       <c r="EK22" s="7"/>
       <c r="EL22" s="7"/>
       <c r="EM22" s="7"/>
@@ -7124,9 +7099,8 @@
       <c r="GK22" s="7"/>
       <c r="GL22" s="7"/>
       <c r="GM22" s="7"/>
-      <c r="GN22" s="7"/>
-    </row>
-    <row r="23" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -7167,7 +7141,7 @@
       <c r="AL23" s="20"/>
       <c r="AM23" s="20"/>
       <c r="AN23" s="20"/>
-      <c r="AO23" s="20"/>
+      <c r="AO23" s="7"/>
       <c r="AP23" s="7"/>
       <c r="AQ23" s="7"/>
       <c r="AR23" s="7"/>
@@ -7202,12 +7176,12 @@
       <c r="BU23" s="7"/>
       <c r="BV23" s="7"/>
       <c r="BW23" s="7"/>
-      <c r="BX23" s="7"/>
-      <c r="BY23" s="20"/>
-      <c r="BZ23" s="7"/>
-      <c r="CA23" s="20"/>
-      <c r="CB23" s="7"/>
-      <c r="CC23" s="20"/>
+      <c r="BX23" s="20"/>
+      <c r="BY23" s="7"/>
+      <c r="BZ23" s="20"/>
+      <c r="CA23" s="7"/>
+      <c r="CB23" s="20"/>
+      <c r="CC23" s="7"/>
       <c r="CD23" s="7"/>
       <c r="CE23" s="7"/>
       <c r="CF23" s="7"/>
@@ -7216,10 +7190,10 @@
       <c r="CI23" s="7"/>
       <c r="CJ23" s="7"/>
       <c r="CK23" s="7"/>
-      <c r="CL23" s="7"/>
+      <c r="CL23" s="21"/>
       <c r="CM23" s="21"/>
-      <c r="CN23" s="21"/>
-      <c r="CO23" s="22"/>
+      <c r="CN23" s="22"/>
+      <c r="CO23" s="7"/>
       <c r="CP23" s="7"/>
       <c r="CQ23" s="7"/>
       <c r="CR23" s="7"/>
@@ -7232,41 +7206,41 @@
       <c r="CY23" s="7"/>
       <c r="CZ23" s="7"/>
       <c r="DA23" s="7"/>
-      <c r="DB23" s="7"/>
-      <c r="DC23" s="23"/>
+      <c r="DB23" s="23"/>
+      <c r="DC23" s="7"/>
       <c r="DD23" s="7"/>
       <c r="DE23" s="7"/>
-      <c r="DF23" s="7"/>
+      <c r="DF23" s="20"/>
       <c r="DG23" s="20"/>
       <c r="DH23" s="20"/>
       <c r="DI23" s="20"/>
       <c r="DJ23" s="20"/>
-      <c r="DK23" s="20"/>
+      <c r="DK23" s="24"/>
       <c r="DL23" s="24"/>
       <c r="DM23" s="24"/>
-      <c r="DN23" s="24"/>
-      <c r="DO23" s="7"/>
-      <c r="DP23" s="20"/>
-      <c r="DQ23" s="23"/>
+      <c r="DN23" s="7"/>
+      <c r="DO23" s="20"/>
+      <c r="DP23" s="23"/>
+      <c r="DQ23" s="7"/>
       <c r="DR23" s="7"/>
       <c r="DS23" s="7"/>
-      <c r="DT23" s="7"/>
+      <c r="DT23" s="20"/>
       <c r="DU23" s="20"/>
       <c r="DV23" s="20"/>
       <c r="DW23" s="20"/>
-      <c r="DX23" s="20"/>
-      <c r="DY23" s="7"/>
-      <c r="DZ23" s="23"/>
-      <c r="EA23" s="20"/>
-      <c r="EB23" s="7"/>
-      <c r="EC23" s="23"/>
-      <c r="ED23" s="20"/>
+      <c r="DX23" s="7"/>
+      <c r="DY23" s="23"/>
+      <c r="DZ23" s="20"/>
+      <c r="EA23" s="7"/>
+      <c r="EB23" s="23"/>
+      <c r="EC23" s="20"/>
+      <c r="ED23" s="7"/>
       <c r="EE23" s="7"/>
       <c r="EF23" s="7"/>
-      <c r="EG23" s="7"/>
+      <c r="EG23" s="20"/>
       <c r="EH23" s="20"/>
       <c r="EI23" s="20"/>
-      <c r="EJ23" s="20"/>
+      <c r="EJ23" s="7"/>
       <c r="EK23" s="7"/>
       <c r="EL23" s="7"/>
       <c r="EM23" s="7"/>
@@ -7322,9 +7296,8 @@
       <c r="GK23" s="7"/>
       <c r="GL23" s="7"/>
       <c r="GM23" s="7"/>
-      <c r="GN23" s="7"/>
-    </row>
-    <row r="24" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -7365,7 +7338,7 @@
       <c r="AL24" s="20"/>
       <c r="AM24" s="20"/>
       <c r="AN24" s="20"/>
-      <c r="AO24" s="20"/>
+      <c r="AO24" s="7"/>
       <c r="AP24" s="7"/>
       <c r="AQ24" s="7"/>
       <c r="AR24" s="7"/>
@@ -7400,12 +7373,12 @@
       <c r="BU24" s="7"/>
       <c r="BV24" s="7"/>
       <c r="BW24" s="7"/>
-      <c r="BX24" s="7"/>
-      <c r="BY24" s="20"/>
-      <c r="BZ24" s="7"/>
-      <c r="CA24" s="20"/>
-      <c r="CB24" s="7"/>
-      <c r="CC24" s="20"/>
+      <c r="BX24" s="20"/>
+      <c r="BY24" s="7"/>
+      <c r="BZ24" s="20"/>
+      <c r="CA24" s="7"/>
+      <c r="CB24" s="20"/>
+      <c r="CC24" s="7"/>
       <c r="CD24" s="7"/>
       <c r="CE24" s="7"/>
       <c r="CF24" s="7"/>
@@ -7414,10 +7387,10 @@
       <c r="CI24" s="7"/>
       <c r="CJ24" s="7"/>
       <c r="CK24" s="7"/>
-      <c r="CL24" s="7"/>
+      <c r="CL24" s="21"/>
       <c r="CM24" s="21"/>
-      <c r="CN24" s="21"/>
-      <c r="CO24" s="22"/>
+      <c r="CN24" s="22"/>
+      <c r="CO24" s="7"/>
       <c r="CP24" s="7"/>
       <c r="CQ24" s="7"/>
       <c r="CR24" s="7"/>
@@ -7430,41 +7403,41 @@
       <c r="CY24" s="7"/>
       <c r="CZ24" s="7"/>
       <c r="DA24" s="7"/>
-      <c r="DB24" s="7"/>
-      <c r="DC24" s="23"/>
+      <c r="DB24" s="23"/>
+      <c r="DC24" s="7"/>
       <c r="DD24" s="7"/>
       <c r="DE24" s="7"/>
-      <c r="DF24" s="7"/>
+      <c r="DF24" s="20"/>
       <c r="DG24" s="20"/>
       <c r="DH24" s="20"/>
       <c r="DI24" s="20"/>
       <c r="DJ24" s="20"/>
-      <c r="DK24" s="20"/>
+      <c r="DK24" s="24"/>
       <c r="DL24" s="24"/>
       <c r="DM24" s="24"/>
-      <c r="DN24" s="24"/>
-      <c r="DO24" s="7"/>
-      <c r="DP24" s="20"/>
-      <c r="DQ24" s="23"/>
+      <c r="DN24" s="7"/>
+      <c r="DO24" s="20"/>
+      <c r="DP24" s="23"/>
+      <c r="DQ24" s="7"/>
       <c r="DR24" s="7"/>
       <c r="DS24" s="7"/>
-      <c r="DT24" s="7"/>
+      <c r="DT24" s="20"/>
       <c r="DU24" s="20"/>
       <c r="DV24" s="20"/>
       <c r="DW24" s="20"/>
-      <c r="DX24" s="20"/>
-      <c r="DY24" s="7"/>
-      <c r="DZ24" s="23"/>
-      <c r="EA24" s="20"/>
-      <c r="EB24" s="7"/>
-      <c r="EC24" s="23"/>
-      <c r="ED24" s="20"/>
+      <c r="DX24" s="7"/>
+      <c r="DY24" s="23"/>
+      <c r="DZ24" s="20"/>
+      <c r="EA24" s="7"/>
+      <c r="EB24" s="23"/>
+      <c r="EC24" s="20"/>
+      <c r="ED24" s="7"/>
       <c r="EE24" s="7"/>
       <c r="EF24" s="7"/>
-      <c r="EG24" s="7"/>
+      <c r="EG24" s="20"/>
       <c r="EH24" s="20"/>
       <c r="EI24" s="20"/>
-      <c r="EJ24" s="20"/>
+      <c r="EJ24" s="7"/>
       <c r="EK24" s="7"/>
       <c r="EL24" s="7"/>
       <c r="EM24" s="7"/>
@@ -7520,9 +7493,8 @@
       <c r="GK24" s="7"/>
       <c r="GL24" s="7"/>
       <c r="GM24" s="7"/>
-      <c r="GN24" s="7"/>
-    </row>
-    <row r="25" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -7563,7 +7535,7 @@
       <c r="AL25" s="20"/>
       <c r="AM25" s="20"/>
       <c r="AN25" s="20"/>
-      <c r="AO25" s="20"/>
+      <c r="AO25" s="7"/>
       <c r="AP25" s="7"/>
       <c r="AQ25" s="7"/>
       <c r="AR25" s="7"/>
@@ -7598,12 +7570,12 @@
       <c r="BU25" s="7"/>
       <c r="BV25" s="7"/>
       <c r="BW25" s="7"/>
-      <c r="BX25" s="7"/>
-      <c r="BY25" s="20"/>
-      <c r="BZ25" s="7"/>
-      <c r="CA25" s="20"/>
-      <c r="CB25" s="7"/>
-      <c r="CC25" s="20"/>
+      <c r="BX25" s="20"/>
+      <c r="BY25" s="7"/>
+      <c r="BZ25" s="20"/>
+      <c r="CA25" s="7"/>
+      <c r="CB25" s="20"/>
+      <c r="CC25" s="7"/>
       <c r="CD25" s="7"/>
       <c r="CE25" s="7"/>
       <c r="CF25" s="7"/>
@@ -7612,10 +7584,10 @@
       <c r="CI25" s="7"/>
       <c r="CJ25" s="7"/>
       <c r="CK25" s="7"/>
-      <c r="CL25" s="7"/>
+      <c r="CL25" s="21"/>
       <c r="CM25" s="21"/>
-      <c r="CN25" s="21"/>
-      <c r="CO25" s="22"/>
+      <c r="CN25" s="22"/>
+      <c r="CO25" s="7"/>
       <c r="CP25" s="7"/>
       <c r="CQ25" s="7"/>
       <c r="CR25" s="7"/>
@@ -7628,41 +7600,41 @@
       <c r="CY25" s="7"/>
       <c r="CZ25" s="7"/>
       <c r="DA25" s="7"/>
-      <c r="DB25" s="7"/>
-      <c r="DC25" s="23"/>
+      <c r="DB25" s="23"/>
+      <c r="DC25" s="7"/>
       <c r="DD25" s="7"/>
       <c r="DE25" s="7"/>
-      <c r="DF25" s="7"/>
+      <c r="DF25" s="20"/>
       <c r="DG25" s="20"/>
       <c r="DH25" s="20"/>
       <c r="DI25" s="20"/>
       <c r="DJ25" s="20"/>
-      <c r="DK25" s="20"/>
+      <c r="DK25" s="24"/>
       <c r="DL25" s="24"/>
       <c r="DM25" s="24"/>
-      <c r="DN25" s="24"/>
-      <c r="DO25" s="7"/>
-      <c r="DP25" s="20"/>
-      <c r="DQ25" s="23"/>
+      <c r="DN25" s="7"/>
+      <c r="DO25" s="20"/>
+      <c r="DP25" s="23"/>
+      <c r="DQ25" s="7"/>
       <c r="DR25" s="7"/>
       <c r="DS25" s="7"/>
-      <c r="DT25" s="7"/>
+      <c r="DT25" s="20"/>
       <c r="DU25" s="20"/>
       <c r="DV25" s="20"/>
       <c r="DW25" s="20"/>
-      <c r="DX25" s="20"/>
-      <c r="DY25" s="7"/>
-      <c r="DZ25" s="23"/>
-      <c r="EA25" s="20"/>
-      <c r="EB25" s="7"/>
-      <c r="EC25" s="23"/>
-      <c r="ED25" s="20"/>
+      <c r="DX25" s="7"/>
+      <c r="DY25" s="23"/>
+      <c r="DZ25" s="20"/>
+      <c r="EA25" s="7"/>
+      <c r="EB25" s="23"/>
+      <c r="EC25" s="20"/>
+      <c r="ED25" s="7"/>
       <c r="EE25" s="7"/>
       <c r="EF25" s="7"/>
-      <c r="EG25" s="7"/>
+      <c r="EG25" s="20"/>
       <c r="EH25" s="20"/>
       <c r="EI25" s="20"/>
-      <c r="EJ25" s="20"/>
+      <c r="EJ25" s="7"/>
       <c r="EK25" s="7"/>
       <c r="EL25" s="7"/>
       <c r="EM25" s="7"/>
@@ -7718,9 +7690,8 @@
       <c r="GK25" s="7"/>
       <c r="GL25" s="7"/>
       <c r="GM25" s="7"/>
-      <c r="GN25" s="7"/>
-    </row>
-    <row r="26" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -7761,7 +7732,7 @@
       <c r="AL26" s="20"/>
       <c r="AM26" s="20"/>
       <c r="AN26" s="20"/>
-      <c r="AO26" s="20"/>
+      <c r="AO26" s="7"/>
       <c r="AP26" s="7"/>
       <c r="AQ26" s="7"/>
       <c r="AR26" s="7"/>
@@ -7796,12 +7767,12 @@
       <c r="BU26" s="7"/>
       <c r="BV26" s="7"/>
       <c r="BW26" s="7"/>
-      <c r="BX26" s="7"/>
-      <c r="BY26" s="20"/>
-      <c r="BZ26" s="7"/>
-      <c r="CA26" s="20"/>
-      <c r="CB26" s="7"/>
-      <c r="CC26" s="20"/>
+      <c r="BX26" s="20"/>
+      <c r="BY26" s="7"/>
+      <c r="BZ26" s="20"/>
+      <c r="CA26" s="7"/>
+      <c r="CB26" s="20"/>
+      <c r="CC26" s="7"/>
       <c r="CD26" s="7"/>
       <c r="CE26" s="7"/>
       <c r="CF26" s="7"/>
@@ -7810,10 +7781,10 @@
       <c r="CI26" s="7"/>
       <c r="CJ26" s="7"/>
       <c r="CK26" s="7"/>
-      <c r="CL26" s="7"/>
+      <c r="CL26" s="21"/>
       <c r="CM26" s="21"/>
-      <c r="CN26" s="21"/>
-      <c r="CO26" s="22"/>
+      <c r="CN26" s="22"/>
+      <c r="CO26" s="7"/>
       <c r="CP26" s="7"/>
       <c r="CQ26" s="7"/>
       <c r="CR26" s="7"/>
@@ -7826,41 +7797,41 @@
       <c r="CY26" s="7"/>
       <c r="CZ26" s="7"/>
       <c r="DA26" s="7"/>
-      <c r="DB26" s="7"/>
-      <c r="DC26" s="23"/>
+      <c r="DB26" s="23"/>
+      <c r="DC26" s="7"/>
       <c r="DD26" s="7"/>
       <c r="DE26" s="7"/>
-      <c r="DF26" s="7"/>
+      <c r="DF26" s="20"/>
       <c r="DG26" s="20"/>
       <c r="DH26" s="20"/>
       <c r="DI26" s="20"/>
       <c r="DJ26" s="20"/>
-      <c r="DK26" s="20"/>
+      <c r="DK26" s="24"/>
       <c r="DL26" s="24"/>
       <c r="DM26" s="24"/>
-      <c r="DN26" s="24"/>
-      <c r="DO26" s="7"/>
-      <c r="DP26" s="20"/>
-      <c r="DQ26" s="23"/>
+      <c r="DN26" s="7"/>
+      <c r="DO26" s="20"/>
+      <c r="DP26" s="23"/>
+      <c r="DQ26" s="7"/>
       <c r="DR26" s="7"/>
       <c r="DS26" s="7"/>
-      <c r="DT26" s="7"/>
+      <c r="DT26" s="20"/>
       <c r="DU26" s="20"/>
       <c r="DV26" s="20"/>
       <c r="DW26" s="20"/>
-      <c r="DX26" s="20"/>
-      <c r="DY26" s="7"/>
-      <c r="DZ26" s="23"/>
-      <c r="EA26" s="20"/>
-      <c r="EB26" s="7"/>
-      <c r="EC26" s="23"/>
-      <c r="ED26" s="20"/>
+      <c r="DX26" s="7"/>
+      <c r="DY26" s="23"/>
+      <c r="DZ26" s="20"/>
+      <c r="EA26" s="7"/>
+      <c r="EB26" s="23"/>
+      <c r="EC26" s="20"/>
+      <c r="ED26" s="7"/>
       <c r="EE26" s="7"/>
       <c r="EF26" s="7"/>
-      <c r="EG26" s="7"/>
+      <c r="EG26" s="20"/>
       <c r="EH26" s="20"/>
       <c r="EI26" s="20"/>
-      <c r="EJ26" s="20"/>
+      <c r="EJ26" s="7"/>
       <c r="EK26" s="7"/>
       <c r="EL26" s="7"/>
       <c r="EM26" s="7"/>
@@ -7916,9 +7887,8 @@
       <c r="GK26" s="7"/>
       <c r="GL26" s="7"/>
       <c r="GM26" s="7"/>
-      <c r="GN26" s="7"/>
-    </row>
-    <row r="27" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -7959,7 +7929,7 @@
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
       <c r="AN27" s="20"/>
-      <c r="AO27" s="20"/>
+      <c r="AO27" s="7"/>
       <c r="AP27" s="7"/>
       <c r="AQ27" s="7"/>
       <c r="AR27" s="7"/>
@@ -7994,12 +7964,12 @@
       <c r="BU27" s="7"/>
       <c r="BV27" s="7"/>
       <c r="BW27" s="7"/>
-      <c r="BX27" s="7"/>
-      <c r="BY27" s="20"/>
-      <c r="BZ27" s="7"/>
-      <c r="CA27" s="20"/>
-      <c r="CB27" s="7"/>
-      <c r="CC27" s="20"/>
+      <c r="BX27" s="20"/>
+      <c r="BY27" s="7"/>
+      <c r="BZ27" s="20"/>
+      <c r="CA27" s="7"/>
+      <c r="CB27" s="20"/>
+      <c r="CC27" s="7"/>
       <c r="CD27" s="7"/>
       <c r="CE27" s="7"/>
       <c r="CF27" s="7"/>
@@ -8008,10 +7978,10 @@
       <c r="CI27" s="7"/>
       <c r="CJ27" s="7"/>
       <c r="CK27" s="7"/>
-      <c r="CL27" s="7"/>
+      <c r="CL27" s="21"/>
       <c r="CM27" s="21"/>
-      <c r="CN27" s="21"/>
-      <c r="CO27" s="22"/>
+      <c r="CN27" s="22"/>
+      <c r="CO27" s="7"/>
       <c r="CP27" s="7"/>
       <c r="CQ27" s="7"/>
       <c r="CR27" s="7"/>
@@ -8024,41 +7994,41 @@
       <c r="CY27" s="7"/>
       <c r="CZ27" s="7"/>
       <c r="DA27" s="7"/>
-      <c r="DB27" s="7"/>
-      <c r="DC27" s="23"/>
+      <c r="DB27" s="23"/>
+      <c r="DC27" s="7"/>
       <c r="DD27" s="7"/>
       <c r="DE27" s="7"/>
-      <c r="DF27" s="7"/>
+      <c r="DF27" s="20"/>
       <c r="DG27" s="20"/>
       <c r="DH27" s="20"/>
       <c r="DI27" s="20"/>
       <c r="DJ27" s="20"/>
-      <c r="DK27" s="20"/>
+      <c r="DK27" s="24"/>
       <c r="DL27" s="24"/>
       <c r="DM27" s="24"/>
-      <c r="DN27" s="24"/>
-      <c r="DO27" s="7"/>
-      <c r="DP27" s="20"/>
-      <c r="DQ27" s="23"/>
+      <c r="DN27" s="7"/>
+      <c r="DO27" s="20"/>
+      <c r="DP27" s="23"/>
+      <c r="DQ27" s="7"/>
       <c r="DR27" s="7"/>
       <c r="DS27" s="7"/>
-      <c r="DT27" s="7"/>
+      <c r="DT27" s="20"/>
       <c r="DU27" s="20"/>
       <c r="DV27" s="20"/>
       <c r="DW27" s="20"/>
-      <c r="DX27" s="20"/>
-      <c r="DY27" s="7"/>
-      <c r="DZ27" s="23"/>
-      <c r="EA27" s="20"/>
-      <c r="EB27" s="7"/>
-      <c r="EC27" s="23"/>
-      <c r="ED27" s="20"/>
+      <c r="DX27" s="7"/>
+      <c r="DY27" s="23"/>
+      <c r="DZ27" s="20"/>
+      <c r="EA27" s="7"/>
+      <c r="EB27" s="23"/>
+      <c r="EC27" s="20"/>
+      <c r="ED27" s="7"/>
       <c r="EE27" s="7"/>
       <c r="EF27" s="7"/>
-      <c r="EG27" s="7"/>
+      <c r="EG27" s="20"/>
       <c r="EH27" s="20"/>
       <c r="EI27" s="20"/>
-      <c r="EJ27" s="20"/>
+      <c r="EJ27" s="7"/>
       <c r="EK27" s="7"/>
       <c r="EL27" s="7"/>
       <c r="EM27" s="7"/>
@@ -8114,9 +8084,8 @@
       <c r="GK27" s="7"/>
       <c r="GL27" s="7"/>
       <c r="GM27" s="7"/>
-      <c r="GN27" s="7"/>
-    </row>
-    <row r="28" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -8157,7 +8126,7 @@
       <c r="AL28" s="20"/>
       <c r="AM28" s="20"/>
       <c r="AN28" s="20"/>
-      <c r="AO28" s="20"/>
+      <c r="AO28" s="7"/>
       <c r="AP28" s="7"/>
       <c r="AQ28" s="7"/>
       <c r="AR28" s="7"/>
@@ -8192,12 +8161,12 @@
       <c r="BU28" s="7"/>
       <c r="BV28" s="7"/>
       <c r="BW28" s="7"/>
-      <c r="BX28" s="7"/>
-      <c r="BY28" s="20"/>
-      <c r="BZ28" s="7"/>
-      <c r="CA28" s="20"/>
-      <c r="CB28" s="7"/>
-      <c r="CC28" s="20"/>
+      <c r="BX28" s="20"/>
+      <c r="BY28" s="7"/>
+      <c r="BZ28" s="20"/>
+      <c r="CA28" s="7"/>
+      <c r="CB28" s="20"/>
+      <c r="CC28" s="7"/>
       <c r="CD28" s="7"/>
       <c r="CE28" s="7"/>
       <c r="CF28" s="7"/>
@@ -8206,10 +8175,10 @@
       <c r="CI28" s="7"/>
       <c r="CJ28" s="7"/>
       <c r="CK28" s="7"/>
-      <c r="CL28" s="7"/>
+      <c r="CL28" s="21"/>
       <c r="CM28" s="21"/>
-      <c r="CN28" s="21"/>
-      <c r="CO28" s="22"/>
+      <c r="CN28" s="22"/>
+      <c r="CO28" s="7"/>
       <c r="CP28" s="7"/>
       <c r="CQ28" s="7"/>
       <c r="CR28" s="7"/>
@@ -8222,41 +8191,41 @@
       <c r="CY28" s="7"/>
       <c r="CZ28" s="7"/>
       <c r="DA28" s="7"/>
-      <c r="DB28" s="7"/>
-      <c r="DC28" s="23"/>
+      <c r="DB28" s="23"/>
+      <c r="DC28" s="7"/>
       <c r="DD28" s="7"/>
       <c r="DE28" s="7"/>
-      <c r="DF28" s="7"/>
+      <c r="DF28" s="20"/>
       <c r="DG28" s="20"/>
       <c r="DH28" s="20"/>
       <c r="DI28" s="20"/>
       <c r="DJ28" s="20"/>
-      <c r="DK28" s="20"/>
+      <c r="DK28" s="24"/>
       <c r="DL28" s="24"/>
       <c r="DM28" s="24"/>
-      <c r="DN28" s="24"/>
-      <c r="DO28" s="7"/>
-      <c r="DP28" s="20"/>
-      <c r="DQ28" s="23"/>
+      <c r="DN28" s="7"/>
+      <c r="DO28" s="20"/>
+      <c r="DP28" s="23"/>
+      <c r="DQ28" s="7"/>
       <c r="DR28" s="7"/>
       <c r="DS28" s="7"/>
-      <c r="DT28" s="7"/>
+      <c r="DT28" s="20"/>
       <c r="DU28" s="20"/>
       <c r="DV28" s="20"/>
       <c r="DW28" s="20"/>
-      <c r="DX28" s="20"/>
-      <c r="DY28" s="7"/>
-      <c r="DZ28" s="23"/>
-      <c r="EA28" s="20"/>
-      <c r="EB28" s="7"/>
-      <c r="EC28" s="23"/>
-      <c r="ED28" s="20"/>
+      <c r="DX28" s="7"/>
+      <c r="DY28" s="23"/>
+      <c r="DZ28" s="20"/>
+      <c r="EA28" s="7"/>
+      <c r="EB28" s="23"/>
+      <c r="EC28" s="20"/>
+      <c r="ED28" s="7"/>
       <c r="EE28" s="7"/>
       <c r="EF28" s="7"/>
-      <c r="EG28" s="7"/>
+      <c r="EG28" s="20"/>
       <c r="EH28" s="20"/>
       <c r="EI28" s="20"/>
-      <c r="EJ28" s="20"/>
+      <c r="EJ28" s="7"/>
       <c r="EK28" s="7"/>
       <c r="EL28" s="7"/>
       <c r="EM28" s="7"/>
@@ -8312,9 +8281,8 @@
       <c r="GK28" s="7"/>
       <c r="GL28" s="7"/>
       <c r="GM28" s="7"/>
-      <c r="GN28" s="7"/>
-    </row>
-    <row r="29" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -8355,7 +8323,7 @@
       <c r="AL29" s="20"/>
       <c r="AM29" s="20"/>
       <c r="AN29" s="20"/>
-      <c r="AO29" s="20"/>
+      <c r="AO29" s="7"/>
       <c r="AP29" s="7"/>
       <c r="AQ29" s="7"/>
       <c r="AR29" s="7"/>
@@ -8390,12 +8358,12 @@
       <c r="BU29" s="7"/>
       <c r="BV29" s="7"/>
       <c r="BW29" s="7"/>
-      <c r="BX29" s="7"/>
-      <c r="BY29" s="20"/>
-      <c r="BZ29" s="7"/>
-      <c r="CA29" s="20"/>
-      <c r="CB29" s="7"/>
-      <c r="CC29" s="20"/>
+      <c r="BX29" s="20"/>
+      <c r="BY29" s="7"/>
+      <c r="BZ29" s="20"/>
+      <c r="CA29" s="7"/>
+      <c r="CB29" s="20"/>
+      <c r="CC29" s="7"/>
       <c r="CD29" s="7"/>
       <c r="CE29" s="7"/>
       <c r="CF29" s="7"/>
@@ -8404,10 +8372,10 @@
       <c r="CI29" s="7"/>
       <c r="CJ29" s="7"/>
       <c r="CK29" s="7"/>
-      <c r="CL29" s="7"/>
+      <c r="CL29" s="21"/>
       <c r="CM29" s="21"/>
-      <c r="CN29" s="21"/>
-      <c r="CO29" s="22"/>
+      <c r="CN29" s="22"/>
+      <c r="CO29" s="7"/>
       <c r="CP29" s="7"/>
       <c r="CQ29" s="7"/>
       <c r="CR29" s="7"/>
@@ -8420,41 +8388,41 @@
       <c r="CY29" s="7"/>
       <c r="CZ29" s="7"/>
       <c r="DA29" s="7"/>
-      <c r="DB29" s="7"/>
-      <c r="DC29" s="23"/>
+      <c r="DB29" s="23"/>
+      <c r="DC29" s="7"/>
       <c r="DD29" s="7"/>
       <c r="DE29" s="7"/>
-      <c r="DF29" s="7"/>
+      <c r="DF29" s="20"/>
       <c r="DG29" s="20"/>
       <c r="DH29" s="20"/>
       <c r="DI29" s="20"/>
       <c r="DJ29" s="20"/>
-      <c r="DK29" s="20"/>
+      <c r="DK29" s="24"/>
       <c r="DL29" s="24"/>
       <c r="DM29" s="24"/>
-      <c r="DN29" s="24"/>
-      <c r="DO29" s="7"/>
-      <c r="DP29" s="20"/>
-      <c r="DQ29" s="23"/>
+      <c r="DN29" s="7"/>
+      <c r="DO29" s="20"/>
+      <c r="DP29" s="23"/>
+      <c r="DQ29" s="7"/>
       <c r="DR29" s="7"/>
       <c r="DS29" s="7"/>
-      <c r="DT29" s="7"/>
+      <c r="DT29" s="20"/>
       <c r="DU29" s="20"/>
       <c r="DV29" s="20"/>
       <c r="DW29" s="20"/>
-      <c r="DX29" s="20"/>
-      <c r="DY29" s="7"/>
-      <c r="DZ29" s="23"/>
-      <c r="EA29" s="20"/>
-      <c r="EB29" s="7"/>
-      <c r="EC29" s="23"/>
-      <c r="ED29" s="20"/>
+      <c r="DX29" s="7"/>
+      <c r="DY29" s="23"/>
+      <c r="DZ29" s="20"/>
+      <c r="EA29" s="7"/>
+      <c r="EB29" s="23"/>
+      <c r="EC29" s="20"/>
+      <c r="ED29" s="7"/>
       <c r="EE29" s="7"/>
       <c r="EF29" s="7"/>
-      <c r="EG29" s="7"/>
+      <c r="EG29" s="20"/>
       <c r="EH29" s="20"/>
       <c r="EI29" s="20"/>
-      <c r="EJ29" s="20"/>
+      <c r="EJ29" s="7"/>
       <c r="EK29" s="7"/>
       <c r="EL29" s="7"/>
       <c r="EM29" s="7"/>
@@ -8510,9 +8478,8 @@
       <c r="GK29" s="7"/>
       <c r="GL29" s="7"/>
       <c r="GM29" s="7"/>
-      <c r="GN29" s="7"/>
-    </row>
-    <row r="30" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -8553,7 +8520,7 @@
       <c r="AL30" s="20"/>
       <c r="AM30" s="20"/>
       <c r="AN30" s="20"/>
-      <c r="AO30" s="20"/>
+      <c r="AO30" s="7"/>
       <c r="AP30" s="7"/>
       <c r="AQ30" s="7"/>
       <c r="AR30" s="7"/>
@@ -8588,12 +8555,12 @@
       <c r="BU30" s="7"/>
       <c r="BV30" s="7"/>
       <c r="BW30" s="7"/>
-      <c r="BX30" s="7"/>
-      <c r="BY30" s="20"/>
-      <c r="BZ30" s="7"/>
-      <c r="CA30" s="20"/>
-      <c r="CB30" s="7"/>
-      <c r="CC30" s="20"/>
+      <c r="BX30" s="20"/>
+      <c r="BY30" s="7"/>
+      <c r="BZ30" s="20"/>
+      <c r="CA30" s="7"/>
+      <c r="CB30" s="20"/>
+      <c r="CC30" s="7"/>
       <c r="CD30" s="7"/>
       <c r="CE30" s="7"/>
       <c r="CF30" s="7"/>
@@ -8602,10 +8569,10 @@
       <c r="CI30" s="7"/>
       <c r="CJ30" s="7"/>
       <c r="CK30" s="7"/>
-      <c r="CL30" s="7"/>
+      <c r="CL30" s="21"/>
       <c r="CM30" s="21"/>
-      <c r="CN30" s="21"/>
-      <c r="CO30" s="22"/>
+      <c r="CN30" s="22"/>
+      <c r="CO30" s="7"/>
       <c r="CP30" s="7"/>
       <c r="CQ30" s="7"/>
       <c r="CR30" s="7"/>
@@ -8618,41 +8585,41 @@
       <c r="CY30" s="7"/>
       <c r="CZ30" s="7"/>
       <c r="DA30" s="7"/>
-      <c r="DB30" s="7"/>
-      <c r="DC30" s="23"/>
+      <c r="DB30" s="23"/>
+      <c r="DC30" s="7"/>
       <c r="DD30" s="7"/>
       <c r="DE30" s="7"/>
-      <c r="DF30" s="7"/>
+      <c r="DF30" s="20"/>
       <c r="DG30" s="20"/>
       <c r="DH30" s="20"/>
       <c r="DI30" s="20"/>
       <c r="DJ30" s="20"/>
-      <c r="DK30" s="20"/>
+      <c r="DK30" s="24"/>
       <c r="DL30" s="24"/>
       <c r="DM30" s="24"/>
-      <c r="DN30" s="24"/>
-      <c r="DO30" s="7"/>
-      <c r="DP30" s="20"/>
-      <c r="DQ30" s="23"/>
+      <c r="DN30" s="7"/>
+      <c r="DO30" s="20"/>
+      <c r="DP30" s="23"/>
+      <c r="DQ30" s="7"/>
       <c r="DR30" s="7"/>
       <c r="DS30" s="7"/>
-      <c r="DT30" s="7"/>
+      <c r="DT30" s="20"/>
       <c r="DU30" s="20"/>
       <c r="DV30" s="20"/>
       <c r="DW30" s="20"/>
-      <c r="DX30" s="20"/>
-      <c r="DY30" s="7"/>
-      <c r="DZ30" s="23"/>
-      <c r="EA30" s="20"/>
-      <c r="EB30" s="7"/>
-      <c r="EC30" s="23"/>
-      <c r="ED30" s="20"/>
+      <c r="DX30" s="7"/>
+      <c r="DY30" s="23"/>
+      <c r="DZ30" s="20"/>
+      <c r="EA30" s="7"/>
+      <c r="EB30" s="23"/>
+      <c r="EC30" s="20"/>
+      <c r="ED30" s="7"/>
       <c r="EE30" s="7"/>
       <c r="EF30" s="7"/>
-      <c r="EG30" s="7"/>
+      <c r="EG30" s="20"/>
       <c r="EH30" s="20"/>
       <c r="EI30" s="20"/>
-      <c r="EJ30" s="20"/>
+      <c r="EJ30" s="7"/>
       <c r="EK30" s="7"/>
       <c r="EL30" s="7"/>
       <c r="EM30" s="7"/>
@@ -8708,9 +8675,8 @@
       <c r="GK30" s="7"/>
       <c r="GL30" s="7"/>
       <c r="GM30" s="7"/>
-      <c r="GN30" s="7"/>
-    </row>
-    <row r="31" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -8751,7 +8717,7 @@
       <c r="AL31" s="20"/>
       <c r="AM31" s="20"/>
       <c r="AN31" s="20"/>
-      <c r="AO31" s="20"/>
+      <c r="AO31" s="7"/>
       <c r="AP31" s="7"/>
       <c r="AQ31" s="7"/>
       <c r="AR31" s="7"/>
@@ -8786,12 +8752,12 @@
       <c r="BU31" s="7"/>
       <c r="BV31" s="7"/>
       <c r="BW31" s="7"/>
-      <c r="BX31" s="7"/>
-      <c r="BY31" s="20"/>
-      <c r="BZ31" s="7"/>
-      <c r="CA31" s="20"/>
-      <c r="CB31" s="7"/>
-      <c r="CC31" s="20"/>
+      <c r="BX31" s="20"/>
+      <c r="BY31" s="7"/>
+      <c r="BZ31" s="20"/>
+      <c r="CA31" s="7"/>
+      <c r="CB31" s="20"/>
+      <c r="CC31" s="7"/>
       <c r="CD31" s="7"/>
       <c r="CE31" s="7"/>
       <c r="CF31" s="7"/>
@@ -8800,10 +8766,10 @@
       <c r="CI31" s="7"/>
       <c r="CJ31" s="7"/>
       <c r="CK31" s="7"/>
-      <c r="CL31" s="7"/>
+      <c r="CL31" s="21"/>
       <c r="CM31" s="21"/>
-      <c r="CN31" s="21"/>
-      <c r="CO31" s="22"/>
+      <c r="CN31" s="22"/>
+      <c r="CO31" s="7"/>
       <c r="CP31" s="7"/>
       <c r="CQ31" s="7"/>
       <c r="CR31" s="7"/>
@@ -8816,41 +8782,41 @@
       <c r="CY31" s="7"/>
       <c r="CZ31" s="7"/>
       <c r="DA31" s="7"/>
-      <c r="DB31" s="7"/>
-      <c r="DC31" s="23"/>
+      <c r="DB31" s="23"/>
+      <c r="DC31" s="7"/>
       <c r="DD31" s="7"/>
       <c r="DE31" s="7"/>
-      <c r="DF31" s="7"/>
+      <c r="DF31" s="20"/>
       <c r="DG31" s="20"/>
       <c r="DH31" s="20"/>
       <c r="DI31" s="20"/>
       <c r="DJ31" s="20"/>
-      <c r="DK31" s="20"/>
+      <c r="DK31" s="24"/>
       <c r="DL31" s="24"/>
       <c r="DM31" s="24"/>
-      <c r="DN31" s="24"/>
-      <c r="DO31" s="7"/>
-      <c r="DP31" s="20"/>
-      <c r="DQ31" s="23"/>
+      <c r="DN31" s="7"/>
+      <c r="DO31" s="20"/>
+      <c r="DP31" s="23"/>
+      <c r="DQ31" s="7"/>
       <c r="DR31" s="7"/>
       <c r="DS31" s="7"/>
-      <c r="DT31" s="7"/>
+      <c r="DT31" s="20"/>
       <c r="DU31" s="20"/>
       <c r="DV31" s="20"/>
       <c r="DW31" s="20"/>
-      <c r="DX31" s="20"/>
-      <c r="DY31" s="7"/>
-      <c r="DZ31" s="23"/>
-      <c r="EA31" s="20"/>
-      <c r="EB31" s="7"/>
-      <c r="EC31" s="23"/>
-      <c r="ED31" s="20"/>
+      <c r="DX31" s="7"/>
+      <c r="DY31" s="23"/>
+      <c r="DZ31" s="20"/>
+      <c r="EA31" s="7"/>
+      <c r="EB31" s="23"/>
+      <c r="EC31" s="20"/>
+      <c r="ED31" s="7"/>
       <c r="EE31" s="7"/>
       <c r="EF31" s="7"/>
-      <c r="EG31" s="7"/>
+      <c r="EG31" s="20"/>
       <c r="EH31" s="20"/>
       <c r="EI31" s="20"/>
-      <c r="EJ31" s="20"/>
+      <c r="EJ31" s="7"/>
       <c r="EK31" s="7"/>
       <c r="EL31" s="7"/>
       <c r="EM31" s="7"/>
@@ -8906,9 +8872,8 @@
       <c r="GK31" s="7"/>
       <c r="GL31" s="7"/>
       <c r="GM31" s="7"/>
-      <c r="GN31" s="7"/>
-    </row>
-    <row r="32" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -8949,7 +8914,7 @@
       <c r="AL32" s="20"/>
       <c r="AM32" s="20"/>
       <c r="AN32" s="20"/>
-      <c r="AO32" s="20"/>
+      <c r="AO32" s="7"/>
       <c r="AP32" s="7"/>
       <c r="AQ32" s="7"/>
       <c r="AR32" s="7"/>
@@ -8984,12 +8949,12 @@
       <c r="BU32" s="7"/>
       <c r="BV32" s="7"/>
       <c r="BW32" s="7"/>
-      <c r="BX32" s="7"/>
-      <c r="BY32" s="20"/>
-      <c r="BZ32" s="7"/>
-      <c r="CA32" s="20"/>
-      <c r="CB32" s="7"/>
-      <c r="CC32" s="20"/>
+      <c r="BX32" s="20"/>
+      <c r="BY32" s="7"/>
+      <c r="BZ32" s="20"/>
+      <c r="CA32" s="7"/>
+      <c r="CB32" s="20"/>
+      <c r="CC32" s="7"/>
       <c r="CD32" s="7"/>
       <c r="CE32" s="7"/>
       <c r="CF32" s="7"/>
@@ -8998,10 +8963,10 @@
       <c r="CI32" s="7"/>
       <c r="CJ32" s="7"/>
       <c r="CK32" s="7"/>
-      <c r="CL32" s="7"/>
+      <c r="CL32" s="21"/>
       <c r="CM32" s="21"/>
-      <c r="CN32" s="21"/>
-      <c r="CO32" s="22"/>
+      <c r="CN32" s="22"/>
+      <c r="CO32" s="7"/>
       <c r="CP32" s="7"/>
       <c r="CQ32" s="7"/>
       <c r="CR32" s="7"/>
@@ -9014,41 +8979,41 @@
       <c r="CY32" s="7"/>
       <c r="CZ32" s="7"/>
       <c r="DA32" s="7"/>
-      <c r="DB32" s="7"/>
-      <c r="DC32" s="23"/>
+      <c r="DB32" s="23"/>
+      <c r="DC32" s="7"/>
       <c r="DD32" s="7"/>
       <c r="DE32" s="7"/>
-      <c r="DF32" s="7"/>
+      <c r="DF32" s="20"/>
       <c r="DG32" s="20"/>
       <c r="DH32" s="20"/>
       <c r="DI32" s="20"/>
       <c r="DJ32" s="20"/>
-      <c r="DK32" s="20"/>
+      <c r="DK32" s="24"/>
       <c r="DL32" s="24"/>
       <c r="DM32" s="24"/>
-      <c r="DN32" s="24"/>
-      <c r="DO32" s="7"/>
-      <c r="DP32" s="20"/>
-      <c r="DQ32" s="23"/>
+      <c r="DN32" s="7"/>
+      <c r="DO32" s="20"/>
+      <c r="DP32" s="23"/>
+      <c r="DQ32" s="7"/>
       <c r="DR32" s="7"/>
       <c r="DS32" s="7"/>
-      <c r="DT32" s="7"/>
+      <c r="DT32" s="20"/>
       <c r="DU32" s="20"/>
       <c r="DV32" s="20"/>
       <c r="DW32" s="20"/>
-      <c r="DX32" s="20"/>
-      <c r="DY32" s="7"/>
-      <c r="DZ32" s="23"/>
-      <c r="EA32" s="20"/>
-      <c r="EB32" s="7"/>
-      <c r="EC32" s="23"/>
-      <c r="ED32" s="20"/>
+      <c r="DX32" s="7"/>
+      <c r="DY32" s="23"/>
+      <c r="DZ32" s="20"/>
+      <c r="EA32" s="7"/>
+      <c r="EB32" s="23"/>
+      <c r="EC32" s="20"/>
+      <c r="ED32" s="7"/>
       <c r="EE32" s="7"/>
       <c r="EF32" s="7"/>
-      <c r="EG32" s="7"/>
+      <c r="EG32" s="20"/>
       <c r="EH32" s="20"/>
       <c r="EI32" s="20"/>
-      <c r="EJ32" s="20"/>
+      <c r="EJ32" s="7"/>
       <c r="EK32" s="7"/>
       <c r="EL32" s="7"/>
       <c r="EM32" s="7"/>
@@ -9104,9 +9069,8 @@
       <c r="GK32" s="7"/>
       <c r="GL32" s="7"/>
       <c r="GM32" s="7"/>
-      <c r="GN32" s="7"/>
-    </row>
-    <row r="33" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -9147,7 +9111,7 @@
       <c r="AL33" s="20"/>
       <c r="AM33" s="20"/>
       <c r="AN33" s="20"/>
-      <c r="AO33" s="20"/>
+      <c r="AO33" s="7"/>
       <c r="AP33" s="7"/>
       <c r="AQ33" s="7"/>
       <c r="AR33" s="7"/>
@@ -9182,12 +9146,12 @@
       <c r="BU33" s="7"/>
       <c r="BV33" s="7"/>
       <c r="BW33" s="7"/>
-      <c r="BX33" s="7"/>
-      <c r="BY33" s="20"/>
-      <c r="BZ33" s="7"/>
-      <c r="CA33" s="20"/>
-      <c r="CB33" s="7"/>
-      <c r="CC33" s="20"/>
+      <c r="BX33" s="20"/>
+      <c r="BY33" s="7"/>
+      <c r="BZ33" s="20"/>
+      <c r="CA33" s="7"/>
+      <c r="CB33" s="20"/>
+      <c r="CC33" s="7"/>
       <c r="CD33" s="7"/>
       <c r="CE33" s="7"/>
       <c r="CF33" s="7"/>
@@ -9196,10 +9160,10 @@
       <c r="CI33" s="7"/>
       <c r="CJ33" s="7"/>
       <c r="CK33" s="7"/>
-      <c r="CL33" s="7"/>
+      <c r="CL33" s="21"/>
       <c r="CM33" s="21"/>
-      <c r="CN33" s="21"/>
-      <c r="CO33" s="22"/>
+      <c r="CN33" s="22"/>
+      <c r="CO33" s="7"/>
       <c r="CP33" s="7"/>
       <c r="CQ33" s="7"/>
       <c r="CR33" s="7"/>
@@ -9212,41 +9176,41 @@
       <c r="CY33" s="7"/>
       <c r="CZ33" s="7"/>
       <c r="DA33" s="7"/>
-      <c r="DB33" s="7"/>
-      <c r="DC33" s="23"/>
+      <c r="DB33" s="23"/>
+      <c r="DC33" s="7"/>
       <c r="DD33" s="7"/>
       <c r="DE33" s="7"/>
-      <c r="DF33" s="7"/>
+      <c r="DF33" s="20"/>
       <c r="DG33" s="20"/>
       <c r="DH33" s="20"/>
       <c r="DI33" s="20"/>
       <c r="DJ33" s="20"/>
-      <c r="DK33" s="20"/>
+      <c r="DK33" s="24"/>
       <c r="DL33" s="24"/>
       <c r="DM33" s="24"/>
-      <c r="DN33" s="24"/>
-      <c r="DO33" s="7"/>
-      <c r="DP33" s="20"/>
-      <c r="DQ33" s="23"/>
+      <c r="DN33" s="7"/>
+      <c r="DO33" s="20"/>
+      <c r="DP33" s="23"/>
+      <c r="DQ33" s="7"/>
       <c r="DR33" s="7"/>
       <c r="DS33" s="7"/>
-      <c r="DT33" s="7"/>
+      <c r="DT33" s="20"/>
       <c r="DU33" s="20"/>
       <c r="DV33" s="20"/>
       <c r="DW33" s="20"/>
-      <c r="DX33" s="20"/>
-      <c r="DY33" s="7"/>
-      <c r="DZ33" s="23"/>
-      <c r="EA33" s="20"/>
-      <c r="EB33" s="7"/>
-      <c r="EC33" s="23"/>
-      <c r="ED33" s="20"/>
+      <c r="DX33" s="7"/>
+      <c r="DY33" s="23"/>
+      <c r="DZ33" s="20"/>
+      <c r="EA33" s="7"/>
+      <c r="EB33" s="23"/>
+      <c r="EC33" s="20"/>
+      <c r="ED33" s="7"/>
       <c r="EE33" s="7"/>
       <c r="EF33" s="7"/>
-      <c r="EG33" s="7"/>
+      <c r="EG33" s="20"/>
       <c r="EH33" s="20"/>
       <c r="EI33" s="20"/>
-      <c r="EJ33" s="20"/>
+      <c r="EJ33" s="7"/>
       <c r="EK33" s="7"/>
       <c r="EL33" s="7"/>
       <c r="EM33" s="7"/>
@@ -9302,9 +9266,8 @@
       <c r="GK33" s="7"/>
       <c r="GL33" s="7"/>
       <c r="GM33" s="7"/>
-      <c r="GN33" s="7"/>
-    </row>
-    <row r="34" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -9345,7 +9308,7 @@
       <c r="AL34" s="20"/>
       <c r="AM34" s="20"/>
       <c r="AN34" s="20"/>
-      <c r="AO34" s="20"/>
+      <c r="AO34" s="7"/>
       <c r="AP34" s="7"/>
       <c r="AQ34" s="7"/>
       <c r="AR34" s="7"/>
@@ -9380,12 +9343,12 @@
       <c r="BU34" s="7"/>
       <c r="BV34" s="7"/>
       <c r="BW34" s="7"/>
-      <c r="BX34" s="7"/>
-      <c r="BY34" s="20"/>
-      <c r="BZ34" s="7"/>
-      <c r="CA34" s="20"/>
-      <c r="CB34" s="7"/>
-      <c r="CC34" s="20"/>
+      <c r="BX34" s="20"/>
+      <c r="BY34" s="7"/>
+      <c r="BZ34" s="20"/>
+      <c r="CA34" s="7"/>
+      <c r="CB34" s="20"/>
+      <c r="CC34" s="7"/>
       <c r="CD34" s="7"/>
       <c r="CE34" s="7"/>
       <c r="CF34" s="7"/>
@@ -9394,10 +9357,10 @@
       <c r="CI34" s="7"/>
       <c r="CJ34" s="7"/>
       <c r="CK34" s="7"/>
-      <c r="CL34" s="7"/>
+      <c r="CL34" s="21"/>
       <c r="CM34" s="21"/>
-      <c r="CN34" s="21"/>
-      <c r="CO34" s="22"/>
+      <c r="CN34" s="22"/>
+      <c r="CO34" s="7"/>
       <c r="CP34" s="7"/>
       <c r="CQ34" s="7"/>
       <c r="CR34" s="7"/>
@@ -9410,41 +9373,41 @@
       <c r="CY34" s="7"/>
       <c r="CZ34" s="7"/>
       <c r="DA34" s="7"/>
-      <c r="DB34" s="7"/>
-      <c r="DC34" s="23"/>
+      <c r="DB34" s="23"/>
+      <c r="DC34" s="7"/>
       <c r="DD34" s="7"/>
       <c r="DE34" s="7"/>
-      <c r="DF34" s="7"/>
+      <c r="DF34" s="20"/>
       <c r="DG34" s="20"/>
       <c r="DH34" s="20"/>
       <c r="DI34" s="20"/>
       <c r="DJ34" s="20"/>
-      <c r="DK34" s="20"/>
+      <c r="DK34" s="24"/>
       <c r="DL34" s="24"/>
       <c r="DM34" s="24"/>
-      <c r="DN34" s="24"/>
-      <c r="DO34" s="7"/>
-      <c r="DP34" s="20"/>
-      <c r="DQ34" s="23"/>
+      <c r="DN34" s="7"/>
+      <c r="DO34" s="20"/>
+      <c r="DP34" s="23"/>
+      <c r="DQ34" s="7"/>
       <c r="DR34" s="7"/>
       <c r="DS34" s="7"/>
-      <c r="DT34" s="7"/>
+      <c r="DT34" s="20"/>
       <c r="DU34" s="20"/>
       <c r="DV34" s="20"/>
       <c r="DW34" s="20"/>
-      <c r="DX34" s="20"/>
-      <c r="DY34" s="7"/>
-      <c r="DZ34" s="23"/>
-      <c r="EA34" s="20"/>
-      <c r="EB34" s="7"/>
-      <c r="EC34" s="23"/>
-      <c r="ED34" s="20"/>
+      <c r="DX34" s="7"/>
+      <c r="DY34" s="23"/>
+      <c r="DZ34" s="20"/>
+      <c r="EA34" s="7"/>
+      <c r="EB34" s="23"/>
+      <c r="EC34" s="20"/>
+      <c r="ED34" s="7"/>
       <c r="EE34" s="7"/>
       <c r="EF34" s="7"/>
-      <c r="EG34" s="7"/>
+      <c r="EG34" s="20"/>
       <c r="EH34" s="20"/>
       <c r="EI34" s="20"/>
-      <c r="EJ34" s="20"/>
+      <c r="EJ34" s="7"/>
       <c r="EK34" s="7"/>
       <c r="EL34" s="7"/>
       <c r="EM34" s="7"/>
@@ -9500,9 +9463,8 @@
       <c r="GK34" s="7"/>
       <c r="GL34" s="7"/>
       <c r="GM34" s="7"/>
-      <c r="GN34" s="7"/>
-    </row>
-    <row r="35" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -9543,7 +9505,7 @@
       <c r="AL35" s="20"/>
       <c r="AM35" s="20"/>
       <c r="AN35" s="20"/>
-      <c r="AO35" s="20"/>
+      <c r="AO35" s="7"/>
       <c r="AP35" s="7"/>
       <c r="AQ35" s="7"/>
       <c r="AR35" s="7"/>
@@ -9578,12 +9540,12 @@
       <c r="BU35" s="7"/>
       <c r="BV35" s="7"/>
       <c r="BW35" s="7"/>
-      <c r="BX35" s="7"/>
-      <c r="BY35" s="20"/>
-      <c r="BZ35" s="7"/>
-      <c r="CA35" s="20"/>
-      <c r="CB35" s="7"/>
-      <c r="CC35" s="20"/>
+      <c r="BX35" s="20"/>
+      <c r="BY35" s="7"/>
+      <c r="BZ35" s="20"/>
+      <c r="CA35" s="7"/>
+      <c r="CB35" s="20"/>
+      <c r="CC35" s="7"/>
       <c r="CD35" s="7"/>
       <c r="CE35" s="7"/>
       <c r="CF35" s="7"/>
@@ -9592,10 +9554,10 @@
       <c r="CI35" s="7"/>
       <c r="CJ35" s="7"/>
       <c r="CK35" s="7"/>
-      <c r="CL35" s="7"/>
+      <c r="CL35" s="21"/>
       <c r="CM35" s="21"/>
-      <c r="CN35" s="21"/>
-      <c r="CO35" s="22"/>
+      <c r="CN35" s="22"/>
+      <c r="CO35" s="7"/>
       <c r="CP35" s="7"/>
       <c r="CQ35" s="7"/>
       <c r="CR35" s="7"/>
@@ -9608,41 +9570,41 @@
       <c r="CY35" s="7"/>
       <c r="CZ35" s="7"/>
       <c r="DA35" s="7"/>
-      <c r="DB35" s="7"/>
-      <c r="DC35" s="23"/>
+      <c r="DB35" s="23"/>
+      <c r="DC35" s="7"/>
       <c r="DD35" s="7"/>
       <c r="DE35" s="7"/>
-      <c r="DF35" s="7"/>
+      <c r="DF35" s="20"/>
       <c r="DG35" s="20"/>
       <c r="DH35" s="20"/>
       <c r="DI35" s="20"/>
       <c r="DJ35" s="20"/>
-      <c r="DK35" s="20"/>
+      <c r="DK35" s="24"/>
       <c r="DL35" s="24"/>
       <c r="DM35" s="24"/>
-      <c r="DN35" s="24"/>
-      <c r="DO35" s="7"/>
-      <c r="DP35" s="20"/>
-      <c r="DQ35" s="23"/>
+      <c r="DN35" s="7"/>
+      <c r="DO35" s="20"/>
+      <c r="DP35" s="23"/>
+      <c r="DQ35" s="7"/>
       <c r="DR35" s="7"/>
       <c r="DS35" s="7"/>
-      <c r="DT35" s="7"/>
+      <c r="DT35" s="20"/>
       <c r="DU35" s="20"/>
       <c r="DV35" s="20"/>
       <c r="DW35" s="20"/>
-      <c r="DX35" s="20"/>
-      <c r="DY35" s="7"/>
-      <c r="DZ35" s="23"/>
-      <c r="EA35" s="20"/>
-      <c r="EB35" s="7"/>
-      <c r="EC35" s="23"/>
-      <c r="ED35" s="20"/>
+      <c r="DX35" s="7"/>
+      <c r="DY35" s="23"/>
+      <c r="DZ35" s="20"/>
+      <c r="EA35" s="7"/>
+      <c r="EB35" s="23"/>
+      <c r="EC35" s="20"/>
+      <c r="ED35" s="7"/>
       <c r="EE35" s="7"/>
       <c r="EF35" s="7"/>
-      <c r="EG35" s="7"/>
+      <c r="EG35" s="20"/>
       <c r="EH35" s="20"/>
       <c r="EI35" s="20"/>
-      <c r="EJ35" s="20"/>
+      <c r="EJ35" s="7"/>
       <c r="EK35" s="7"/>
       <c r="EL35" s="7"/>
       <c r="EM35" s="7"/>
@@ -9698,9 +9660,8 @@
       <c r="GK35" s="7"/>
       <c r="GL35" s="7"/>
       <c r="GM35" s="7"/>
-      <c r="GN35" s="7"/>
-    </row>
-    <row r="36" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -9741,7 +9702,7 @@
       <c r="AL36" s="20"/>
       <c r="AM36" s="20"/>
       <c r="AN36" s="20"/>
-      <c r="AO36" s="20"/>
+      <c r="AO36" s="7"/>
       <c r="AP36" s="7"/>
       <c r="AQ36" s="7"/>
       <c r="AR36" s="7"/>
@@ -9776,12 +9737,12 @@
       <c r="BU36" s="7"/>
       <c r="BV36" s="7"/>
       <c r="BW36" s="7"/>
-      <c r="BX36" s="7"/>
-      <c r="BY36" s="20"/>
-      <c r="BZ36" s="7"/>
-      <c r="CA36" s="20"/>
-      <c r="CB36" s="7"/>
-      <c r="CC36" s="20"/>
+      <c r="BX36" s="20"/>
+      <c r="BY36" s="7"/>
+      <c r="BZ36" s="20"/>
+      <c r="CA36" s="7"/>
+      <c r="CB36" s="20"/>
+      <c r="CC36" s="7"/>
       <c r="CD36" s="7"/>
       <c r="CE36" s="7"/>
       <c r="CF36" s="7"/>
@@ -9790,10 +9751,10 @@
       <c r="CI36" s="7"/>
       <c r="CJ36" s="7"/>
       <c r="CK36" s="7"/>
-      <c r="CL36" s="7"/>
+      <c r="CL36" s="21"/>
       <c r="CM36" s="21"/>
-      <c r="CN36" s="21"/>
-      <c r="CO36" s="22"/>
+      <c r="CN36" s="22"/>
+      <c r="CO36" s="7"/>
       <c r="CP36" s="7"/>
       <c r="CQ36" s="7"/>
       <c r="CR36" s="7"/>
@@ -9806,41 +9767,41 @@
       <c r="CY36" s="7"/>
       <c r="CZ36" s="7"/>
       <c r="DA36" s="7"/>
-      <c r="DB36" s="7"/>
-      <c r="DC36" s="23"/>
+      <c r="DB36" s="23"/>
+      <c r="DC36" s="7"/>
       <c r="DD36" s="7"/>
       <c r="DE36" s="7"/>
-      <c r="DF36" s="7"/>
+      <c r="DF36" s="20"/>
       <c r="DG36" s="20"/>
       <c r="DH36" s="20"/>
       <c r="DI36" s="20"/>
       <c r="DJ36" s="20"/>
-      <c r="DK36" s="20"/>
+      <c r="DK36" s="24"/>
       <c r="DL36" s="24"/>
       <c r="DM36" s="24"/>
-      <c r="DN36" s="24"/>
-      <c r="DO36" s="7"/>
-      <c r="DP36" s="20"/>
-      <c r="DQ36" s="23"/>
+      <c r="DN36" s="7"/>
+      <c r="DO36" s="20"/>
+      <c r="DP36" s="23"/>
+      <c r="DQ36" s="7"/>
       <c r="DR36" s="7"/>
       <c r="DS36" s="7"/>
-      <c r="DT36" s="7"/>
+      <c r="DT36" s="20"/>
       <c r="DU36" s="20"/>
       <c r="DV36" s="20"/>
       <c r="DW36" s="20"/>
-      <c r="DX36" s="20"/>
-      <c r="DY36" s="7"/>
-      <c r="DZ36" s="23"/>
-      <c r="EA36" s="20"/>
-      <c r="EB36" s="7"/>
-      <c r="EC36" s="23"/>
-      <c r="ED36" s="20"/>
+      <c r="DX36" s="7"/>
+      <c r="DY36" s="23"/>
+      <c r="DZ36" s="20"/>
+      <c r="EA36" s="7"/>
+      <c r="EB36" s="23"/>
+      <c r="EC36" s="20"/>
+      <c r="ED36" s="7"/>
       <c r="EE36" s="7"/>
       <c r="EF36" s="7"/>
-      <c r="EG36" s="7"/>
+      <c r="EG36" s="20"/>
       <c r="EH36" s="20"/>
       <c r="EI36" s="20"/>
-      <c r="EJ36" s="20"/>
+      <c r="EJ36" s="7"/>
       <c r="EK36" s="7"/>
       <c r="EL36" s="7"/>
       <c r="EM36" s="7"/>
@@ -9896,9 +9857,8 @@
       <c r="GK36" s="7"/>
       <c r="GL36" s="7"/>
       <c r="GM36" s="7"/>
-      <c r="GN36" s="7"/>
-    </row>
-    <row r="37" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -9939,7 +9899,7 @@
       <c r="AL37" s="20"/>
       <c r="AM37" s="20"/>
       <c r="AN37" s="20"/>
-      <c r="AO37" s="20"/>
+      <c r="AO37" s="7"/>
       <c r="AP37" s="7"/>
       <c r="AQ37" s="7"/>
       <c r="AR37" s="7"/>
@@ -9974,12 +9934,12 @@
       <c r="BU37" s="7"/>
       <c r="BV37" s="7"/>
       <c r="BW37" s="7"/>
-      <c r="BX37" s="7"/>
-      <c r="BY37" s="20"/>
-      <c r="BZ37" s="7"/>
-      <c r="CA37" s="20"/>
-      <c r="CB37" s="7"/>
-      <c r="CC37" s="20"/>
+      <c r="BX37" s="20"/>
+      <c r="BY37" s="7"/>
+      <c r="BZ37" s="20"/>
+      <c r="CA37" s="7"/>
+      <c r="CB37" s="20"/>
+      <c r="CC37" s="7"/>
       <c r="CD37" s="7"/>
       <c r="CE37" s="7"/>
       <c r="CF37" s="7"/>
@@ -9988,10 +9948,10 @@
       <c r="CI37" s="7"/>
       <c r="CJ37" s="7"/>
       <c r="CK37" s="7"/>
-      <c r="CL37" s="7"/>
+      <c r="CL37" s="21"/>
       <c r="CM37" s="21"/>
-      <c r="CN37" s="21"/>
-      <c r="CO37" s="22"/>
+      <c r="CN37" s="22"/>
+      <c r="CO37" s="7"/>
       <c r="CP37" s="7"/>
       <c r="CQ37" s="7"/>
       <c r="CR37" s="7"/>
@@ -10004,41 +9964,41 @@
       <c r="CY37" s="7"/>
       <c r="CZ37" s="7"/>
       <c r="DA37" s="7"/>
-      <c r="DB37" s="7"/>
-      <c r="DC37" s="23"/>
+      <c r="DB37" s="23"/>
+      <c r="DC37" s="7"/>
       <c r="DD37" s="7"/>
       <c r="DE37" s="7"/>
-      <c r="DF37" s="7"/>
+      <c r="DF37" s="20"/>
       <c r="DG37" s="20"/>
       <c r="DH37" s="20"/>
       <c r="DI37" s="20"/>
       <c r="DJ37" s="20"/>
-      <c r="DK37" s="20"/>
+      <c r="DK37" s="24"/>
       <c r="DL37" s="24"/>
       <c r="DM37" s="24"/>
-      <c r="DN37" s="24"/>
-      <c r="DO37" s="7"/>
-      <c r="DP37" s="20"/>
-      <c r="DQ37" s="23"/>
+      <c r="DN37" s="7"/>
+      <c r="DO37" s="20"/>
+      <c r="DP37" s="23"/>
+      <c r="DQ37" s="7"/>
       <c r="DR37" s="7"/>
       <c r="DS37" s="7"/>
-      <c r="DT37" s="7"/>
+      <c r="DT37" s="20"/>
       <c r="DU37" s="20"/>
       <c r="DV37" s="20"/>
       <c r="DW37" s="20"/>
-      <c r="DX37" s="20"/>
-      <c r="DY37" s="7"/>
-      <c r="DZ37" s="23"/>
-      <c r="EA37" s="20"/>
-      <c r="EB37" s="7"/>
-      <c r="EC37" s="23"/>
-      <c r="ED37" s="20"/>
+      <c r="DX37" s="7"/>
+      <c r="DY37" s="23"/>
+      <c r="DZ37" s="20"/>
+      <c r="EA37" s="7"/>
+      <c r="EB37" s="23"/>
+      <c r="EC37" s="20"/>
+      <c r="ED37" s="7"/>
       <c r="EE37" s="7"/>
       <c r="EF37" s="7"/>
-      <c r="EG37" s="7"/>
+      <c r="EG37" s="20"/>
       <c r="EH37" s="20"/>
       <c r="EI37" s="20"/>
-      <c r="EJ37" s="20"/>
+      <c r="EJ37" s="7"/>
       <c r="EK37" s="7"/>
       <c r="EL37" s="7"/>
       <c r="EM37" s="7"/>
@@ -10094,9 +10054,8 @@
       <c r="GK37" s="7"/>
       <c r="GL37" s="7"/>
       <c r="GM37" s="7"/>
-      <c r="GN37" s="7"/>
-    </row>
-    <row r="38" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -10137,7 +10096,7 @@
       <c r="AL38" s="20"/>
       <c r="AM38" s="20"/>
       <c r="AN38" s="20"/>
-      <c r="AO38" s="20"/>
+      <c r="AO38" s="7"/>
       <c r="AP38" s="7"/>
       <c r="AQ38" s="7"/>
       <c r="AR38" s="7"/>
@@ -10172,12 +10131,12 @@
       <c r="BU38" s="7"/>
       <c r="BV38" s="7"/>
       <c r="BW38" s="7"/>
-      <c r="BX38" s="7"/>
-      <c r="BY38" s="20"/>
-      <c r="BZ38" s="7"/>
-      <c r="CA38" s="20"/>
-      <c r="CB38" s="7"/>
-      <c r="CC38" s="20"/>
+      <c r="BX38" s="20"/>
+      <c r="BY38" s="7"/>
+      <c r="BZ38" s="20"/>
+      <c r="CA38" s="7"/>
+      <c r="CB38" s="20"/>
+      <c r="CC38" s="7"/>
       <c r="CD38" s="7"/>
       <c r="CE38" s="7"/>
       <c r="CF38" s="7"/>
@@ -10186,10 +10145,10 @@
       <c r="CI38" s="7"/>
       <c r="CJ38" s="7"/>
       <c r="CK38" s="7"/>
-      <c r="CL38" s="7"/>
+      <c r="CL38" s="21"/>
       <c r="CM38" s="21"/>
-      <c r="CN38" s="21"/>
-      <c r="CO38" s="22"/>
+      <c r="CN38" s="22"/>
+      <c r="CO38" s="7"/>
       <c r="CP38" s="7"/>
       <c r="CQ38" s="7"/>
       <c r="CR38" s="7"/>
@@ -10202,41 +10161,41 @@
       <c r="CY38" s="7"/>
       <c r="CZ38" s="7"/>
       <c r="DA38" s="7"/>
-      <c r="DB38" s="7"/>
-      <c r="DC38" s="23"/>
+      <c r="DB38" s="23"/>
+      <c r="DC38" s="7"/>
       <c r="DD38" s="7"/>
       <c r="DE38" s="7"/>
-      <c r="DF38" s="7"/>
+      <c r="DF38" s="20"/>
       <c r="DG38" s="20"/>
       <c r="DH38" s="20"/>
       <c r="DI38" s="20"/>
       <c r="DJ38" s="20"/>
-      <c r="DK38" s="20"/>
+      <c r="DK38" s="24"/>
       <c r="DL38" s="24"/>
       <c r="DM38" s="24"/>
-      <c r="DN38" s="24"/>
-      <c r="DO38" s="7"/>
-      <c r="DP38" s="20"/>
-      <c r="DQ38" s="23"/>
+      <c r="DN38" s="7"/>
+      <c r="DO38" s="20"/>
+      <c r="DP38" s="23"/>
+      <c r="DQ38" s="7"/>
       <c r="DR38" s="7"/>
       <c r="DS38" s="7"/>
-      <c r="DT38" s="7"/>
+      <c r="DT38" s="20"/>
       <c r="DU38" s="20"/>
       <c r="DV38" s="20"/>
       <c r="DW38" s="20"/>
-      <c r="DX38" s="20"/>
-      <c r="DY38" s="7"/>
-      <c r="DZ38" s="23"/>
-      <c r="EA38" s="20"/>
-      <c r="EB38" s="7"/>
-      <c r="EC38" s="23"/>
-      <c r="ED38" s="20"/>
+      <c r="DX38" s="7"/>
+      <c r="DY38" s="23"/>
+      <c r="DZ38" s="20"/>
+      <c r="EA38" s="7"/>
+      <c r="EB38" s="23"/>
+      <c r="EC38" s="20"/>
+      <c r="ED38" s="7"/>
       <c r="EE38" s="7"/>
       <c r="EF38" s="7"/>
-      <c r="EG38" s="7"/>
+      <c r="EG38" s="20"/>
       <c r="EH38" s="20"/>
       <c r="EI38" s="20"/>
-      <c r="EJ38" s="20"/>
+      <c r="EJ38" s="7"/>
       <c r="EK38" s="7"/>
       <c r="EL38" s="7"/>
       <c r="EM38" s="7"/>
@@ -10292,9 +10251,8 @@
       <c r="GK38" s="7"/>
       <c r="GL38" s="7"/>
       <c r="GM38" s="7"/>
-      <c r="GN38" s="7"/>
-    </row>
-    <row r="39" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -10335,7 +10293,7 @@
       <c r="AL39" s="20"/>
       <c r="AM39" s="20"/>
       <c r="AN39" s="20"/>
-      <c r="AO39" s="20"/>
+      <c r="AO39" s="7"/>
       <c r="AP39" s="7"/>
       <c r="AQ39" s="7"/>
       <c r="AR39" s="7"/>
@@ -10370,12 +10328,12 @@
       <c r="BU39" s="7"/>
       <c r="BV39" s="7"/>
       <c r="BW39" s="7"/>
-      <c r="BX39" s="7"/>
-      <c r="BY39" s="20"/>
-      <c r="BZ39" s="7"/>
-      <c r="CA39" s="20"/>
-      <c r="CB39" s="7"/>
-      <c r="CC39" s="20"/>
+      <c r="BX39" s="20"/>
+      <c r="BY39" s="7"/>
+      <c r="BZ39" s="20"/>
+      <c r="CA39" s="7"/>
+      <c r="CB39" s="20"/>
+      <c r="CC39" s="7"/>
       <c r="CD39" s="7"/>
       <c r="CE39" s="7"/>
       <c r="CF39" s="7"/>
@@ -10384,10 +10342,10 @@
       <c r="CI39" s="7"/>
       <c r="CJ39" s="7"/>
       <c r="CK39" s="7"/>
-      <c r="CL39" s="7"/>
+      <c r="CL39" s="21"/>
       <c r="CM39" s="21"/>
-      <c r="CN39" s="21"/>
-      <c r="CO39" s="22"/>
+      <c r="CN39" s="22"/>
+      <c r="CO39" s="7"/>
       <c r="CP39" s="7"/>
       <c r="CQ39" s="7"/>
       <c r="CR39" s="7"/>
@@ -10400,41 +10358,41 @@
       <c r="CY39" s="7"/>
       <c r="CZ39" s="7"/>
       <c r="DA39" s="7"/>
-      <c r="DB39" s="7"/>
-      <c r="DC39" s="23"/>
+      <c r="DB39" s="23"/>
+      <c r="DC39" s="7"/>
       <c r="DD39" s="7"/>
       <c r="DE39" s="7"/>
-      <c r="DF39" s="7"/>
+      <c r="DF39" s="20"/>
       <c r="DG39" s="20"/>
       <c r="DH39" s="20"/>
       <c r="DI39" s="20"/>
       <c r="DJ39" s="20"/>
-      <c r="DK39" s="20"/>
+      <c r="DK39" s="24"/>
       <c r="DL39" s="24"/>
       <c r="DM39" s="24"/>
-      <c r="DN39" s="24"/>
-      <c r="DO39" s="7"/>
-      <c r="DP39" s="20"/>
-      <c r="DQ39" s="23"/>
+      <c r="DN39" s="7"/>
+      <c r="DO39" s="20"/>
+      <c r="DP39" s="23"/>
+      <c r="DQ39" s="7"/>
       <c r="DR39" s="7"/>
       <c r="DS39" s="7"/>
-      <c r="DT39" s="7"/>
+      <c r="DT39" s="20"/>
       <c r="DU39" s="20"/>
       <c r="DV39" s="20"/>
       <c r="DW39" s="20"/>
-      <c r="DX39" s="20"/>
-      <c r="DY39" s="7"/>
-      <c r="DZ39" s="23"/>
-      <c r="EA39" s="20"/>
-      <c r="EB39" s="7"/>
-      <c r="EC39" s="23"/>
-      <c r="ED39" s="20"/>
+      <c r="DX39" s="7"/>
+      <c r="DY39" s="23"/>
+      <c r="DZ39" s="20"/>
+      <c r="EA39" s="7"/>
+      <c r="EB39" s="23"/>
+      <c r="EC39" s="20"/>
+      <c r="ED39" s="7"/>
       <c r="EE39" s="7"/>
       <c r="EF39" s="7"/>
-      <c r="EG39" s="7"/>
+      <c r="EG39" s="20"/>
       <c r="EH39" s="20"/>
       <c r="EI39" s="20"/>
-      <c r="EJ39" s="20"/>
+      <c r="EJ39" s="7"/>
       <c r="EK39" s="7"/>
       <c r="EL39" s="7"/>
       <c r="EM39" s="7"/>
@@ -10490,9 +10448,8 @@
       <c r="GK39" s="7"/>
       <c r="GL39" s="7"/>
       <c r="GM39" s="7"/>
-      <c r="GN39" s="7"/>
-    </row>
-    <row r="40" spans="1:196" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:195" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -10533,7 +10490,7 @@
       <c r="AL40" s="20"/>
       <c r="AM40" s="20"/>
       <c r="AN40" s="20"/>
-      <c r="AO40" s="20"/>
+      <c r="AO40" s="7"/>
       <c r="AP40" s="7"/>
       <c r="AQ40" s="7"/>
       <c r="AR40" s="7"/>
@@ -10568,12 +10525,12 @@
       <c r="BU40" s="7"/>
       <c r="BV40" s="7"/>
       <c r="BW40" s="7"/>
-      <c r="BX40" s="7"/>
-      <c r="BY40" s="20"/>
-      <c r="BZ40" s="7"/>
-      <c r="CA40" s="20"/>
-      <c r="CB40" s="7"/>
-      <c r="CC40" s="20"/>
+      <c r="BX40" s="20"/>
+      <c r="BY40" s="7"/>
+      <c r="BZ40" s="20"/>
+      <c r="CA40" s="7"/>
+      <c r="CB40" s="20"/>
+      <c r="CC40" s="7"/>
       <c r="CD40" s="7"/>
       <c r="CE40" s="7"/>
       <c r="CF40" s="7"/>
@@ -10582,10 +10539,10 @@
       <c r="CI40" s="7"/>
       <c r="CJ40" s="7"/>
       <c r="CK40" s="7"/>
-      <c r="CL40" s="7"/>
+      <c r="CL40" s="21"/>
       <c r="CM40" s="21"/>
-      <c r="CN40" s="21"/>
-      <c r="CO40" s="22"/>
+      <c r="CN40" s="22"/>
+      <c r="CO40" s="7"/>
       <c r="CP40" s="7"/>
       <c r="CQ40" s="7"/>
       <c r="CR40" s="7"/>
@@ -10598,41 +10555,41 @@
       <c r="CY40" s="7"/>
       <c r="CZ40" s="7"/>
       <c r="DA40" s="7"/>
-      <c r="DB40" s="7"/>
-      <c r="DC40" s="23"/>
+      <c r="DB40" s="23"/>
+      <c r="DC40" s="7"/>
       <c r="DD40" s="7"/>
       <c r="DE40" s="7"/>
-      <c r="DF40" s="7"/>
+      <c r="DF40" s="20"/>
       <c r="DG40" s="20"/>
       <c r="DH40" s="20"/>
       <c r="DI40" s="20"/>
       <c r="DJ40" s="20"/>
-      <c r="DK40" s="20"/>
+      <c r="DK40" s="24"/>
       <c r="DL40" s="24"/>
       <c r="DM40" s="24"/>
-      <c r="DN40" s="24"/>
-      <c r="DO40" s="7"/>
-      <c r="DP40" s="20"/>
-      <c r="DQ40" s="23"/>
+      <c r="DN40" s="7"/>
+      <c r="DO40" s="20"/>
+      <c r="DP40" s="23"/>
+      <c r="DQ40" s="7"/>
       <c r="DR40" s="7"/>
       <c r="DS40" s="7"/>
-      <c r="DT40" s="7"/>
+      <c r="DT40" s="20"/>
       <c r="DU40" s="20"/>
       <c r="DV40" s="20"/>
       <c r="DW40" s="20"/>
-      <c r="DX40" s="20"/>
-      <c r="DY40" s="7"/>
-      <c r="DZ40" s="23"/>
-      <c r="EA40" s="20"/>
-      <c r="EB40" s="7"/>
-      <c r="EC40" s="23"/>
-      <c r="ED40" s="20"/>
+      <c r="DX40" s="7"/>
+      <c r="DY40" s="23"/>
+      <c r="DZ40" s="20"/>
+      <c r="EA40" s="7"/>
+      <c r="EB40" s="23"/>
+      <c r="EC40" s="20"/>
+      <c r="ED40" s="7"/>
       <c r="EE40" s="7"/>
       <c r="EF40" s="7"/>
-      <c r="EG40" s="7"/>
+      <c r="EG40" s="20"/>
       <c r="EH40" s="20"/>
       <c r="EI40" s="20"/>
-      <c r="EJ40" s="20"/>
+      <c r="EJ40" s="7"/>
       <c r="EK40" s="7"/>
       <c r="EL40" s="7"/>
       <c r="EM40" s="7"/>
@@ -10688,42 +10645,41 @@
       <c r="GK40" s="7"/>
       <c r="GL40" s="7"/>
       <c r="GM40" s="7"/>
-      <c r="GN40" s="7"/>
-    </row>
-    <row r="41" spans="1:196" x14ac:dyDescent="0.2">
-      <c r="CM41" s="26"/>
+    </row>
+    <row r="41" spans="1:195" x14ac:dyDescent="0.2">
+      <c r="CL41" s="26"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:EJ41" xr:uid="{1D7D8389-CC47-1246-87AB-996B447D177D}"/>
+  <autoFilter ref="A2:EI41" xr:uid="{1D7D8389-CC47-1246-87AB-996B447D177D}"/>
   <mergeCells count="21">
+    <mergeCell ref="DX1:EC1"/>
+    <mergeCell ref="ED1:EI1"/>
+    <mergeCell ref="GD1:GI1"/>
+    <mergeCell ref="EN1:GC1"/>
+    <mergeCell ref="EK1:EM1"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="CR1:DD1"/>
-    <mergeCell ref="DT1:DX1"/>
+    <mergeCell ref="CQ1:DC1"/>
+    <mergeCell ref="DS1:DW1"/>
     <mergeCell ref="E1:H1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AX1:BB1"/>
-    <mergeCell ref="BC1:BL1"/>
-    <mergeCell ref="BM1:BW1"/>
-    <mergeCell ref="BX1:CG1"/>
-    <mergeCell ref="DE1:DG1"/>
-    <mergeCell ref="DH1:DP1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="I1:AM1"/>
-    <mergeCell ref="AP1:AR1"/>
-    <mergeCell ref="DQ1:DS1"/>
-    <mergeCell ref="CH1:CQ1"/>
-    <mergeCell ref="DY1:ED1"/>
-    <mergeCell ref="EE1:EJ1"/>
-    <mergeCell ref="GE1:GJ1"/>
-    <mergeCell ref="EO1:GD1"/>
-    <mergeCell ref="EL1:EN1"/>
+    <mergeCell ref="AR1:AV1"/>
+    <mergeCell ref="AW1:BA1"/>
+    <mergeCell ref="BB1:BK1"/>
+    <mergeCell ref="BL1:BV1"/>
+    <mergeCell ref="BW1:CF1"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DG1:DO1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="I1:AL1"/>
+    <mergeCell ref="AO1:AQ1"/>
+    <mergeCell ref="DP1:DR1"/>
+    <mergeCell ref="CG1:CP1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="AW3" r:id="rId1" xr:uid="{5A46F90C-9D74-2241-85EE-A756047D2EFB}"/>
-    <hyperlink ref="BB3" r:id="rId2" xr:uid="{59C4D77B-3A18-AA4D-9C0D-FA8F9DF44FAC}"/>
-    <hyperlink ref="BK3" r:id="rId3" display="mailto:john.smith@lpa.co.uk" xr:uid="{AB0C2625-FF88-F84D-850E-C8683731B219}"/>
-    <hyperlink ref="BV3" r:id="rId4" xr:uid="{B4107AFD-646D-8247-8F48-EBE92F490E63}"/>
+    <hyperlink ref="AV3" r:id="rId1" xr:uid="{5A46F90C-9D74-2241-85EE-A756047D2EFB}"/>
+    <hyperlink ref="BA3" r:id="rId2" xr:uid="{59C4D77B-3A18-AA4D-9C0D-FA8F9DF44FAC}"/>
+    <hyperlink ref="BJ3" r:id="rId3" display="mailto:john.smith@lpa.co.uk" xr:uid="{AB0C2625-FF88-F84D-850E-C8683731B219}"/>
+    <hyperlink ref="BU3" r:id="rId4" xr:uid="{B4107AFD-646D-8247-8F48-EBE92F490E63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId5"/>
@@ -10758,49 +10714,49 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$21:$A$30</xm:f>
           </x14:formula1>
-          <xm:sqref>AS3:AS40 AX3:AX40</xm:sqref>
+          <xm:sqref>AR3:AR40 AW3:AW40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{532019B4-5ECC-E84A-BC22-066ADC9BEF33}">
           <x14:formula1>
             <xm:f>Sheet2!$A$33:$A$34</xm:f>
           </x14:formula1>
-          <xm:sqref>BM3:BM40</xm:sqref>
+          <xm:sqref>BL3:BL40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{76D12EEA-444B-F645-9861-A3D523F1A936}">
           <x14:formula1>
             <xm:f>Sheet2!$A$37:$A$39</xm:f>
           </x14:formula1>
-          <xm:sqref>CT3:CT40</xm:sqref>
+          <xm:sqref>CS3:CS40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{67C58EBB-C243-D846-AA9B-60DD3821727B}">
           <x14:formula1>
             <xm:f>Sheet2!$A$42:$A$51</xm:f>
           </x14:formula1>
-          <xm:sqref>CS5:CS40 CS3</xm:sqref>
+          <xm:sqref>CR5:CR40 CR3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2A7BEC16-8476-0D46-87AE-984416E2CE46}">
           <x14:formula1>
             <xm:f>Sheet2!$A$54:$A$55</xm:f>
           </x14:formula1>
-          <xm:sqref>CP3:CP40</xm:sqref>
+          <xm:sqref>CO3:CO40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FEDEE41E-8D0C-D741-AE90-E2D589304134}">
           <x14:formula1>
             <xm:f>Sheet2!$A$61:$A$62</xm:f>
           </x14:formula1>
-          <xm:sqref>EF3:EF40</xm:sqref>
+          <xm:sqref>EE3:EE40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{76A2E0C4-BC97-D748-AC85-375A811A7E21}">
           <x14:formula1>
             <xm:f>Sheet2!$A$65:$A$66</xm:f>
           </x14:formula1>
-          <xm:sqref>EG3:EG40</xm:sqref>
+          <xm:sqref>EF3:EF40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9A0D4856-A55A-F24B-9214-9A5A986AAAC4}">
           <x14:formula1>
             <xm:f>Sheet2!$A$69:$A$84</xm:f>
           </x14:formula1>
-          <xm:sqref>CU3:CU40</xm:sqref>
+          <xm:sqref>CT3:CT40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{719F229F-027A-9A4A-A470-8C5C9A971ED4}">
           <x14:formula1>
@@ -10818,19 +10774,19 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$57:$A$58</xm:f>
           </x14:formula1>
-          <xm:sqref>CY3:CY40 CV3:CV40 DB3:DB40 AP3:AP40 DY3:DY40 EB3:EB40 DT3:DT40 DD3:DF40</xm:sqref>
+          <xm:sqref>CX3:CX40 CU3:CU40 DA3:DA40 AO3:AO40 DX3:DX40 EA3:EA40 DS3:DS40 DC3:DE40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{28AA7E49-2286-3248-BF5A-39ACA006F781}">
           <x14:formula1>
             <xm:f>Sheet2!$A$114:$A$115</xm:f>
           </x14:formula1>
-          <xm:sqref>DA3:DA40</xm:sqref>
+          <xm:sqref>CZ3:CZ40</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6B7CC7B6-908B-5543-BB33-A57F17C85436}">
           <x14:formula1>
             <xm:f>Sheet2!$A$118:$A$119</xm:f>
           </x14:formula1>
-          <xm:sqref>AL3:AL40</xm:sqref>
+          <xm:sqref>AK3:AK40</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11487,12 +11443,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f1c51713-a7b9-4899-a01c-db85572982cc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3ac97f74-887d-4038-a207-790912953edc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11703,20 +11661,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f1c51713-a7b9-4899-a01c-db85572982cc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3ac97f74-887d-4038-a207-790912953edc" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D4EAE7A-B432-4F08-90D6-081071C41FC4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB839FD4-FF38-42DD-92C4-398A48A6D7F1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="3ac97f74-887d-4038-a207-790912953edc"/>
+    <ds:schemaRef ds:uri="f1c51713-a7b9-4899-a01c-db85572982cc"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11741,18 +11706,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB839FD4-FF38-42DD-92C4-398A48A6D7F1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D4EAE7A-B432-4F08-90D6-081071C41FC4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="3ac97f74-887d-4038-a207-790912953edc"/>
-    <ds:schemaRef ds:uri="f1c51713-a7b9-4899-a01c-db85572982cc"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>